--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quotations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="quotations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="items" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,66 +624,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SKRTB67OEL</t>
+          <t>SKB8DXCYGE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salobo 2</t>
+          <t>Dilmatec</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
+          <t>Diagnostico e resoluçao problema em 02 equipamentos que nao estavam atingindo temperatura</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="b">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-04T15:24:13.519Z</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>2025-08-28T15:35:41.479Z</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NjU3ZmQ5M2UtYjlmZC00NTdmLTlmM2EtZGI0YzE2MmZhMGQ3OjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -701,79 +701,75 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>RAFAEL BARBOZA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
+          <t>2025-08-08T18:27:17.728Z</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -784,44 +780,44 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Substituição de 3 compressores</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -830,39 +826,43 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>2023-06-07T21:55:05.692Z</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>jose da silva</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>HENRIQUE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -873,105 +873,194 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2024-09-05T20:49:15.417Z</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>NDIxMTExMTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -988,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,91 +1175,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
+          <t>MTc3NWUyYTAtZjAxNy00NWQwLTg2ZTMtYWFiZjYzMzZhOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>47370</v>
+        <v>680</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>NGMwNTQyYWMtNGNjZC00NjljLThlZWItMDYxMjg2NzkzMmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>10000</v>
+        <v>855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10000</v>
+        <v>855</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1185,7 +1278,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1203,25 +1296,25 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1229,23 +1322,107 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,7 +644,7 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -667,23 +667,27 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Rafael Machado Barboza</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/2a7e8c69-1223-41d3-967d-474788d2fb01/signatures/51c1ade7-ff37-4ee9-b84d-46ee75381607.png</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>2025-08-28T15:35:41.479Z</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>NjU3ZmQ5M2UtYjlmZC00NTdmLTlmM2EtZGI0YzE2MmZhMGQ3OjU3MDE2</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -706,7 +710,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -802,67 +806,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
+          <t>2025-08-28T16:05:56.490Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -873,85 +873,89 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Substituição de 3 compressores</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>2023-06-07T21:55:05.692Z</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>jose da silva</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>HENRIQUE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -962,105 +966,287 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Aprovada</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2025-09-04T16:07:52.834Z</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-08-28T16:10:11.398Z</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HYICEAM_GE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>47370</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>47370</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Recusada</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>RAFAEL BARBOZA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2024-09-12T20:48:10.536Z</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2024-09-05T20:49:15.417Z</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>NDIxMTExMTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1077,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1207,7 +1393,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1303,75 +1489,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>10000</v>
+        <v>680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10000</v>
+        <v>680</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>47370</v>
+        <v>855</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1380,25 +1570,25 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1406,23 +1596,195 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>680</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>680</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>855</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>855</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,27 +717,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+          <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKRTB67OEL</t>
+          <t>HYS55O45GG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Salobo 2</t>
+          <t>Bayer Uberlandia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Teste</t>
+          <t>Cliente informa: equipamento nao gela
+Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
+Diagnostico do  tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo do  nitrogenio que vai utlizado + laudo de garrafa  maçarico e caneta (laudo )  para poder entrar com esses produtos para realizaçao do atendimento 
+senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer
+OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Teste</t>
+          <t>Cliente informa: equipamento nao gela
+Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
+Diagnostico do  tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo do  nitrogenio que vai utlizado + laudo de garrafa  maçarico e caneta (laudo )  para poder entrar com esses produtos para realizaçao do atendimento 
+senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer
+OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -745,35 +753,35 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
+          <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -794,39 +802,39 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+          <t>Teste</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+          <t>Teste</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -834,35 +842,35 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
+          <t>2025-08-08T18:27:17.728Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -883,79 +891,75 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
+          <t>2025-08-28T16:05:56.490Z</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -966,58 +970,58 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1027,28 +1031,28 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>rffccfc</t>
+          <t>jose da silva</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>HENRIQUE</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
+          <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1059,17 +1063,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1081,22 +1085,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
+          <t>teste</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Substituição de 3 compressores</t>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1105,39 +1109,43 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>2025-09-04T16:07:52.834Z</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1158,97 +1166,285 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2024-09-05T20:49:15.417Z</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>NDIxMTExMTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HJE6OUN5LE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bayer Uberlandia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cliente informa: equipamento nao gela
+Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
+Diagnostico do  tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo do  nitrogenio que vai utlizado + laudo de garrafa  maçarico e caneta (laudo )  para poder entrar com esses produtos para realizaçao do atendimento 
+senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cliente informa: equipamento nao gela
+Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
+Diagnostico tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo nitrogenio, maçarico (laudo da garrafa) e caneta para poder entrar com esses produtos para realizaçao do atendimento 
+senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2025-09-09T13:53:17.012Z</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1449,31 +1645,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
+          <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>1700</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cliente informa: equipamento nao gela
+Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
+Diagnostico tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo nitrogenio, maçarico (laudo da garrafa) e caneta para poder entrar com esses produtos para realizaçao do atendimento 
+senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
+        </is>
+      </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+          <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>47370</v>
+        <v>1700</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1482,42 +1685,38 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+          <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
+          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>680</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>47370</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>680</v>
+        <v>47370</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1526,25 +1725,25 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1557,11 +1756,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1577,106 +1776,106 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>10000</v>
+        <v>855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10000</v>
+        <v>855</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>680</v>
+        <v>10000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>680</v>
+        <v>10000</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1689,11 +1888,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1709,31 +1908,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>47370</v>
+        <v>855</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1742,51 +1945,138 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
-        </is>
-      </c>
+        <v>47370</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H13" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1700</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cliente informa: equipamento nao gela
+Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
+Diagnostico tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo nitrogenio, maçarico (laudo da garrafa) e caneta para poder entrar com esses produtos para realizaçao do atendimento 
+senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1700</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,50 +903,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -959,10 +955,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+          <t>2025-09-08T22:01:45.251Z</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -980,79 +980,75 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
+          <t>2025-08-28T16:05:56.490Z</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1063,58 +1059,58 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1124,28 +1120,28 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>rffccfc</t>
+          <t>jose da silva</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>HENRIQUE</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
+          <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1156,17 +1152,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1178,22 +1174,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
+          <t>teste</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Substituição de 3 compressores</t>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1202,39 +1198,43 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>2025-09-04T16:07:52.834Z</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1255,74 +1255,78 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1340,32 +1344,117 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1373,7 +1462,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1381,68 +1470,153 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F11" t="b">
+      <c r="F12" t="b">
         <v>0</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>1700</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>1700</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>2025-09-02T14:01:32.021Z</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BYOHBAHQXX</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5996.77</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5996.77</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2025-09-15T21:48:09.008Z</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-09-08T21:59:15.256Z</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
@@ -1459,7 +1633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1732,35 +1906,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
+          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>680</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>1050</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>680</v>
+        <v>1050</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1769,25 +1939,38 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
+          <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>855</v>
+        <v>494677</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+          <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
+B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
+B527034 - MANTA ISOL FIBRA CERAMICA  ALUM 3810X610X38MM 2.32 M³ P/ROLO Qtd = 0,2 M2
+B538109 - TERMINAL C/ ISOLACAO CABO 1,5 - 2,5MM OLHAL AZUL TP2,5-4 - INTELLI Qtd = 6 PC
+B538119 - LUVA C/ ISOLACAO CABO 1,5 / 2,5 (EMENDA AZUL) INTELLI LEP-22 Qtd = 2 PC
+B538121 - CONJ.TERMOSTATO CAEM TU HC 120°C 30A 5MMX080MM 980MM 3/8CBP Qtd = 1 PC
+B538233 - INTERRUPTOR DE TECLA MARGIRUS 30223 M2FT1DE3Q/197 BIP. 10A VERDE Qtd = 1 PC
+B538345 - CABO ELETRICO FLEX. 1,5MM SILICONE C/ FIBRA DE VIDRO 200º Qtd = 2 MT
+B538683 - CABO PP C/PLUG CABO INJETADO 90º10A(3.0X1.5X2000MM) Qtd = 1 PC
+B538806 - TERMINAL DE ENCAIXE FEMEA "FASTON" C/ ISOL. (AZUL 1,5 - 2,5MM) Qtd = 4 PC
+B538A84 - PRENSA CABO BSP 1/2 LP+P/UV-LT-PA-40 DAN KRAUS MULLER Qtd = 1 PC
+B538I97 - ESPELHO PLASTICO CAEM PRETO Qtd = 1 PC
+B546053 - MICROVENT. LINEAR 110/220V 60HZ MOD. MINILINE Qtd = 1 PC
+B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1795,87 +1978,87 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>855</v>
+        <v>494677</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>10000</v>
+        <v>680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10000</v>
+        <v>680</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>680</v>
+        <v>855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1883,16 +2066,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>680</v>
+        <v>855</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1901,82 +2084,86 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>855</v>
+        <v>10000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>855</v>
+        <v>10000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>47370</v>
+        <v>680</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1985,67 +2172,151 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>855</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
         <v>1700</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2053,30 +2324,127 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E16" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H16" t="n">
         <v>1700</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>494677</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
+B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
+B527034 - MANTA ISOL FIBRA CERAMICA  ALUM 3810X610X38MM 2.32 M³ P/ROLO Qtd = 0,2 M2
+B538109 - TERMINAL C/ ISOLACAO CABO 1,5 - 2,5MM OLHAL AZUL TP2,5-4 - INTELLI Qtd = 6 PC
+B538119 - LUVA C/ ISOLACAO CABO 1,5 / 2,5 (EMENDA AZUL) INTELLI LEP-22 Qtd = 2 PC
+B538121 - CONJ.TERMOSTATO CAEM TU HC 120°C 30A 5MMX080MM 980MM 3/8CBP Qtd = 1 PC
+B538233 - INTERRUPTOR DE TECLA MARGIRUS 30223 M2FT1DE3Q/197 BIP. 10A VERDE Qtd = 1 PC
+B538345 - CABO ELETRICO FLEX. 1,5MM SILICONE C/ FIBRA DE VIDRO 200º Qtd = 2 MT
+B538683 - CABO PP C/PLUG CABO INJETADO 90º10A(3.0X1.5X2000MM) Qtd = 1 PC
+B538806 - TERMINAL DE ENCAIXE FEMEA "FASTON" C/ ISOL. (AZUL 1,5 - 2,5MM) Qtd = 4 PC
+B538A84 - PRENSA CABO BSP 1/2 LP+P/UV-LT-PA-40 DAN KRAUS MULLER Qtd = 1 PC
+B538I97 - ESPELHO PLASTICO CAEM PRETO Qtd = 1 PC
+B546053 - MICROVENT. LINEAR 110/220V 60HZ MOD. MINILINE Qtd = 1 PC
+B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>494677</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -937,7 +937,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,20 +717,113 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HJ0GXQO2EG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>JOANA DARC OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Orçamento  para reforma de TFK 02 kg</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Reforma</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2167.29</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2167.29</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2025-10-06T13:42:48.402Z</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-29T15:17:10.234Z</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>MzM3ODI5ODo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -739,7 +832,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -748,106 +841,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -857,20 +861,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
+          <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -891,7 +895,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -903,36 +907,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SJBLZ0HQLG</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OUTBACK MORUMBI</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -942,27 +950,23 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:27:17.728Z</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -980,7 +984,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -992,40 +996,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1048,10 +1048,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>2025-09-08T22:01:45.251Z</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1069,7 +1073,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1081,67 +1085,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
+          <t>2025-08-28T16:05:56.490Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1152,58 +1152,58 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1213,28 +1213,28 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>rffccfc</t>
+          <t>jose da silva</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>HENRIQUE</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
+          <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1267,22 +1267,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
+          <t>teste</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Substituição de 3 compressores</t>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -1291,39 +1291,43 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>2025-09-04T16:07:52.834Z</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1344,74 +1348,78 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1429,32 +1437,117 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1462,7 +1555,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1470,106 +1563,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1579,7 +1583,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1592,31 +1596,120 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BYOHBAHQXX</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>5996.77</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>5996.77</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2025-09-15T21:48:09.008Z</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>2025-09-08T21:59:15.256Z</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1633,7 +1726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,16 +1912,656 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>MDFmODQ2OWUtMmMyMC00NzEwLWE4NTEtMmFkOWFjYjRlYjQ2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NDUwZmFlOTEtODg1My00ZTcwLWIwOTgtZWM2Nzc3MzgzNjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MjhmNDNmYjAtZjgzMi00MThiLWEyNTAtZWVlODc0ZjQxYzliOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1365</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MmQyOGU2OWYtM2IzOS00ZjYwLWJmYTctYmViYTY2M2UxNzdjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>375</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>18</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>375</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MzVjNDRmYjctMTI1My00NDg3LThlNmUtOWZhN2YyYWMyNjg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.152e+16</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NDM0MjA4NTAtZjAwOC00YzMyLWJlM2QtODFlMzljMjE0OTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.152e+16</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NDNkMGNjZmMtMjFmMS00NjQyLWI4OWYtYTk4ODg2NjkxMjcwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>84</v>
+      </c>
+      <c r="C9" t="n">
+        <v>168</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NDRlYzI5NjAtMTZmYi00MzM3LWEzZTEtNGJmOTg0Y2Y1MzFhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>700</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>18</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>350</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>N2NjNjliYTAtNTVlZi00NjNmLThkMmUtZGMzYzIyZjRhM2FiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>350</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>350</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OTg0ZDY5MWUtZTJiZS00NmM0LTg1OGMtNDQ1ZTMwMmY2MWE3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>85</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>85</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OWRkMWJkNWQtMjE5Yy00OTY0LWExNzYtZTI4YzkyN2Q4ODdlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>72</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Y2FjZGRiY2YtOTQ5NS00NDIyLWE4ODctYjk4ZGUxNjU1MzMyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>18</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>YTAxNDZjNzgtMDljZi00ZGQ4LTkwOTItZmM5N2QyNzM3MGEwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>18025</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>18025</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>YTM1YmFkNmQtN2EzNS00Njk0LTliNTMtNmZiMjAwNzQ5NzFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>25625</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MTdjYWQ5ZTAtMmQ3YS00OTM0LWIyOGEtYzMxYjY1ODZkNDIzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>25625</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>YzFlYTExODctMmJkNy00N2RhLThiMTQtZTVjMTY0NWY1Y2Y5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>182225</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>18</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>OWU3NmYwYWEtZWNhZi00YTBiLWE2NTUtNjE5NTkwNDIwZDNjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>182225</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>YzRiYzAxZjEtOWY2Zi00ZWQ0LWJmMjgtZmYxY2RjNjY1OTBiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>9940000000000000</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>18</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>OWMxNWU5ZjUtOWI3Ny00ZmYyLWExMWYtM2RkYzA3ZWFjYzU5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>9940000000000000</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ZGMxMDhlMDAtNmY3Ni00OWE1LTg0MDMtZjVmNjUyZGVkNzZlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2073</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>18</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2073</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ZjczNzc1Y2UtNGU2Mi00NGEzLTk5NWUtYzRlZmRjMzFhMTI2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>36</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ZmQ5YTY2ZWEtZDM4NS00MWMwLWI0NWYtODI3ZjAxNzRjNzE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>9</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ZmQ3OWNiYjEtZmY3Yi00MjVkLWJhODgtYjA3NjQyZWY1MzYwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1578</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>18</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Y2I2NzA1MTItNDc5NS00ZWVmLWJkOTktY2JlZmJiZTNmNTFlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1578</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
         <v>1700</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1836,126 +2569,126 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E21" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H21" t="n">
         <v>1700</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
         <v>47370</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H22" t="n">
         <v>47370</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
         <v>1050</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H23" t="n">
         <v>1050</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
         <v>494677</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -1973,350 +2706,350 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E24" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H24" t="n">
         <v>494677</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
         <v>680</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E25" t="n">
         <v>3</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H25" t="n">
         <v>680</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
         <v>855</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E26" t="n">
         <v>3</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H26" t="n">
         <v>855</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
         <v>10000</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E27" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H27" t="n">
         <v>10000</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
         <v>680</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E28" t="n">
         <v>3</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H28" t="n">
         <v>680</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
         <v>855</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E29" t="n">
         <v>3</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H29" t="n">
         <v>855</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
         <v>47370</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="n">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H30" t="n">
         <v>47370</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>ORCAMENTO REALIZADO PELO BLING</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E31" t="n">
         <v>2</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
         <v>1700</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2324,46 +3057,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E32" t="n">
         <v>2</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="H32" t="n">
         <v>1700</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
         <v>494677</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -2381,68 +3114,68 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E33" t="n">
         <v>3</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="H33" t="n">
         <v>494677</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
         <v>1050</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
         <v>3</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="H34" t="n">
         <v>1050</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -810,20 +810,190 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HYTE7IDHEX</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MAQUINA 02</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>979.73</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>979.73</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2025-10-06T18:41:42.725Z</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-29T18:42:56.833Z</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SYLVG8O3EG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MAQUINA 01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1298.9</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1298.9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2025-10-06T18:34:31.188Z</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-29T18:38:37.635Z</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -832,7 +1002,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -841,191 +1011,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>47370</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>47370</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2025-08-15T18:25:59.379Z</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>RAFAEL BARBOZA</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:27:17.728Z</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SJBLZ0HQLG</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="b">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1035,7 +1031,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1048,14 +1044,10 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-09-02T14:09:17.339Z</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1073,7 +1065,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1085,27 +1077,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+          <t>Teste</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+          <t>Teste</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1113,12 +1105,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1128,20 +1120,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
+          <t>2025-08-08T18:27:17.728Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1162,7 +1154,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1174,70 +1166,66 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
+          <t>2025-09-08T22:01:45.251Z</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1245,92 +1233,84 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>rffccfc</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1348,75 +1328,75 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Substituição de 3 compressores</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
+          <t>2025-09-04T16:01:06.048Z</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-08-28T16:05:56.490Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1437,74 +1417,82 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>TESTE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TESTE</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>jose da silva</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>HENRIQUE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2023-05-31T21:56:50.448Z</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1512,42 +1500,309 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S1SWKWAKXG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Aprovada</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2025-09-04T16:07:52.834Z</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-08-28T16:10:11.398Z</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HYICEAM_GE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>47370</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>47370</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Recusada</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>RAFAEL BARBOZA</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1555,7 +1810,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1563,153 +1818,153 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F13" t="b">
+      <c r="F16" t="b">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>1700</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>1700</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>2025-09-02T14:01:32.021Z</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>BYOHBAHQXX</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>OUTBACK MORUMBI</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="b">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="b">
         <v>0</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>5996.77</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>5996.77</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>2025-09-08T21:59:15.256Z</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -1726,7 +1981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2552,16 +2807,616 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>MTE0NDUwMGUtM2ZiMi00OWQ1LWFmY2EtMzNjNzZmNjBhMTVmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>350</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>350</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NWM5YzAxYzktMTIwMS00ZjhkLWJjOGMtN2U3NDlmOTlmMzRkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>85</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>85</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NjRmMDVhODItNmU2Mi00ZDRhLTk5NmItNzM2ODI0YjE2MjRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1365</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OGUzMjVkZDYtOTA3Yi00MjFjLWFjYzgtOWVlMGI3MjJkNjIzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>350</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>350</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Yjk2YzIwMDktMzVkMy00ZGRjLWIwOTYtOTJjOWFlMjZiM2FhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>375</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>375</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ZTA0MDdkOTgtNjJjMi00ZTgyLWFmMzEtYzg4MzdkYzhjYmMzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2073</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2073</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MDhmZjQ1YWQtNTY2Yi00YTlkLWIyMWEtZDI5Y2RkYThlODAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>9</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>N2EyYTQzZjktNzgxZi00Mzk2LWEyNzMtODM0NmViMTE4MWE2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>85</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>85</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OWIyYjYwOTktYTg5MC00ZjRhLWEzOGMtNDI3YTE2MTA1NTI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>700</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>350</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>YTJjM2ExNTAtOWExYi00Mzk1LWE1N2MtM2JkYTU3MDBiMzhlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>375</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>375</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>YTYxMjU3ODEtZjY4ZS00MDQyLTg5YmItYzg1YTA3YTdmZmY5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>350</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>350</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>YTg1ZmQyOGMtNDZkOC00YTgwLWJhODUtOGI5OTA5ZDliZjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>YTlhNDQ1NWItMWI4OS00ZGM0LThiOTgtMzZlOTcxNTE0NzcyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2073</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>10</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>2073</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ZTZmYzJiNjEtYzBjNS00NjM2LWI0YmEtNzZlMGE1NWI2ODIwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2502</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>2502</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ZWQ1NDY3MTUtZjAxMC00OTM2LTljZDctNzBmMjRlZjVhYTQwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>6325</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>6325</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="n">
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
         <v>1700</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2569,126 +3424,126 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E36" t="n">
         <v>2</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="H36" t="n">
         <v>1700</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="n">
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
         <v>47370</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="H37" t="n">
         <v>47370</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="n">
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
         <v>1050</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
         <v>3</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="H38" t="n">
         <v>1050</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="n">
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
         <v>494677</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -2706,350 +3561,550 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E39" t="n">
         <v>3</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="H39" t="n">
         <v>494677</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NWUzYWQ2Y2ItMGM4NC00YjkwLThjYjQtZjNhNjEyZGE0M2NjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>350</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>350</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>YzBmZmExOTEtNmY5Ni00NTlkLWI4ZmYtZWJjNjliN2JhZmVmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2073</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>2073</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ZDY5M2E2MjItZmI3OC00YmJiLTg1NWItMzFjY2RlOTg0YWUyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>375</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>375</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ZDcyNzVkNDktZjNlYy00ZmZhLWFkNzAtZTRjMmI0NTk0YWZhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7375</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>7375</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ZjQ0M2Q5ZWQtNjg1YS00MjA1LWFlNDgtY2FhM2ExODdlNTMwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="n">
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
         <v>680</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E45" t="n">
         <v>3</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="H45" t="n">
         <v>680</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="n">
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
         <v>855</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E46" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="H46" t="n">
         <v>855</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="n">
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
         <v>10000</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E47" t="n">
         <v>2</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="H47" t="n">
         <v>10000</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="n">
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
         <v>680</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E48" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="H48" t="n">
         <v>680</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="n">
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
         <v>855</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E49" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="H49" t="n">
         <v>855</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="n">
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
         <v>47370</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="n">
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
         <v>2</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="H50" t="n">
         <v>47370</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>ORCAMENTO REALIZADO PELO BLING</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E51" t="n">
         <v>2</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="n">
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
         <v>1700</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -3057,46 +4112,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E52" t="n">
         <v>2</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="H52" t="n">
         <v>1700</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="n">
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
         <v>494677</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -3114,68 +4169,68 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E53" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="H53" t="n">
         <v>494677</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="n">
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
         <v>1050</v>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="n">
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="H54" t="n">
         <v>1050</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -3591,7 +3591,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NWUzYWQ2Y2ItMGM4NC00YjkwLThjYjQtZjNhNjEyZGE0M2NjOjU3MDE2</t>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -3631,7 +3631,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>YzBmZmExOTEtNmY5Ni00NTlkLWI4ZmYtZWJjNjliN2JhZmVmOjU3MDE2</t>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -3671,14 +3671,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ZDY5M2E2MjItZmI3OC00YmJiLTg1NWItMzFjY2RlOTg0YWUyOjU3MDE2</t>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>375</v>
+        <v>7375</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
@@ -3691,11 +3691,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>375</v>
+        <v>7375</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3711,14 +3711,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ZDcyNzVkNDktZjNlYy00ZmZhLWFkNzAtZTRjMmI0NTk0YWZhOjU3MDE2</t>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>7375</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
@@ -3731,11 +3731,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>7375</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3751,14 +3751,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ZjQ0M2Q5ZWQtNjg1YS00MjA1LWFlNDgtY2FhM2ExODdlNTMwOjU3MDE2</t>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>8399999999999999</v>
+        <v>375</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
@@ -3771,11 +3771,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8399999999999999</v>
+        <v>375</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,6 +1967,96 @@
       <c r="U17" t="inlineStr">
         <is>
           <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R1BQOWO2EE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
+BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2025-10-06T19:05:55.326Z</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-09-29T20:26:53.403Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>NDgyNTE1Mzo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1981,7 +2071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4236,6 +4326,490 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>43</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CORREIO VIA SEDEX 43,00</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>13</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>43</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3325</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>13</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>3325</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>717</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>13</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>717</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>7375</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>13</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>7375</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>117</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>13</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>117</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4.2e+16</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>13</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>4.2e+16</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>6449999999999999</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>13</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>6449999999999999</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>48</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>13</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>48</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>475</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>13</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>475</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1725</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>13</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>13</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>13</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,40 +717,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HJ0GXQO2EG</t>
+          <t>RYUVNWH3EG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JOANA DARC OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Orçamento  para reforma de TFK 02 kg</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Reforma</t>
-        </is>
-      </c>
+          <t>GARANTIA/61012019000142 - ASSOCIAÇÃO BRASILEIRA IJCSUD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2167.29</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2167.29</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -760,7 +752,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-10-06T13:42:48.402Z</t>
+          <t>2025-10-09T21:18:04.630Z</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -773,12 +765,12 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-09-29T15:17:10.234Z</t>
+          <t>2025-10-02T21:19:25.794Z</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
+          <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -798,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>MzM3ODI5ODo1NzAxNg==</t>
+          <t>NDcxNTkzODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -810,32 +802,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HYTE7IDHEX</t>
+          <t>HJ0GXQO2EG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MAQUINA 02</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>JOANA DARC OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Orçamento  para reforma de TFK 02 kg</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Reforma</t>
+        </is>
+      </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>979.73</t>
+          <t>2167.29</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>979.73</t>
+          <t>2167.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-10-06T18:41:42.725Z</t>
+          <t>2025-10-06T13:42:48.402Z</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -858,12 +858,12 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-09-29T18:42:56.833Z</t>
+          <t>2025-09-29T15:17:10.234Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzM3ODI5ODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -895,17 +895,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SYLVG8O3EG</t>
+          <t>HYTE7IDHEX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
+          <t>MAQUINA 02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>979.73</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>979.73</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-10-06T18:34:31.188Z</t>
+          <t>2025-10-06T18:41:42.725Z</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -943,7 +943,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2025-09-29T18:38:37.635Z</t>
+          <t>2025-09-29T18:42:56.833Z</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -980,20 +980,105 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SYLVG8O3EG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MAQUINA 01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1298.9</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1298.9</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2025-10-06T18:34:31.188Z</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-29T18:38:37.635Z</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1002,7 +1087,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1011,106 +1096,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1120,20 +1116,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
+          <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1154,7 +1150,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1166,36 +1162,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SJBLZ0HQLG</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OUTBACK MORUMBI</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1205,27 +1205,23 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:27:17.728Z</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1243,7 +1239,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1255,42 +1251,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1303,12 +1303,12 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
+          <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1328,62 +1328,54 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1396,10 +1388,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1417,79 +1413,75 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
+          <t>2025-08-28T16:05:56.490Z</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1500,58 +1492,58 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1561,28 +1553,28 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>rffccfc</t>
+          <t>jose da silva</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>HENRIQUE</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
+          <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1593,17 +1585,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1615,22 +1607,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
+          <t>teste</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Substituição de 3 compressores</t>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1639,39 +1631,43 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>2025-09-04T16:07:52.834Z</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1692,74 +1688,78 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1777,32 +1777,117 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1810,7 +1895,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1818,106 +1903,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1927,7 +1923,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1940,10 +1936,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1973,23 +1973,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R1BQOWO2EE</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GRALHA AZUL PONTA GROSSA</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
-BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+          <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1998,22 +1997,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-10-06T19:05:55.326Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2026,35 +2025,121 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
+          <t>2025-09-08T21:59:15.256Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R1BQOWO2EE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
+BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2025-10-06T19:05:55.326Z</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>2025-09-29T20:26:53.403Z</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>NDgyNTE1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
@@ -2071,7 +2156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2257,31 +2342,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDFmODQ2OWUtMmMyMC00NzEwLWE4NTEtMmFkOWFjYjRlYjQ2OjU3MDE2</t>
+          <t>NGRlMTM3N2EtNzUwNC00YmUyLThmZjItMDQxZTc1ZDNjODRiOjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>18025</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TROCADO EM GARANTIA</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NDUwZmFlOTEtODg1My00ZTcwLWIwOTgtZWM2Nzc3MzgzNjgyOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>18025</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2290,38 +2379,42 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MjhmNDNmYjAtZjgzMi00MThiLWEyNTAtZWVlODc0ZjQxYzliOjU3MDE2</t>
+          <t>NmQ1MDliODYtNGYyYy00YTNiLTk1YWEtYmM0MTZhNDBkNTY1OjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1365</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TROCADO EM GARANTIA</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1365</v>
+        <v>350</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2330,21 +2423,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MmQyOGU2OWYtM2IzOS00ZjYwLWJmYTctYmViYTY2M2UxNzdjOjU3MDE2</t>
+          <t>MDFmODQ2OWUtMmMyMC00NzEwLWE4NTEtMmFkOWFjYjRlYjQ2OjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>375</v>
+        <v>50</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
@@ -2357,11 +2450,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>NDUwZmFlOTEtODg1My00ZTcwLWIwOTgtZWM2Nzc3MzgzNjgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>375</v>
+        <v>50</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2377,14 +2470,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MzVjNDRmYjctMTI1My00NDg3LThlNmUtOWZhN2YyYWMyNjg3OjU3MDE2</t>
+          <t>MjhmNDNmYjAtZjgzMi00MThiLWEyNTAtZWVlODc0ZjQxYzliOjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1.152e+16</v>
+        <v>1365</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
@@ -2397,11 +2490,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NDM0MjA4NTAtZjAwOC00YzMyLWJlM2QtODFlMzljMjE0OTk4OjU3MDE2</t>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.152e+16</v>
+        <v>1365</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2417,14 +2510,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NDNkMGNjZmMtMjFmMS00NjQyLWI4OWYtYTk4ODg2NjkxMjcwOjU3MDE2</t>
+          <t>MmQyOGU2OWYtM2IzOS00ZjYwLWJmYTctYmViYTY2M2UxNzdjOjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>168</v>
+        <v>375</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
@@ -2437,15 +2530,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>375</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2457,14 +2550,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NDRlYzI5NjAtMTZmYi00MzM3LWEzZTEtNGJmOTg0Y2Y1MzFhOjU3MDE2</t>
+          <t>MzVjNDRmYjctMTI1My00NDg3LThlNmUtOWZhN2YyYWMyNjg3OjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>700</v>
+        <v>1.152e+16</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
@@ -2477,15 +2570,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>NDM0MjA4NTAtZjAwOC00YzMyLWJlM2QtODFlMzljMjE0OTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>350</v>
+        <v>1.152e+16</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2497,14 +2590,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N2NjNjliYTAtNTVlZi00NjNmLThkMmUtZGMzYzIyZjRhM2FiOjU3MDE2</t>
+          <t>NDNkMGNjZmMtMjFmMS00NjQyLWI4OWYtYTk4ODg2NjkxMjcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C11" t="n">
-        <v>350</v>
+        <v>168</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
@@ -2517,15 +2610,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>350</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2537,14 +2630,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OTg0ZDY5MWUtZTJiZS00NmM0LTg1OGMtNDQ1ZTMwMmY2MWE3OjU3MDE2</t>
+          <t>NDRlYzI5NjAtMTZmYi00MzM3LWEzZTEtNGJmOTg0Y2Y1MzFhOjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
@@ -2557,15 +2650,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2577,14 +2670,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OWRkMWJkNWQtMjE5Yy00OTY0LWExNzYtZTI4YzkyN2Q4ODdlOjU3MDE2</t>
+          <t>N2NjNjliYTAtNTVlZi00NjNmLThkMmUtZGMzYzIyZjRhM2FiOjU3MDE2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>350</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
@@ -2597,11 +2690,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Y2FjZGRiY2YtOTQ5NS00NDIyLWE4ODctYjk4ZGUxNjU1MzMyOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>350</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2617,14 +2710,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>YTAxNDZjNzgtMDljZi00ZGQ4LTkwOTItZmM5N2QyNzM3MGEwOjU3MDE2</t>
+          <t>OTg0ZDY5MWUtZTJiZS00NmM0LTg1OGMtNDQ1ZTMwMmY2MWE3OjU3MDE2</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>18025</v>
+        <v>85</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
@@ -2637,11 +2730,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>18025</v>
+        <v>85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2657,14 +2750,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>YTM1YmFkNmQtN2EzNS00Njk0LTliNTMtNmZiMjAwNzQ5NzFkOjU3MDE2</t>
+          <t>OWRkMWJkNWQtMjE5Yy00OTY0LWExNzYtZTI4YzkyN2Q4ODdlOjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>25625</v>
+        <v>72</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
@@ -2677,11 +2770,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MTdjYWQ5ZTAtMmQ3YS00OTM0LWIyOGEtYzMxYjY1ODZkNDIzOjU3MDE2</t>
+          <t>Y2FjZGRiY2YtOTQ5NS00NDIyLWE4ODctYjk4ZGUxNjU1MzMyOjU3MDE2</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>25625</v>
+        <v>18</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2697,14 +2790,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>YzFlYTExODctMmJkNy00N2RhLThiMTQtZTVjMTY0NWY1Y2Y5OjU3MDE2</t>
+          <t>YTAxNDZjNzgtMDljZi00ZGQ4LTkwOTItZmM5N2QyNzM3MGEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>182225</v>
+        <v>18025</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
@@ -2717,11 +2810,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>OWU3NmYwYWEtZWNhZi00YTBiLWE2NTUtNjE5NTkwNDIwZDNjOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>182225</v>
+        <v>18025</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2737,14 +2830,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>YzRiYzAxZjEtOWY2Zi00ZWQ0LWJmMjgtZmYxY2RjNjY1OTBiOjU3MDE2</t>
+          <t>YTM1YmFkNmQtN2EzNS00Njk0LTliNTMtNmZiMjAwNzQ5NzFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>9940000000000000</v>
+        <v>25625</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
@@ -2757,11 +2850,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>OWMxNWU5ZjUtOWI3Ny00ZmYyLWExMWYtM2RkYzA3ZWFjYzU5OjU3MDE2</t>
+          <t>MTdjYWQ5ZTAtMmQ3YS00OTM0LWIyOGEtYzMxYjY1ODZkNDIzOjU3MDE2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>9940000000000000</v>
+        <v>25625</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2777,14 +2870,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ZGMxMDhlMDAtNmY3Ni00OWE1LTg0MDMtZjVmNjUyZGVkNzZlOjU3MDE2</t>
+          <t>YzFlYTExODctMmJkNy00N2RhLThiMTQtZTVjMTY0NWY1Y2Y5OjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>2073</v>
+        <v>182225</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
@@ -2797,11 +2890,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>OWU3NmYwYWEtZWNhZi00YTBiLWE2NTUtNjE5NTkwNDIwZDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2073</v>
+        <v>182225</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2817,14 +2910,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ZjczNzc1Y2UtNGU2Mi00NGEzLTk5NWUtYzRlZmRjMzFhMTI2OjU3MDE2</t>
+          <t>YzRiYzAxZjEtOWY2Zi00ZWQ0LWJmMjgtZmYxY2RjNjY1OTBiOjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>36</v>
+        <v>9940000000000000</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
@@ -2837,11 +2930,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ZmQ5YTY2ZWEtZDM4NS00MWMwLWI0NWYtODI3ZjAxNzRjNzE1OjU3MDE2</t>
+          <t>OWMxNWU5ZjUtOWI3Ny00ZmYyLWExMWYtM2RkYzA3ZWFjYzU5OjU3MDE2</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>9940000000000000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2857,14 +2950,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ZmQ3OWNiYjEtZmY3Yi00MjVkLWJhODgtYjA3NjQyZWY1MzYwOjU3MDE2</t>
+          <t>ZGMxMDhlMDAtNmY3Ni00OWE1LTg0MDMtZjVmNjUyZGVkNzZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1578</v>
+        <v>2073</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
@@ -2877,11 +2970,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Y2I2NzA1MTItNDc5NS00ZWVmLWJkOTktY2JlZmJiZTNmNTFlOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1578</v>
+        <v>2073</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2897,71 +2990,71 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MTE0NDUwMGUtM2ZiMi00OWQ1LWFmY2EtMzNjNzZmNjBhMTVmOjU3MDE2</t>
+          <t>ZjczNzc1Y2UtNGU2Mi00NGEzLTk5NWUtYzRlZmRjMzFhMTI2OjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>350</v>
+        <v>36</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ZmQ5YTY2ZWEtZDM4NS00MWMwLWI0NWYtODI3ZjAxNzRjNzE1OjU3MDE2</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>350</v>
+        <v>9</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NWM5YzAxYzktMTIwMS00ZjhkLWJjOGMtN2U3NDlmOTlmMzRkOjU3MDE2</t>
+          <t>ZmQ3OWNiYjEtZmY3Yi00MjVkLWJhODgtYjA3NjQyZWY1MzYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>85</v>
+        <v>1578</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>Y2I2NzA1MTItNDc5NS00ZWVmLWJkOTktY2JlZmJiZTNmNTFlOjU3MDE2</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>85</v>
+        <v>1578</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2970,21 +3063,21 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NjRmMDVhODItNmU2Mi00ZDRhLTk5NmItNzM2ODI0YjE2MjRmOjU3MDE2</t>
+          <t>MTE0NDUwMGUtM2ZiMi00OWQ1LWFmY2EtMzNjNzZmNjBhMTVmOjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1365</v>
+        <v>350</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
@@ -2997,15 +3090,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1365</v>
+        <v>350</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3017,14 +3110,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OGUzMjVkZDYtOTA3Yi00MjFjLWFjYzgtOWVlMGI3MjJkNjIzOjU3MDE2</t>
+          <t>NWM5YzAxYzktMTIwMS00ZjhkLWJjOGMtN2U3NDlmOTlmMzRkOjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
@@ -3037,11 +3130,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3057,14 +3150,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Yjk2YzIwMDktMzVkMy00ZGRjLWIwOTYtOTJjOWFlMjZiM2FhOjU3MDE2</t>
+          <t>NjRmMDVhODItNmU2Mi00ZDRhLTk5NmItNzM2ODI0YjE2MjRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>375</v>
+        <v>1365</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
@@ -3077,11 +3170,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>375</v>
+        <v>1365</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3097,14 +3190,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZTA0MDdkOTgtNjJjMi00ZTgyLWFmMzEtYzg4MzdkYzhjYmMzOjU3MDE2</t>
+          <t>OGUzMjVkZDYtOTA3Yi00MjFjLWFjYzgtOWVlMGI3MjJkNjIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
@@ -3117,11 +3210,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3137,31 +3230,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MDhmZjQ1YWQtNTY2Yi00YTlkLWIyMWEtZDI5Y2RkYThlODAwOjU3MDE2</t>
+          <t>Yjk2YzIwMDktMzVkMy00ZGRjLWIwOTYtOTJjOWFlMjZiM2FhOjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>375</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>375</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3170,38 +3263,38 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>N2EyYTQzZjktNzgxZi00Mzk2LWEyNzMtODM0NmViMTE4MWE2OjU3MDE2</t>
+          <t>ZTA0MDdkOTgtNjJjMi00ZTgyLWFmMzEtYzg4MzdkYzhjYmMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3210,21 +3303,21 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OWIyYjYwOTktYTg5MC00ZjRhLWEzOGMtNDI3YTE2MTA1NTI1OjU3MDE2</t>
+          <t>MDhmZjQ1YWQtNTY2Yi00YTlkLWIyMWEtZDI5Y2RkYThlODAwOjU3MDE2</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>700</v>
+        <v>9</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
@@ -3237,15 +3330,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>350</v>
+        <v>9</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3257,14 +3350,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>YTJjM2ExNTAtOWExYi00Mzk1LWE1N2MtM2JkYTU3MDBiMzhlOjU3MDE2</t>
+          <t>N2EyYTQzZjktNzgxZi00Mzk2LWEyNzMtODM0NmViMTE4MWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>375</v>
+        <v>85</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
@@ -3277,11 +3370,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>375</v>
+        <v>85</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3297,14 +3390,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>YTYxMjU3ODEtZjY4ZS00MDQyLTg5YmItYzg1YTA3YTdmZmY5OjU3MDE2</t>
+          <t>OWIyYjYwOTktYTg5MC00ZjRhLWEzOGMtNDI3YTE2MTA1NTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
@@ -3317,7 +3410,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3325,7 +3418,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3337,14 +3430,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>YTg1ZmQyOGMtNDZkOC00YTgwLWJhODUtOGI5OTA5ZDliZjg1OjU3MDE2</t>
+          <t>YTJjM2ExNTAtOWExYi00Mzk1LWE1N2MtM2JkYTU3MDBiMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>8399999999999999</v>
+        <v>375</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
@@ -3357,11 +3450,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>8399999999999999</v>
+        <v>375</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3377,14 +3470,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>YTlhNDQ1NWItMWI4OS00ZGM0LThiOTgtMzZlOTcxNTE0NzcyOjU3MDE2</t>
+          <t>YTYxMjU3ODEtZjY4ZS00MDQyLTg5YmItYzg1YTA3YTdmZmY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
@@ -3397,11 +3490,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3417,14 +3510,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ZTZmYzJiNjEtYzBjNS00NjM2LWI0YmEtNzZlMGE1NWI2ODIwOjU3MDE2</t>
+          <t>YTg1ZmQyOGMtNDZkOC00YTgwLWJhODUtOGI5OTA5ZDliZjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>2502</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
@@ -3437,11 +3530,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2502</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3457,14 +3550,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ZWQ1NDY3MTUtZjAxMC00OTM2LTljZDctNzBmMjRlZjVhYTQwOjU3MDE2</t>
+          <t>YTlhNDQ1NWItMWI4OS00ZGM0LThiOTgtMzZlOTcxNTE0NzcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>6325</v>
+        <v>2073</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
@@ -3477,11 +3570,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6325</v>
+        <v>2073</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3497,16 +3590,96 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>ZTZmYzJiNjEtYzBjNS00NjM2LWI0YmEtNzZlMGE1NWI2ODIwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2502</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>2502</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ZWQ1NDY3MTUtZjAxMC00OTM2LTljZDctNzBmMjRlZjVhYTQwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6325</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>6325</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="n">
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
         <v>1700</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -3514,126 +3687,126 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E38" t="n">
         <v>2</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="H38" t="n">
         <v>1700</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>47370</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="n">
-        <v>3</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="n">
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
         <v>494677</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -3651,124 +3824,44 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E41" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="H41" t="n">
         <v>494677</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="n">
-        <v>350</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>6</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>350</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="n">
-        <v>6</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>2073</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>7375</v>
+        <v>350</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
@@ -3781,15 +3874,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>7375</v>
+        <v>350</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3801,14 +3894,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>8399999999999999</v>
+        <v>2073</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
@@ -3821,11 +3914,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>8399999999999999</v>
+        <v>2073</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3841,14 +3934,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>375</v>
+        <v>7375</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
@@ -3861,11 +3954,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>375</v>
+        <v>7375</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3881,150 +3974,142 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>680</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>8399999999999999</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>680</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>855</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>855</v>
+        <v>375</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>10000</v>
+        <v>680</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>10000</v>
+        <v>680</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>680</v>
+        <v>855</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -4032,16 +4117,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>680</v>
+        <v>855</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4050,82 +4135,86 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>855</v>
+        <v>10000</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>855</v>
+        <v>10000</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>47370</v>
+        <v>680</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4134,67 +4223,151 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>855</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>855</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" t="n">
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
         <v>1700</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -4202,46 +4375,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E54" t="n">
         <v>2</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H52" t="n">
+      <c r="H54" t="n">
         <v>1700</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="n">
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
         <v>494677</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -4259,170 +4432,90 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E55" t="n">
         <v>3</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="H55" t="n">
         <v>494677</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="n">
-        <v>3</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="n">
-        <v>43</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>CORREIO VIA SEDEX 43,00</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>13</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>43</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>3325</v>
+        <v>1050</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3325</v>
+        <v>1050</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>717</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CORREIO VIA SEDEX 43,00</t>
+        </is>
+      </c>
       <c r="E57" t="n">
         <v>13</v>
       </c>
@@ -4433,11 +4526,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>717</v>
+        <v>43</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4453,14 +4546,14 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>7375</v>
+        <v>3325</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
@@ -4473,11 +4566,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>7375</v>
+        <v>3325</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4493,14 +4586,14 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
+          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>117</v>
+        <v>717</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
@@ -4513,11 +4606,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>117</v>
+        <v>717</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4533,14 +4626,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
+          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>4.2e+16</v>
+        <v>7375</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
@@ -4553,11 +4646,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>4.2e+16</v>
+        <v>7375</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4573,14 +4666,14 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
+          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>6449999999999999</v>
+        <v>117</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
@@ -4593,11 +4686,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6449999999999999</v>
+        <v>117</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4613,14 +4706,14 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>48</v>
+        <v>4.2e+16</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
@@ -4633,11 +4726,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>48</v>
+        <v>4.2e+16</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4653,14 +4746,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>475</v>
+        <v>6449999999999999</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
@@ -4673,11 +4766,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>475</v>
+        <v>6449999999999999</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4693,14 +4786,14 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>1725</v>
+        <v>48</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
@@ -4713,11 +4806,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1725</v>
+        <v>48</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -4733,14 +4826,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>6000000000000001</v>
+        <v>475</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
@@ -4753,11 +4846,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>6000000000000001</v>
+        <v>475</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -4773,14 +4866,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>8399999999999999</v>
+        <v>1725</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
@@ -4793,18 +4886,98 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>13</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>13</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
-      <c r="H66" t="n">
+      <c r="H68" t="n">
         <v>8399999999999999</v>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -849,13 +849,21 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joana D’Arc Oliveira </t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>2025-09-29T15:17:10.234Z</t>
@@ -888,7 +896,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -933,7 +933,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2066,47 +2066,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R1BQOWO2EE</t>
+          <t>H16WCCZPEG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GRALHA AZUL PONTA GROSSA</t>
+          <t>FRANCESCO DE TOMMASO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
-BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-10-06T19:05:55.326Z</t>
+          <t>2025-10-14T18:12:15.015Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2119,35 +2122,125 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
+          <t>2025-10-07T18:22:28.553Z</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R1BQOWO2EE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
+BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2025-10-06T19:05:55.326Z</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>2025-09-29T20:26:53.403Z</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>NDgyNTE1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2164,7 +2257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4510,35 +4603,31 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>43</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>CORREIO VIA SEDEX 43,00</t>
-        </is>
-      </c>
+        <v>1086</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>43</v>
+        <v>1086</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4547,38 +4636,38 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>3325</v>
+        <v>350</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>3325</v>
+        <v>350</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4587,38 +4676,38 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>717</v>
+        <v>4050000000000001</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>717</v>
+        <v>4050000000000001</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4627,38 +4716,38 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>7375</v>
+        <v>3795</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>7375</v>
+        <v>3795</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4667,78 +4756,78 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
+          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>117</v>
+        <v>350</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>117</v>
+        <v>350</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
+          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>4.2e+16</v>
+        <v>18025</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.2e+16</v>
+        <v>18025</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4747,38 +4836,38 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
+          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>6449999999999999</v>
+        <v>1.68e+16</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>6449999999999999</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4787,23 +4876,27 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>48</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CORREIO VIA SEDEX 43,00</t>
+        </is>
+      </c>
       <c r="E64" t="n">
         <v>13</v>
       </c>
@@ -4814,11 +4907,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -4834,14 +4927,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>475</v>
+        <v>3325</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
@@ -4854,11 +4947,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>475</v>
+        <v>3325</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -4874,14 +4967,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>1725</v>
+        <v>717</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
@@ -4894,11 +4987,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1725</v>
+        <v>717</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -4914,14 +5007,14 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>6000000000000001</v>
+        <v>7375</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
@@ -4934,11 +5027,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>6000000000000001</v>
+        <v>7375</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4954,14 +5047,14 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>8399999999999999</v>
+        <v>117</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
@@ -4974,18 +5067,298 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>117</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>4.2e+16</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>13</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>4.2e+16</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="n">
+        <v>6449999999999999</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>13</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>6449999999999999</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>48</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>13</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>48</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>475</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>13</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>475</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1725</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>13</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>13</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>13</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
-      <c r="H68" t="n">
+      <c r="H75" t="n">
         <v>8399999999999999</v>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1073,20 +1073,105 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BJFPMUNTXG</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MIX SOLUCOES AMBIENTAIS LTDA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4984</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4984</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2025-10-15T21:09:42.233Z</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-08T21:12:33.362Z</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>NDgzNDc2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1095,7 +1180,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1104,106 +1189,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1213,20 +1209,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
+          <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1247,7 +1243,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1259,36 +1255,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SJBLZ0HQLG</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OUTBACK MORUMBI</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1298,27 +1298,23 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:27:17.728Z</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1336,7 +1332,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1348,32 +1344,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1396,12 +1396,12 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
+          <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1433,40 +1433,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1476,7 +1468,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1489,10 +1481,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1510,7 +1506,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1522,67 +1518,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
+          <t>2025-08-28T16:05:56.490Z</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1593,58 +1585,58 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1654,28 +1646,28 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>rffccfc</t>
+          <t>jose da silva</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>HENRIQUE</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
+          <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1686,17 +1678,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1708,22 +1700,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
+          <t>teste</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Substituição de 3 compressores</t>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1732,39 +1724,43 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>2025-09-04T16:07:52.834Z</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1785,74 +1781,78 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1870,32 +1870,117 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1903,7 +1988,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1911,106 +1996,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2020,7 +2016,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2033,10 +2029,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2066,50 +2066,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H16WCCZPEG</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-10-14T18:12:15.015Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2122,14 +2118,10 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-10-07T18:22:28.553Z</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-09-08T21:59:15.256Z</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2147,59 +2139,62 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R1BQOWO2EE</t>
+          <t>H16WCCZPEG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GRALHA AZUL PONTA GROSSA</t>
+          <t>FRANCESCO DE TOMMASO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
-BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-10-06T19:05:55.326Z</t>
+          <t>2025-10-14T18:12:15.015Z</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2212,35 +2207,125 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
+          <t>2025-10-07T18:22:28.553Z</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>R1BQOWO2EE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
+BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2025-10-06T19:05:55.326Z</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>2025-09-29T20:26:53.403Z</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>NDgyNTE1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2257,7 +2342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,16 +3856,140 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>NjA1ZWIxZDMtNWMxMC00NGE2LWEzZjEtYTZkZjM1MWVhNjQwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1793</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NjdjMzI5NDAtMmU1Mi00MjQ1LTgxNGQtNjUyNWI3ZTQyNDU4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1793</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OTFkMjc2ZDEtOTkxOC00OGZlLWEyMWYtZGEwNDg3MDFiNzkxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>350</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>350</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>YTlhMGVhYzMtYjJhZS00OWUwLTg5YWQtNjdjYzIyMWUyZDZmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2841</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>MGQ3YTYzZmEtOGQyZS00YWNiLTljMWYtNTNiM2JkMzRmOTYwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>2841</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="n">
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
         <v>1700</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -3788,126 +3997,126 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E41" t="n">
         <v>2</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="H41" t="n">
         <v>1700</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="n">
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
         <v>47370</v>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="n">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
         <v>2</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="H42" t="n">
         <v>47370</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="n">
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
         <v>1050</v>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="H43" t="n">
         <v>1050</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="n">
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
         <v>494677</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -3925,164 +4134,44 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E44" t="n">
         <v>3</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="H44" t="n">
         <v>494677</v>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="n">
-        <v>350</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="n">
-        <v>6</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>350</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="n">
-        <v>6</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>2073</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="n">
-        <v>7375</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="n">
-        <v>6</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>7375</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>8399999999999999</v>
+        <v>350</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
@@ -4095,15 +4184,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8399999999999999</v>
+        <v>350</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4115,14 +4204,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>375</v>
+        <v>2073</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
@@ -4135,11 +4224,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>375</v>
+        <v>2073</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4155,123 +4244,111 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>680</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>7375</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>680</v>
+        <v>7375</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>855</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>8399999999999999</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>855</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
-        </is>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>10000</v>
+        <v>375</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4280,14 +4357,14 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -4306,7 +4383,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4324,14 +4401,14 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -4350,7 +4427,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4368,107 +4445,239 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+        </is>
+      </c>
       <c r="E52" t="n">
         <v>2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>47370</v>
+        <v>10000</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>680</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>680</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>855</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>855</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="n">
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
         <v>1700</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -4476,46 +4685,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E57" t="n">
         <v>2</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="H57" t="n">
         <v>1700</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="n">
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
         <v>494677</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -4533,204 +4742,84 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="E58" t="n">
         <v>3</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="H58" t="n">
         <v>494677</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="n">
-        <v>3</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="n">
-        <v>1086</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="n">
-        <v>8</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>1086</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="n">
-        <v>350</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="n">
-        <v>8</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>350</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>4050000000000001</v>
+        <v>1050</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>4050000000000001</v>
+        <v>1050</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
+          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>3795</v>
+        <v>1086</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
@@ -4743,11 +4832,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>3795</v>
+        <v>1086</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4763,7 +4852,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
+          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -4783,7 +4872,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -4791,7 +4880,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4803,14 +4892,14 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
+          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>18025</v>
+        <v>4050000000000001</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
@@ -4823,11 +4912,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>18025</v>
+        <v>4050000000000001</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4843,14 +4932,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
+          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>1.68e+16</v>
+        <v>3795</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
@@ -4863,11 +4952,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2.1e+16</v>
+        <v>3795</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4883,75 +4972,71 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>43</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>CORREIO VIA SEDEX 43,00</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>43</v>
+        <v>350</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>3325</v>
+        <v>18025</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>3325</v>
+        <v>18025</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -4960,38 +5045,38 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C66" t="n">
-        <v>717</v>
+        <v>1.68e+16</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>717</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5000,23 +5085,27 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>7375</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CORREIO VIA SEDEX 43,00</t>
+        </is>
+      </c>
       <c r="E67" t="n">
         <v>13</v>
       </c>
@@ -5027,11 +5116,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>7375</v>
+        <v>43</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5047,14 +5136,14 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
+          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>117</v>
+        <v>3325</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
@@ -5067,11 +5156,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>117</v>
+        <v>3325</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5087,14 +5176,14 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
+          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>4.2e+16</v>
+        <v>717</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
@@ -5107,11 +5196,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>4.2e+16</v>
+        <v>717</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5127,14 +5216,14 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
+          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>6449999999999999</v>
+        <v>7375</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
@@ -5147,11 +5236,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>6449999999999999</v>
+        <v>7375</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5167,14 +5256,14 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
@@ -5187,11 +5276,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5207,14 +5296,14 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>475</v>
+        <v>4.2e+16</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
@@ -5227,11 +5316,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>475</v>
+        <v>4.2e+16</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5247,14 +5336,14 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>1725</v>
+        <v>6449999999999999</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
@@ -5267,11 +5356,11 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1725</v>
+        <v>6449999999999999</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5287,14 +5376,14 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>6000000000000001</v>
+        <v>48</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
@@ -5307,11 +5396,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>6000000000000001</v>
+        <v>48</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5327,14 +5416,14 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>8399999999999999</v>
+        <v>475</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
@@ -5347,18 +5436,138 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
+          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>475</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1725</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>13</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>13</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="n">
+        <v>13</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
           <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
-      <c r="H75" t="n">
+      <c r="H78" t="n">
         <v>8399999999999999</v>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -747,7 +747,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,20 +1158,113 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BYCZRKIPEL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>62730134620 - FRANCISCO DE LUCCA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GARANTIA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>garantia</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>530.25</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>530.25</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2025-10-17T12:48:39.389Z</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-10T13:07:18.487Z</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>NDgyMzMyODo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1180,7 +1273,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1189,106 +1282,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1298,20 +1302,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
+          <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1332,7 +1336,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1344,36 +1348,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SJBLZ0HQLG</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OUTBACK MORUMBI</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1383,27 +1391,23 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:27:17.728Z</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1421,7 +1425,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1433,32 +1437,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1468,7 +1476,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1481,12 +1489,12 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
+          <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1506,7 +1514,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1518,40 +1526,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1574,10 +1574,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1595,7 +1599,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1607,67 +1611,63 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
+          <t>2025-08-28T16:05:56.490Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1678,58 +1678,58 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1739,28 +1739,28 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>rffccfc</t>
+          <t>jose da silva</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>HENRIQUE</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
+          <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1771,17 +1771,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1793,22 +1793,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
+          <t>teste</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Substituição de 3 compressores</t>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1817,39 +1817,43 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>2025-09-04T16:07:52.834Z</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1870,74 +1874,78 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1955,32 +1963,117 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1988,7 +2081,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1996,106 +2089,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2105,7 +2109,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2118,10 +2122,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2139,7 +2147,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2151,50 +2159,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H16WCCZPEG</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-10-14T18:12:15.015Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2207,14 +2211,10 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-10-07T18:22:28.553Z</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-09-08T21:59:15.256Z</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2232,59 +2232,62 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R1BQOWO2EE</t>
+          <t>H16WCCZPEG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GRALHA AZUL PONTA GROSSA</t>
+          <t>FRANCESCO DE TOMMASO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
-BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-10-06T19:05:55.326Z</t>
+          <t>2025-10-14T18:12:15.015Z</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2297,35 +2300,125 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
+          <t>2025-10-07T18:22:28.553Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>R1BQOWO2EE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
+BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2025-10-06T19:05:55.326Z</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>2025-09-29T20:26:53.403Z</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>NDgyNTE1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2342,7 +2435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3980,16 +4073,96 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>MjA0Mzk0M2ItOWI2Ni00Y2NkLWJlNjgtOTUwNjdmMjVkM2Y3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>350</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>350</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NDUwYmZhOGUtMTA3Ni00MmY2LWFhMjgtNWY5YzNmNzMzMWQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>18025</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>18025</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="n">
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
         <v>1700</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -3997,126 +4170,126 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E43" t="n">
         <v>2</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="H43" t="n">
         <v>1700</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>47370</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="n">
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
         <v>494677</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -4134,124 +4307,44 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E46" t="n">
         <v>3</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="H46" t="n">
         <v>494677</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="n">
-        <v>350</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="n">
-        <v>6</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>350</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="n">
-        <v>6</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>2073</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>7375</v>
+        <v>350</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
@@ -4264,15 +4357,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>7375</v>
+        <v>350</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4284,14 +4377,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>8399999999999999</v>
+        <v>2073</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
@@ -4304,11 +4397,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8399999999999999</v>
+        <v>2073</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4324,14 +4417,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>375</v>
+        <v>7375</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
@@ -4344,11 +4437,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>375</v>
+        <v>7375</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4364,150 +4457,142 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>680</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>8399999999999999</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>680</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>855</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>855</v>
+        <v>375</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>10000</v>
+        <v>680</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>10000</v>
+        <v>680</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>680</v>
+        <v>855</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -4515,16 +4600,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>680</v>
+        <v>855</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4533,82 +4618,86 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>855</v>
+        <v>10000</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>855</v>
+        <v>10000</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>47370</v>
+        <v>680</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4617,67 +4706,151 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>855</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>855</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="n">
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
         <v>1700</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -4685,46 +4858,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="E59" t="n">
         <v>2</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="H59" t="n">
         <v>1700</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="n">
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
         <v>494677</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -4742,164 +4915,84 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E58" t="n">
+      <c r="E60" t="n">
         <v>3</v>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H58" t="n">
+      <c r="H60" t="n">
         <v>494677</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="n">
-        <v>1086</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="n">
-        <v>8</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>1086</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>350</v>
+        <v>1050</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>350</v>
+        <v>1050</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
+          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>4050000000000001</v>
+        <v>1086</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
@@ -4912,11 +5005,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4050000000000001</v>
+        <v>1086</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4932,14 +5025,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
+          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>3795</v>
+        <v>350</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
@@ -4952,11 +5045,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>3795</v>
+        <v>350</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4972,14 +5065,14 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
+          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>350</v>
+        <v>4050000000000001</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
@@ -4992,15 +5085,15 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>350</v>
+        <v>4050000000000001</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5012,14 +5105,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
+          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>18025</v>
+        <v>3795</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
@@ -5032,11 +5125,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>18025</v>
+        <v>3795</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5052,14 +5145,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
+          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>1.68e+16</v>
+        <v>350</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
@@ -5072,15 +5165,15 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2.1e+16</v>
+        <v>350</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5092,35 +5185,31 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>43</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>CORREIO VIA SEDEX 43,00</t>
-        </is>
-      </c>
+        <v>18025</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>43</v>
+        <v>18025</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5129,38 +5218,38 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C68" t="n">
-        <v>3325</v>
+        <v>1.68e+16</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>3325</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5169,23 +5258,27 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>717</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CORREIO VIA SEDEX 43,00</t>
+        </is>
+      </c>
       <c r="E69" t="n">
         <v>13</v>
       </c>
@@ -5196,11 +5289,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>717</v>
+        <v>43</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5216,14 +5309,14 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>7375</v>
+        <v>3325</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
@@ -5236,11 +5329,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>7375</v>
+        <v>3325</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5256,14 +5349,14 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
+          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>117</v>
+        <v>717</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
@@ -5276,11 +5369,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>117</v>
+        <v>717</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5296,14 +5389,14 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
+          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>4.2e+16</v>
+        <v>7375</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
@@ -5316,11 +5409,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>4.2e+16</v>
+        <v>7375</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5336,14 +5429,14 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
+          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>6449999999999999</v>
+        <v>117</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
@@ -5356,11 +5449,11 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>6449999999999999</v>
+        <v>117</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5376,14 +5469,14 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>48</v>
+        <v>4.2e+16</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
@@ -5396,11 +5489,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>48</v>
+        <v>4.2e+16</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5416,14 +5509,14 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>475</v>
+        <v>6449999999999999</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
@@ -5436,11 +5529,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>475</v>
+        <v>6449999999999999</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5456,14 +5549,14 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>1725</v>
+        <v>48</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
@@ -5476,11 +5569,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1725</v>
+        <v>48</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -5496,14 +5589,14 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>6000000000000001</v>
+        <v>475</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
@@ -5516,11 +5609,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>6000000000000001</v>
+        <v>475</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -5536,14 +5629,14 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>8399999999999999</v>
+        <v>1725</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
@@ -5556,18 +5649,98 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="n">
+        <v>13</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="n">
+        <v>13</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
           <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
-      <c r="H78" t="n">
+      <c r="H80" t="n">
         <v>8399999999999999</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2244,40 +2244,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H16WCCZPEG</t>
+          <t>SK1FN_56XX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
+          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2287,7 +2279,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-10-14T18:12:15.015Z</t>
+          <t>2025-10-20T12:26:24.223Z</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2300,12 +2292,12 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-10-07T18:22:28.553Z</t>
+          <t>2025-10-13T12:45:43.188Z</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2325,7 +2317,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>MzQ2NDM2Nzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2337,47 +2329,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R1BQOWO2EE</t>
+          <t>H16WCCZPEG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GRALHA AZUL PONTA GROSSA</t>
+          <t>FRANCESCO DE TOMMASO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
-BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-10-06T19:05:55.326Z</t>
+          <t>2025-10-14T18:12:15.015Z</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2390,35 +2385,125 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
+          <t>2025-10-07T18:22:28.553Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>R1BQOWO2EE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
+BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2025-10-06T19:05:55.326Z</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>2025-09-29T20:26:53.403Z</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>NDgyNTE1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2435,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4985,31 +5070,31 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
+          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>1086</v>
+        <v>99</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1086</v>
+        <v>33</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5018,38 +5103,38 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
+          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>350</v>
+        <v>38656</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5058,38 +5143,38 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
+          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>4050000000000001</v>
+        <v>350</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>4050000000000001</v>
+        <v>350</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5098,38 +5183,38 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
+          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>3795</v>
+        <v>85</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>3795</v>
+        <v>85</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5138,14 +5223,14 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
+          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -5156,11 +5241,11 @@
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5178,21 +5263,21 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
+          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>18025</v>
+        <v>1086</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
@@ -5205,11 +5290,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>18025</v>
+        <v>1086</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5225,14 +5310,14 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
+          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>1.68e+16</v>
+        <v>350</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
@@ -5245,11 +5330,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>2.1e+16</v>
+        <v>350</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5265,35 +5350,31 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>43</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>CORREIO VIA SEDEX 43,00</t>
-        </is>
-      </c>
+        <v>4050000000000001</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>43</v>
+        <v>4050000000000001</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5302,38 +5383,38 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>3325</v>
+        <v>3795</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3325</v>
+        <v>3795</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5342,78 +5423,78 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>717</v>
+        <v>350</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>717</v>
+        <v>350</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>7375</v>
+        <v>18025</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>7375</v>
+        <v>18025</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5422,38 +5503,38 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
+          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C73" t="n">
-        <v>117</v>
+        <v>1.68e+16</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>117</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5462,23 +5543,27 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
+          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>4.2e+16</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CORREIO VIA SEDEX 43,00</t>
+        </is>
+      </c>
       <c r="E74" t="n">
         <v>13</v>
       </c>
@@ -5489,11 +5574,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>4.2e+16</v>
+        <v>43</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5509,14 +5594,14 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
+          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>6449999999999999</v>
+        <v>3325</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
@@ -5529,11 +5614,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>6449999999999999</v>
+        <v>3325</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5549,14 +5634,14 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>48</v>
+        <v>717</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
@@ -5569,11 +5654,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>48</v>
+        <v>717</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -5589,14 +5674,14 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>475</v>
+        <v>7375</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
@@ -5609,11 +5694,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>475</v>
+        <v>7375</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -5629,14 +5714,14 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>1725</v>
+        <v>117</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
@@ -5649,11 +5734,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1725</v>
+        <v>117</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -5669,14 +5754,14 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>6000000000000001</v>
+        <v>4.2e+16</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
@@ -5689,11 +5774,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>6000000000000001</v>
+        <v>4.2e+16</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -5709,14 +5794,14 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>8399999999999999</v>
+        <v>6449999999999999</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
@@ -5729,18 +5814,218 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>6449999999999999</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>48</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="n">
+        <v>13</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>48</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="n">
+        <v>475</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="n">
+        <v>13</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>475</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1725</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="n">
+        <v>13</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="n">
+        <v>13</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="n">
+        <v>13</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
           <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
-      <c r="H80" t="n">
+      <c r="H85" t="n">
         <v>8399999999999999</v>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1886,63 +1886,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>BKMVCD56XX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Substituição de 3 compressores</t>
-        </is>
-      </c>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
+          <t>2025-10-20T12:54:09.917Z</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-10-13T13:10:02.576Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1963,74 +1955,78 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2048,32 +2044,117 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2081,7 +2162,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2089,106 +2170,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2198,7 +2190,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2211,10 +2203,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2232,7 +2228,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2244,42 +2240,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SK1FN_56XX</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-10-20T12:26:24.223Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2292,14 +2292,10 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-10-13T12:45:43.188Z</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-09-08T21:59:15.256Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2317,52 +2313,44 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>MzQ2NDM2Nzo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H16WCCZPEG</t>
+          <t>SK1FN_56XX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
+          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2372,7 +2360,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-10-14T18:12:15.015Z</t>
+          <t>2025-10-20T12:26:24.223Z</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2385,12 +2373,12 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-10-07T18:22:28.553Z</t>
+          <t>2025-10-13T12:45:43.188Z</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2410,7 +2398,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>MzQ2NDM2Nzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2422,47 +2410,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R1BQOWO2EE</t>
+          <t>H16WCCZPEG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GRALHA AZUL PONTA GROSSA</t>
+          <t>FRANCESCO DE TOMMASO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
-BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-10-06T19:05:55.326Z</t>
+          <t>2025-10-14T18:12:15.015Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2475,35 +2466,125 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
+          <t>2025-10-07T18:22:28.553Z</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>R1BQOWO2EE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
+BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2025-10-06T19:05:55.326Z</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>2025-09-29T20:26:53.403Z</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>NDgyNTE1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2520,7 +2601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4842,75 +4923,71 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>47370</v>
+        <v>96</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>47370</v>
+        <v>48</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
-        </is>
-      </c>
+        <v>6000000000000001</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4919,23 +4996,227 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="n">
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
         <v>1700</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -4943,46 +5224,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="E64" t="n">
         <v>2</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H59" t="n">
+      <c r="H64" t="n">
         <v>1700</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="n">
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
         <v>494677</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -5000,261 +5281,61 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="E65" t="n">
         <v>3</v>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H60" t="n">
+      <c r="H65" t="n">
         <v>494677</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="n">
-        <v>3</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3</v>
-      </c>
-      <c r="C62" t="n">
-        <v>99</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="n">
-        <v>6</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>33</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" t="n">
-        <v>38656</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="n">
-        <v>6</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" t="n">
-        <v>350</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="n">
-        <v>6</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>350</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" t="n">
-        <v>85</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="n">
-        <v>6</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>85</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>350</v>
+        <v>1050</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>350</v>
+        <v>1050</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5263,38 +5344,38 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
+          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67" t="n">
-        <v>1086</v>
+        <v>99</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1086</v>
+        <v>33</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5303,38 +5384,38 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
+          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>350</v>
+        <v>38656</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5343,38 +5424,38 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
+          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>4050000000000001</v>
+        <v>350</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>4050000000000001</v>
+        <v>350</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5383,38 +5464,38 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
+          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>3795</v>
+        <v>85</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3795</v>
+        <v>85</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5423,14 +5504,14 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
+          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -5441,11 +5522,11 @@
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5463,21 +5544,21 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
+          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>18025</v>
+        <v>1086</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
@@ -5490,11 +5571,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>18025</v>
+        <v>1086</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5510,14 +5591,14 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
+          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>1.68e+16</v>
+        <v>350</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
@@ -5530,11 +5611,11 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>2.1e+16</v>
+        <v>350</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5550,35 +5631,31 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>43</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>CORREIO VIA SEDEX 43,00</t>
-        </is>
-      </c>
+        <v>4050000000000001</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>43</v>
+        <v>4050000000000001</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5587,38 +5664,38 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>3325</v>
+        <v>3795</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>3325</v>
+        <v>3795</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5627,78 +5704,78 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>717</v>
+        <v>350</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>717</v>
+        <v>350</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>7375</v>
+        <v>18025</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>7375</v>
+        <v>18025</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -5707,38 +5784,38 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
+          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C78" t="n">
-        <v>117</v>
+        <v>1.68e+16</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>117</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -5747,23 +5824,27 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
+          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>4.2e+16</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CORREIO VIA SEDEX 43,00</t>
+        </is>
+      </c>
       <c r="E79" t="n">
         <v>13</v>
       </c>
@@ -5774,11 +5855,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>4.2e+16</v>
+        <v>43</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -5794,14 +5875,14 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
+          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>6449999999999999</v>
+        <v>3325</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
@@ -5814,11 +5895,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>6449999999999999</v>
+        <v>3325</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -5834,14 +5915,14 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>48</v>
+        <v>717</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
@@ -5854,11 +5935,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>48</v>
+        <v>717</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5874,14 +5955,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>475</v>
+        <v>7375</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
@@ -5894,11 +5975,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>475</v>
+        <v>7375</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5914,14 +5995,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>1725</v>
+        <v>117</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
@@ -5934,11 +6015,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1725</v>
+        <v>117</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5954,14 +6035,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>6000000000000001</v>
+        <v>4.2e+16</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
@@ -5974,11 +6055,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>6000000000000001</v>
+        <v>4.2e+16</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5994,14 +6075,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>8399999999999999</v>
+        <v>6449999999999999</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
@@ -6014,18 +6095,218 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>6449999999999999</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="n">
+        <v>48</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="n">
+        <v>13</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>48</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>475</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>13</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>475</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1725</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="n">
+        <v>13</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="n">
+        <v>13</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>13</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
           <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
-      <c r="H85" t="n">
+      <c r="H90" t="n">
         <v>8399999999999999</v>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
         <is>
           <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -2448,7 +2448,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -1196,7 +1196,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -1916,7 +1916,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2325,62 +2325,62 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SK1FN_56XX</t>
+          <t>SYSJ0HARXL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>2123.15</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>2123.15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-10-20T12:26:24.223Z</t>
+          <t>2025-11-04T13:33:37.491Z</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-10-13T12:45:43.188Z</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-10-28T14:06:21.222Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2398,52 +2398,44 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>MzQ2NDM2Nzo1NzAxNg==</t>
+          <t>NDgyMTM3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H16WCCZPEG</t>
+          <t>SK1FN_56XX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
+          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2453,7 +2445,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-10-14T18:12:15.015Z</t>
+          <t>2025-10-20T12:26:24.223Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2466,12 +2458,12 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-10-07T18:22:28.553Z</t>
+          <t>2025-10-13T12:45:43.188Z</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2491,7 +2483,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>MzQ2NDM2Nzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2503,37 +2495,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R1BQOWO2EE</t>
+          <t>H16WCCZPEG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GRALHA AZUL PONTA GROSSA</t>
+          <t>FRANCESCO DE TOMMASO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
-BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2543,7 +2538,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-10-06T19:05:55.326Z</t>
+          <t>2025-10-14T18:12:15.015Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2556,35 +2551,125 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
+          <t>2025-10-07T18:22:28.553Z</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>R1BQOWO2EE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
+BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2025-10-06T19:05:55.326Z</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>2025-09-29T20:26:53.403Z</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>NDgyNTE1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2601,7 +2686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5351,31 +5436,31 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
+          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>99</v>
+        <v>3.2215e+16</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
+          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>33</v>
+        <v>3.2215e+16</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5384,78 +5469,86 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
+          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>38656</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
+        <v>823</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>310Km</t>
+        </is>
+      </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
+          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>350</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Enviado por Sedex10 de SP para DF</t>
+        </is>
+      </c>
       <c r="E69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>350</v>
+        <v>43</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5464,61 +5557,65 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
+          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>85</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
+        <v>908</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
+          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>350</v>
+        <v>99</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
@@ -5531,15 +5628,15 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>350</v>
+        <v>33</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5551,31 +5648,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
+          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>1086</v>
+        <v>38656</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1086</v>
+        <v>0</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5584,14 +5681,14 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
+          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -5602,11 +5699,11 @@
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5624,38 +5721,38 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
+          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>4050000000000001</v>
+        <v>85</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>4050000000000001</v>
+        <v>85</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5664,61 +5761,61 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
+          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>3795</v>
+        <v>350</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>3795</v>
+        <v>350</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
+          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>350</v>
+        <v>1086</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
@@ -5731,15 +5828,15 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>350</v>
+        <v>1086</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5751,14 +5848,14 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
+          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
@@ -5771,11 +5868,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -5791,14 +5888,14 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
+          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>1.68e+16</v>
+        <v>4050000000000001</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
@@ -5811,11 +5908,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2.1e+16</v>
+        <v>4050000000000001</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -5831,35 +5928,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>43</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>CORREIO VIA SEDEX 43,00</t>
-        </is>
-      </c>
+        <v>3795</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>43</v>
+        <v>3795</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -5868,78 +5961,78 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>3325</v>
+        <v>350</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>3325</v>
+        <v>350</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>717</v>
+        <v>18025</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>717</v>
+        <v>18025</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5948,38 +6041,38 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C82" t="n">
-        <v>7375</v>
+        <v>1.68e+16</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>7375</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5988,23 +6081,27 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
+          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>117</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CORREIO VIA SEDEX 43,00</t>
+        </is>
+      </c>
       <c r="E83" t="n">
         <v>13</v>
       </c>
@@ -6015,11 +6112,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6035,14 +6132,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
+          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>4.2e+16</v>
+        <v>3325</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
@@ -6055,11 +6152,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>4.2e+16</v>
+        <v>3325</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6075,14 +6172,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
+          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>6449999999999999</v>
+        <v>717</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
@@ -6095,11 +6192,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>6449999999999999</v>
+        <v>717</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6115,14 +6212,14 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>48</v>
+        <v>7375</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
@@ -6135,11 +6232,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>48</v>
+        <v>7375</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6155,14 +6252,14 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>475</v>
+        <v>117</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
@@ -6175,11 +6272,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>475</v>
+        <v>117</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6195,14 +6292,14 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>1725</v>
+        <v>4.2e+16</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
@@ -6215,11 +6312,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1725</v>
+        <v>4.2e+16</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6235,14 +6332,14 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>6000000000000001</v>
+        <v>6449999999999999</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
@@ -6255,11 +6352,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>6000000000000001</v>
+        <v>6449999999999999</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -6275,14 +6372,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>8399999999999999</v>
+        <v>48</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
@@ -6295,18 +6392,178 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>48</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>475</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="n">
+        <v>13</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>475</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1725</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="n">
+        <v>13</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>1725</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="n">
+        <v>13</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>8399999999999999</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="n">
+        <v>13</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
           <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
-      <c r="H90" t="n">
+      <c r="H94" t="n">
         <v>8399999999999999</v>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
         <is>
           <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2410,62 +2410,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SK1FN_56XX</t>
+          <t>SJH_RHL1BL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>511.65999999999997</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>511.65999999999997</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-10-20T12:26:24.223Z</t>
+          <t>2025-11-10T14:43:09.194Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Viktor Chagas</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-10-13T12:45:43.188Z</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-11-03T15:08:36.141Z</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2483,52 +2491,44 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>MzQ2NDM2Nzo1NzAxNg==</t>
+          <t>MzkzMzA3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H16WCCZPEG</t>
+          <t>SK1FN_56XX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
+          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-10-14T18:12:15.015Z</t>
+          <t>2025-10-20T12:26:24.223Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2551,12 +2551,12 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-10-07T18:22:28.553Z</t>
+          <t>2025-10-13T12:45:43.188Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>MzQ2NDM2Nzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2588,37 +2588,40 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R1BQOWO2EE</t>
+          <t>H16WCCZPEG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GRALHA AZUL PONTA GROSSA</t>
+          <t>FRANCESCO DE TOMMASO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
-BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2628,7 +2631,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-10-06T19:05:55.326Z</t>
+          <t>2025-10-14T18:12:15.015Z</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2641,35 +2644,125 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
+          <t>2025-10-07T18:22:28.553Z</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>R1BQOWO2EE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
+BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2025-10-06T19:05:55.326Z</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>2025-09-29T20:26:53.403Z</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>NDgyNTE1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -2686,7 +2779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5608,31 +5701,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
+          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>99</v>
+        <v>6000000000000001</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>33</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5641,38 +5734,38 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
+          <t>MTE2ZmIzMDUtYWVlNC00N2M1LWI2YWEtYmQ4ZmZmNDMyY2M5OjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>38656</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5681,38 +5774,38 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
+          <t>M2E2MGI3YzMtNmIxZi00NGM4LWEyMzctNWUyNzcxODM0ZWM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>350</v>
+        <v>117</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>350</v>
+        <v>117</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5721,38 +5814,38 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
+          <t>NGI5MDNkYWQtNzdhZC00NTM4LTgxNGItNzE4NDRjZWNlYmYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>85</v>
+        <v>9000000000000001</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>85</v>
+        <v>3e+16</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5761,78 +5854,78 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
+          <t>NTM1MTUxMDQtZGQxYi00ODQ4LWE2YmYtNGZkNDgxY2RlOWU2OjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>350</v>
+        <v>825</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>OTUzMmM4MTUtMjYxYy00ZjI2LThkMDAtMjc0MzkyYjRjYjY2OjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>350</v>
+        <v>825</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
+          <t>NTQ5YjVkYWItMzYyOS00ODg5LWIwOWEtODVjZDhlMWY3N2FkOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>1086</v>
+        <v>717</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1086</v>
+        <v>717</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -5841,38 +5934,38 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
+          <t>NWE2NzVhZjgtYTQ5OC00NjgxLTkxNmYtNzc4YWZhMjZjZTNlOjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>350</v>
+        <v>7375</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>350</v>
+        <v>7375</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -5881,38 +5974,38 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
+          <t>NjM4Y2JlY2EtMTNjZS00ZmRkLWJjMTQtZTU2OTZkMGE1NTM2OjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>4050000000000001</v>
+        <v>96</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>4050000000000001</v>
+        <v>48</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -5921,38 +6014,42 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
+          <t>N2I3ZTkxNTUtMWY0NC00MjhhLWIxZDctYWMxZTFhZWYxOGYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>3795</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Troca do Balde via correio</t>
+        </is>
+      </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>3795</v>
+        <v>43</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -5961,78 +6058,78 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
+          <t>YTdmOGYzMDctZDg5ZS00MGYyLWFkMzAtMTEzNzkzNmI5MjZmOjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>350</v>
+        <v>3.33e+16</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ODEwYWQzODUtY2JhYy00NmM5LWE5M2UtYzQ1MDMyY2JmZjNlOjU3MDE2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>350</v>
+        <v>1.11e+16</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
+          <t>YWVhMDUwNDEtMWZjMy00MGY0LTliMjEtZmQ0Njc2ZmYxMmRiOjU3MDE2</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>18025</v>
+        <v>2525</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>YTI5MDAxYjctNzYxNS00Yzc0LTk1MWItYWJjMDg5NWJiN2QzOjU3MDE2</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>18025</v>
+        <v>2525</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6041,34 +6138,34 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
+          <t>YzczZTA5NTktMzAzNS00NWE1LWJiYWUtNWQ5YWYzOTcwOTYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C82" t="n">
-        <v>1.68e+16</v>
+        <v>1.89e+16</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -6081,42 +6178,38 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+          <t>ZDk0OTlmM2UtNGFlYy00MzM3LWFiY2UtYzRmMjBhYjFiN2ZiOjU3MDE2</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>43</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>CORREIO VIA SEDEX 43,00</t>
-        </is>
-      </c>
+        <v>6449999999999999</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>43</v>
+        <v>6449999999999999</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6125,38 +6218,38 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+          <t>ZDk1OWFkMjYtZGJkZi00OWRkLWI5ZTktMjJiOTZlN2VlYzBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>3325</v>
+        <v>1.26e+16</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>3325</v>
+        <v>4.2e+16</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6165,38 +6258,38 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+          <t>ZTk0MDQ3MTktYzcwMy00ZTU5LTg5MjMtOGU3MDllYTg0MjAyOjU3MDE2</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>717</v>
+        <v>1725</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>717</v>
+        <v>1725</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6205,38 +6298,38 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C86" t="n">
-        <v>7375</v>
+        <v>99</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>7375</v>
+        <v>33</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6245,38 +6338,38 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OGZmOWRhOTQtNDdiZC00MDNlLWE5MTctZTc5MTVlY2FmZWYzOjU3MDE2</t>
+          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>117</v>
+        <v>38656</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6285,38 +6378,38 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>YWQ4YTM5MmEtZDQ0OC00ZjdhLWE3NjQtNGI0MjJlYzBjNGFkOjU3MDE2</t>
+          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>4.2e+16</v>
+        <v>350</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>4.2e+16</v>
+        <v>350</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6325,38 +6418,38 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>YWVmZTk0M2ItZWU2ZS00ODMyLTgzZWUtMGYwMTdkMmVjMmYwOjU3MDE2</t>
+          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>6449999999999999</v>
+        <v>85</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>6449999999999999</v>
+        <v>85</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -6365,78 +6458,78 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>YjA5NTJjYmItOTU2MS00NThlLTliZDQtMzhkNGQwNWY4MGFmOjU3MDE2</t>
+          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>48</v>
+        <v>350</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>48</v>
+        <v>350</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Yjk1N2RlZTctZDMxZi00YzJlLWI1NTktZmEyMjQ1NjQ1ZDg3OjU3MDE2</t>
+          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>475</v>
+        <v>1086</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ODNiOGMzNWItYjY5NC00ZWNlLWFjYzAtNGFmYjE5MTRjZjY0OjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>475</v>
+        <v>1086</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6445,38 +6538,38 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>YmY5ZDcxOGUtOTg3Ny00YjYyLTk4ZmMtZDY4MTk3OTM4MmFjOjU3MDE2</t>
+          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>1725</v>
+        <v>350</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1725</v>
+        <v>350</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6485,38 +6578,38 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>YzMxNzM5OTQtY2Y0MS00NjdmLWI3MzctMzVhYTk3ODgzMWM4OjU3MDE2</t>
+          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>6000000000000001</v>
+        <v>4050000000000001</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>6000000000000001</v>
+        <v>4050000000000001</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6525,45 +6618,329 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ZTNmNTk0NDctYjYxYy00MzgyLWE0NWQtZDY5NjI3NTdkNGQ4OjU3MDE2</t>
+          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>8399999999999999</v>
+        <v>3795</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
+        <v>8</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>3795</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>350</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>8</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>350</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>18025</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="n">
+        <v>8</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>18025</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1.68e+16</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="n">
+        <v>8</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="n">
+        <v>43</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CORREIO VIA SEDEX 43,00</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
         <v>13</v>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H94" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>43</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="n">
+        <v>3325</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="n">
+        <v>13</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>3325</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="n">
+        <v>717</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="n">
+        <v>13</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>717</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="n">
+        <v>7375</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="n">
+        <v>13</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>7375</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
         <is>
           <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
         </is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1700,70 +1700,66 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>R1R8PTIYBL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>orçamento</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-11-10T19:48:40.136Z</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
+          <t>2025-11-03T19:49:41.839Z</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1771,58 +1767,58 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDgyMzkyMzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1832,28 +1828,28 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>rffccfc</t>
+          <t>jose da silva</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>HENRIQUE</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
+          <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1864,17 +1860,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1886,55 +1882,67 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BKMVCD56XX</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-10-20T12:54:09.917Z</t>
+          <t>2025-09-04T16:07:52.834Z</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2025-10-13T13:10:02.576Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1955,75 +1963,67 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NDgyNTIyNjo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>BKMVCD56XX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Substituição de 3 compressores</t>
-        </is>
-      </c>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
+          <t>2025-10-20T12:54:09.917Z</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-10-13T13:10:02.576Z</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2044,74 +2044,78 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2129,32 +2133,117 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2162,7 +2251,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2170,106 +2259,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2292,10 +2292,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2313,7 +2317,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2325,22 +2329,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SYSJ0HARXL</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
+          <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -2349,35 +2353,35 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-04T13:33:37.491Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-10-28T14:06:21.222Z</t>
+          <t>2025-09-08T21:59:15.256Z</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2398,34 +2402,34 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>NDgyMTM3Mjo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SJH_RHL1BL</t>
+          <t>SYSJ0HARXL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
+          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -2434,43 +2438,35 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>511.65999999999997</t>
+          <t>2123.15</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>511.65999999999997</t>
+          <t>2123.15</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-10T14:43:09.194Z</t>
+          <t>2025-11-04T13:33:37.491Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Viktor Chagas</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-11-03T15:08:36.141Z</t>
+          <t>2025-10-28T14:06:21.222Z</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2491,74 +2487,82 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>MzkzMzA3Mjo1NzAxNg==</t>
+          <t>NDgyMTM3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SK1FN_56XX</t>
+          <t>SJH_RHL1BL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>511.65999999999997</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>511.65999999999997</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-10-20T12:26:24.223Z</t>
+          <t>2025-11-10T14:43:09.194Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Viktor Chagas</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-10-13T12:45:43.188Z</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-11-03T15:08:36.141Z</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2576,52 +2580,44 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>MzQ2NDM2Nzo1NzAxNg==</t>
+          <t>MzkzMzA3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H16WCCZPEG</t>
+          <t>SK1FN_56XX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
+          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2631,7 +2627,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-10-14T18:12:15.015Z</t>
+          <t>2025-10-20T12:26:24.223Z</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2644,12 +2640,12 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-10-07T18:22:28.553Z</t>
+          <t>2025-10-13T12:45:43.188Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2669,7 +2665,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>MzQ2NDM2Nzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2681,37 +2677,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R1BQOWO2EE</t>
+          <t>H16WCCZPEG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GRALHA AZUL PONTA GROSSA</t>
+          <t>FRANCESCO DE TOMMASO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
-BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2721,7 +2720,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-10-06T19:05:55.326Z</t>
+          <t>2025-10-14T18:12:15.015Z</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2734,35 +2733,125 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
+          <t>2025-10-07T18:22:28.553Z</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>R1BQOWO2EE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL PONTA GROSSA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
+BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>549.22</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2025-10-06T19:05:55.326Z</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
           <t>2025-09-29T20:26:53.403Z</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>NDgyNTE1Mzo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -4969,35 +5058,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>10000</v>
+        <v>43</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5006,126 +5091,122 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>680</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>680</v>
+        <v>85</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>855</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>855</v>
+        <v>350</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
         <v>2</v>
       </c>
-      <c r="C57" t="n">
-        <v>96</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="n">
-        <v>6</v>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>48</v>
+        <v>10000</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -5134,101 +5215,109 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>6000000000000001</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E58" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>6000000000000001</v>
+        <v>680</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>3.8825e+16</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3.8825e+16</v>
+        <v>855</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>2.1e+16</v>
+        <v>96</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
@@ -5241,11 +5330,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2.1e+16</v>
+        <v>48</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5261,14 +5350,14 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>3e+16</v>
+        <v>6000000000000001</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
@@ -5281,11 +5370,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3e+16</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5301,75 +5390,71 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>47370</v>
+        <v>3.8825e+16</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>47370</v>
+        <v>3.8825e+16</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
-        </is>
-      </c>
+        <v>2.1e+16</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5378,23 +5463,147 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" t="n">
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
         <v>1700</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -5402,46 +5611,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E67" t="n">
         <v>2</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H64" t="n">
+      <c r="H67" t="n">
         <v>1700</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" t="n">
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
         <v>494677</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -5459,218 +5668,86 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="E68" t="n">
         <v>3</v>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H65" t="n">
+      <c r="H68" t="n">
         <v>494677</v>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="n">
-        <v>3</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" t="n">
-        <v>3.2215e+16</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="n">
-        <v>5</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>3.2215e+16</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" t="n">
-        <v>823</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>310Km</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>5</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>2</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>70</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Enviado por Sedex10 de SP para DF</t>
-        </is>
-      </c>
+        <v>1050</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>43</v>
+        <v>1050</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
+          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>908</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>3.2215e+16</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
         <v>5</v>
       </c>
@@ -5681,15 +5758,15 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>350</v>
+        <v>3.2215e+16</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5701,71 +5778,79 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
+          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>6000000000000001</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
+        <v>823</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>310Km</t>
+        </is>
+      </c>
       <c r="E71" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>6000000000000001</v>
+        <v>2</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MTE2ZmIzMDUtYWVlNC00N2M1LWI2YWEtYmQ4ZmZmNDMyY2M5OjU3MDE2</t>
+          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Enviado por Sedex10 de SP para DF</t>
+        </is>
+      </c>
       <c r="E72" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>8399999999999999</v>
+        <v>43</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5774,61 +5859,65 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>M2E2MGI3YzMtNmIxZi00NGM4LWEyMzctNWUyNzcxODM0ZWM5OjU3MDE2</t>
+          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>117</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
+        <v>908</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E73" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>117</v>
+        <v>350</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NGI5MDNkYWQtNzdhZC00NTM4LTgxNGItNzE4NDRjZWNlYmYxOjU3MDE2</t>
+          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>9000000000000001</v>
+        <v>6000000000000001</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
@@ -5841,11 +5930,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>3e+16</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5861,14 +5950,14 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NTM1MTUxMDQtZGQxYi00ODQ4LWE2YmYtNGZkNDgxY2RlOWU2OjU3MDE2</t>
+          <t>MTE2ZmIzMDUtYWVlNC00N2M1LWI2YWEtYmQ4ZmZmNDMyY2M5OjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>825</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
@@ -5881,11 +5970,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>OTUzMmM4MTUtMjYxYy00ZjI2LThkMDAtMjc0MzkyYjRjYjY2OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>825</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5901,14 +5990,14 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NTQ5YjVkYWItMzYyOS00ODg5LWIwOWEtODVjZDhlMWY3N2FkOjU3MDE2</t>
+          <t>M2E2MGI3YzMtNmIxZi00NGM4LWEyMzctNWUyNzcxODM0ZWM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>717</v>
+        <v>117</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
@@ -5921,11 +6010,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>717</v>
+        <v>117</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -5941,14 +6030,14 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NWE2NzVhZjgtYTQ5OC00NjgxLTkxNmYtNzc4YWZhMjZjZTNlOjU3MDE2</t>
+          <t>NGI5MDNkYWQtNzdhZC00NTM4LTgxNGItNzE4NDRjZWNlYmYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>7375</v>
+        <v>9000000000000001</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
@@ -5961,11 +6050,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>7375</v>
+        <v>3e+16</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -5981,14 +6070,14 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NjM4Y2JlY2EtMTNjZS00ZmRkLWJjMTQtZTU2OTZkMGE1NTM2OjU3MDE2</t>
+          <t>NTM1MTUxMDQtZGQxYi00ODQ4LWE2YmYtNGZkNDgxY2RlOWU2OjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>96</v>
+        <v>825</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
@@ -6001,11 +6090,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>OTUzMmM4MTUtMjYxYy00ZjI2LThkMDAtMjc0MzkyYjRjYjY2OjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>48</v>
+        <v>825</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6021,20 +6110,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>N2I3ZTkxNTUtMWY0NC00MjhhLWIxZDctYWMxZTFhZWYxOGYxOjU3MDE2</t>
+          <t>NTQ5YjVkYWItMzYyOS00ODg5LWIwOWEtODVjZDhlMWY3N2FkOjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>43</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Troca do Balde via correio</t>
-        </is>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
         <v>16</v>
       </c>
@@ -6045,11 +6130,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>43</v>
+        <v>717</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6065,14 +6150,14 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>YTdmOGYzMDctZDg5ZS00MGYyLWFkMzAtMTEzNzkzNmI5MjZmOjU3MDE2</t>
+          <t>NWE2NzVhZjgtYTQ5OC00NjgxLTkxNmYtNzc4YWZhMjZjZTNlOjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>3.33e+16</v>
+        <v>7375</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
@@ -6085,11 +6170,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ODEwYWQzODUtY2JhYy00NmM5LWE5M2UtYzQ1MDMyY2JmZjNlOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1.11e+16</v>
+        <v>7375</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -6105,14 +6190,14 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>YWVhMDUwNDEtMWZjMy00MGY0LTliMjEtZmQ0Njc2ZmYxMmRiOjU3MDE2</t>
+          <t>NjM4Y2JlY2EtMTNjZS00ZmRkLWJjMTQtZTU2OTZkMGE1NTM2OjU3MDE2</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>2525</v>
+        <v>96</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
@@ -6125,11 +6210,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>YTI5MDAxYjctNzYxNS00Yzc0LTk1MWItYWJjMDg5NWJiN2QzOjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2525</v>
+        <v>48</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6145,16 +6230,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>YzczZTA5NTktMzAzNS00NWE1LWJiYWUtNWQ5YWYzOTcwOTYwOjU3MDE2</t>
+          <t>N2I3ZTkxNTUtMWY0NC00MjhhLWIxZDctYWMxZTFhZWYxOGYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>1.89e+16</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Troca do Balde via correio</t>
+        </is>
+      </c>
       <c r="E82" t="n">
         <v>16</v>
       </c>
@@ -6165,11 +6254,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>2.1e+16</v>
+        <v>43</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -6185,14 +6274,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ZDk0OTlmM2UtNGFlYy00MzM3LWFiY2UtYzRmMjBhYjFiN2ZiOjU3MDE2</t>
+          <t>YTdmOGYzMDctZDg5ZS00MGYyLWFkMzAtMTEzNzkzNmI5MjZmOjU3MDE2</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C83" t="n">
-        <v>6449999999999999</v>
+        <v>3.33e+16</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
@@ -6205,11 +6294,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+          <t>ODEwYWQzODUtY2JhYy00NmM5LWE5M2UtYzQ1MDMyY2JmZjNlOjU3MDE2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>6449999999999999</v>
+        <v>1.11e+16</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6225,14 +6314,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ZDk1OWFkMjYtZGJkZi00OWRkLWI5ZTktMjJiOTZlN2VlYzBkOjU3MDE2</t>
+          <t>YWVhMDUwNDEtMWZjMy00MGY0LTliMjEtZmQ0Njc2ZmYxMmRiOjU3MDE2</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>1.26e+16</v>
+        <v>2525</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
@@ -6245,11 +6334,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+          <t>YTI5MDAxYjctNzYxNS00Yzc0LTk1MWItYWJjMDg5NWJiN2QzOjU3MDE2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>4.2e+16</v>
+        <v>2525</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6265,14 +6354,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ZTk0MDQ3MTktYzcwMy00ZTU5LTg5MjMtOGU3MDllYTg0MjAyOjU3MDE2</t>
+          <t>YzczZTA5NTktMzAzNS00NWE1LWJiYWUtNWQ5YWYzOTcwOTYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C85" t="n">
-        <v>1725</v>
+        <v>1.89e+16</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
@@ -6285,11 +6374,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1725</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6305,31 +6394,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
+          <t>ZDk0OTlmM2UtNGFlYy00MzM3LWFiY2UtYzRmMjBhYjFiN2ZiOjU3MDE2</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>99</v>
+        <v>6449999999999999</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>33</v>
+        <v>6449999999999999</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6338,38 +6427,38 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
+          <t>ZDk1OWFkMjYtZGJkZi00OWRkLWI5ZTktMjJiOTZlN2VlYzBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C87" t="n">
-        <v>38656</v>
+        <v>1.26e+16</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>4.2e+16</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6378,38 +6467,38 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
+          <t>ZTk0MDQ3MTktYzcwMy00ZTU5LTg5MjMtOGU3MDllYTg0MjAyOjU3MDE2</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>350</v>
+        <v>1725</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>350</v>
+        <v>1725</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6418,21 +6507,21 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
+          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
@@ -6445,11 +6534,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -6465,14 +6554,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
+          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>350</v>
+        <v>38656</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
@@ -6485,15 +6574,15 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6505,31 +6594,31 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
+          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>1086</v>
+        <v>350</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1086</v>
+        <v>350</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6538,38 +6627,38 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
+          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6578,61 +6667,61 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
+          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>4050000000000001</v>
+        <v>350</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>4050000000000001</v>
+        <v>350</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
+          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>3795</v>
+        <v>1086</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
@@ -6645,11 +6734,11 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>3795</v>
+        <v>1086</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -6665,7 +6754,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
+          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -6685,7 +6774,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -6693,7 +6782,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6705,14 +6794,14 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
+          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>18025</v>
+        <v>4050000000000001</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
@@ -6725,11 +6814,11 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>18025</v>
+        <v>4050000000000001</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6745,14 +6834,14 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
+          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>1.68e+16</v>
+        <v>3795</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
@@ -6765,11 +6854,11 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>2.1e+16</v>
+        <v>3795</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6785,75 +6874,71 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>43</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>CORREIO VIA SEDEX 43,00</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>43</v>
+        <v>350</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MzViYTlhNTItOTE2MC00NmJlLTlkNGMtN2MyZTQ3M2NlNzFiOjU3MDE2</t>
+          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>3325</v>
+        <v>18025</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ZDNmZWYzYTctMmQwZC00YTJjLWJjYjAtYTZiYzQ4ZjBiYTIxOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>3325</v>
+        <v>18025</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6862,38 +6947,38 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NGNmZDE3ZWQtZTFhMy00MWZkLWE3ZTgtYjg5ZDA1MTQ2MjUwOjU3MDE2</t>
+          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C100" t="n">
-        <v>717</v>
+        <v>1.68e+16</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>717</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6902,23 +6987,27 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NmRhZDJlMTQtZWQ0My00NWIzLThhMmMtYmM1OTIxYTUxN2UwOjU3MDE2</t>
+          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>7375</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CORREIO VIA SEDEX 43,00</t>
+        </is>
+      </c>
       <c r="E101" t="n">
         <v>13</v>
       </c>
@@ -6929,11 +7018,11 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>7375</v>
+        <v>43</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -2770,67 +2770,58 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R1BQOWO2EE</t>
+          <t>BYDFGIWKZG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GRALHA AZUL PONTA GROSSA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ORÇAMENTO REFERENTE BALDE DANIFICADO POR MAL USO
-BALDE NOVO , SE FOR ENTREGAR O BALDE 43,00 PELO CORREIO VIA SEDEX</t>
-        </is>
-      </c>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>549.22</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-10-06T19:05:55.326Z</t>
+          <t>2025-11-11T15:57:22.457Z</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-09-29T20:26:53.403Z</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>MDBmZTJkNzktN2M1YS00MDc0LWE2YTctNzZiZGNkZWFmYTIwOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-11-04T15:57:50.841Z</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2848,12 +2839,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>NDgyNTE1Mzo1NzAxNg==</t>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -6994,35 +6985,31 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MWUxOTRiYWItMTljOC00NTMwLWIzODQtZjA3YTRjMDYzMjZlOjU3MDE2</t>
+          <t>MzA4MjgxOWUtMzhjMi00NjI1LTllYjctZDU2ZjU3ZTM0YjQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>43</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>CORREIO VIA SEDEX 43,00</t>
-        </is>
-      </c>
+        <v>6000000000000001</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>43</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7031,7 +7018,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>ZWQ5MzRmMGYtZDE1Yy00ODY1LWFjMDAtZTY4ZWE1YzRkODk5OjU3MDE2</t>
+          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -2800,7 +2800,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2809,13 +2809,21 @@
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Marcos</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/e9de7ba0-386a-464d-8581-a8798001ad78/signatures/a05c1641-9b6c-465a-90ae-a4510b4e3986.png</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>2025-11-04T15:57:50.841Z</t>
@@ -2844,7 +2852,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -2448,7 +2448,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -539,60 +539,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B1IJGVB5A</t>
+          <t>SYXJ3ADJZX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R6IHIJPUZR</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>7722118000140 - FUND DE APOIO AO ENSINO PESQ E ASSISTENCIA HCFMRPUSP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Preventiva já foi paga que o atendimento de limpeza da maquina, somente estamos cobrando as peças e 01 hora do técnico</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1056.4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1056.4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2024-08-14T17:42:21.925Z</t>
+          <t>2025-11-12T12:52:46.887Z</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IRACILDA LOPES</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2024-08-07T17:45:02.123Z</t>
+          <t>2025-11-05T13:06:35.085Z</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ZDM4ZDY1NjMtN2E5Yy00ZDQ3LWFlMDktYzUwYzk4NDQ4NWY1OjU3MDE2</t>
+          <t>ZWMwNWE3NTgtODkyOC00ZjE5LWI0YTgtYjY0NmYwMDY2OGIwOjU3MDE2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -612,82 +616,74 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>MzMxMDM0OTo1NzAxNg==</t>
+          <t>NDE2MTc1Nzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SKB8DXCYGE</t>
+          <t>B1IJGVB5A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dilmatec</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Diagnostico e resoluçao problema em 02 equipamentos que nao estavam atingindo temperatura</t>
-        </is>
-      </c>
+          <t>R6IHIJPUZR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-09-04T15:24:13.519Z</t>
+          <t>2024-08-14T17:42:21.925Z</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Rafael Machado Barboza</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/2a7e8c69-1223-41d3-967d-474788d2fb01/signatures/51c1ade7-ff37-4ee9-b84d-46ee75381607.png</t>
-        </is>
-      </c>
+          <t>IRACILDA LOPES</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2025-08-28T15:35:41.479Z</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>2024-08-07T17:45:02.123Z</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ZDM4ZDY1NjMtN2E5Yy00ZDQ3LWFlMDktYzUwYzk4NDQ4NWY1OjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -705,74 +701,82 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzMxMDM0OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RYUVNWH3EG</t>
+          <t>SKB8DXCYGE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GARANTIA/61012019000142 - ASSOCIAÇÃO BRASILEIRA IJCSUD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Dilmatec</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Diagnostico e resoluçao problema em 02 equipamentos que nao estavam atingindo temperatura</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-10-09T21:18:04.630Z</t>
+          <t>2025-09-04T15:24:13.519Z</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Rafael Machado Barboza</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/2a7e8c69-1223-41d3-967d-474788d2fb01/signatures/51c1ade7-ff37-4ee9-b84d-46ee75381607.png</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-10-02T21:19:25.794Z</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-28T15:35:41.479Z</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -790,88 +794,72 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>NDcxNTkzODo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HJ0GXQO2EG</t>
+          <t>RYUVNWH3EG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JOANA DARC OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Orçamento  para reforma de TFK 02 kg</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Reforma</t>
-        </is>
-      </c>
+          <t>GARANTIA/61012019000142 - ASSOCIAÇÃO BRASILEIRA IJCSUD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2167.29</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2167.29</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-10-06T13:42:48.402Z</t>
+          <t>2025-10-09T21:18:04.630Z</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Joana D’Arc Oliveira </t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-09-29T15:17:10.234Z</t>
+          <t>2025-10-02T21:19:25.794Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
+          <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -891,72 +879,88 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>MzM3ODI5ODo1NzAxNg==</t>
+          <t>NDcxNTkzODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HYTE7IDHEX</t>
+          <t>HJ0GXQO2EG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MAQUINA 02</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>JOANA DARC OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Orçamento  para reforma de TFK 02 kg</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Reforma</t>
+        </is>
+      </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>979.73</t>
+          <t>2167.29</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>979.73</t>
+          <t>2167.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-10-06T18:41:42.725Z</t>
+          <t>2025-10-06T13:42:48.402Z</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joana D’Arc Oliveira </t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2025-09-29T18:42:56.833Z</t>
+          <t>2025-09-29T15:17:10.234Z</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -976,29 +980,29 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzM3ODI5ODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SYLVG8O3EG</t>
+          <t>HYTE7IDHEX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
+          <t>MAQUINA 02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1008,12 +1012,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>979.73</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>979.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1023,7 +1027,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-10-06T18:34:31.188Z</t>
+          <t>2025-10-06T18:41:42.725Z</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1036,7 +1040,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-09-29T18:38:37.635Z</t>
+          <t>2025-09-29T18:42:56.833Z</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1073,17 +1077,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BJFPMUNTXG</t>
+          <t>SYLVG8O3EG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MIX SOLUCOES AMBIENTAIS LTDA</t>
+          <t>MAQUINA 01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1093,12 +1097,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1108,7 +1112,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-10-15T21:09:42.233Z</t>
+          <t>2025-10-06T18:34:31.188Z</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1121,12 +1125,12 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-10-08T21:12:33.362Z</t>
+          <t>2025-09-29T18:38:37.635Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1146,7 +1150,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>NDgzNDc2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1158,40 +1162,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BYCZRKIPEL</t>
+          <t>BJFPMUNTXG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>62730134620 - FRANCISCO DE LUCCA JUNIOR</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>GARANTIA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>garantia</t>
-        </is>
-      </c>
+          <t>MIX SOLUCOES AMBIENTAIS LTDA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1201,7 +1197,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-10-17T12:48:39.389Z</t>
+          <t>2025-10-15T21:09:42.233Z</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1214,12 +1210,12 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-10-10T13:07:18.487Z</t>
+          <t>2025-10-08T21:12:33.362Z</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
+          <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1239,7 +1235,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>NDgyMzMyODo1NzAxNg==</t>
+          <t>NDgzNDc2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1251,20 +1247,113 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BYCZRKIPEL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>62730134620 - FRANCISCO DE LUCCA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GARANTIA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>garantia</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>530.25</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>530.25</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2025-10-17T12:48:39.389Z</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-10T13:07:18.487Z</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>NDgyMzMyODo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1273,7 +1362,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1282,106 +1371,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1391,20 +1391,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
+          <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1437,36 +1437,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SJBLZ0HQLG</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OUTBACK MORUMBI</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1476,27 +1480,23 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:27:17.728Z</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1526,32 +1526,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1561,7 +1565,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1574,12 +1578,12 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
+          <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1599,7 +1603,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1611,40 +1615,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1654,7 +1650,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1667,10 +1663,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1700,46 +1700,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R1R8PTIYBL</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>orçamento</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-11-10T19:48:40.136Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1752,14 +1756,10 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2025-11-03T19:49:41.839Z</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-28T16:05:56.490Z</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1777,82 +1777,78 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NDgyMzkyMzo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>R1R8PTIYBL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>orçamento</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-11-10T19:48:40.136Z</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>2025-11-03T19:49:41.839Z</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1860,58 +1856,58 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDgyMzkyMzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1921,28 +1917,28 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>rffccfc</t>
+          <t>jose da silva</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>HENRIQUE</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
+          <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1953,17 +1949,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1975,55 +1971,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BKMVCD56XX</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-10-20T12:54:09.917Z</t>
+          <t>2025-09-04T16:07:52.834Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-10-13T13:10:02.576Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2044,75 +2052,67 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NDgyNTIyNjo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>BKMVCD56XX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Substituição de 3 compressores</t>
-        </is>
-      </c>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
+          <t>2025-10-20T12:54:09.917Z</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-10-13T13:10:02.576Z</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2133,74 +2133,78 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2218,32 +2222,117 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2251,7 +2340,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2259,106 +2348,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2381,10 +2381,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2402,7 +2406,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2414,22 +2418,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SYSJ0HARXL</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
+          <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -2438,12 +2442,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2453,20 +2457,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-04T13:33:37.491Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-10-28T14:06:21.222Z</t>
+          <t>2025-09-08T21:59:15.256Z</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2487,7 +2491,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>NDgyMTM3Mjo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2499,22 +2503,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SJH_RHL1BL</t>
+          <t>SYSJ0HARXL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
+          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -2523,43 +2527,35 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>511.65999999999997</t>
+          <t>2123.15</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>511.65999999999997</t>
+          <t>2123.15</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-10T14:43:09.194Z</t>
+          <t>2025-11-04T13:33:37.491Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Viktor Chagas</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-11-03T15:08:36.141Z</t>
+          <t>2025-10-28T14:06:21.222Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2580,74 +2576,82 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>MzkzMzA3Mjo1NzAxNg==</t>
+          <t>NDgyMTM3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SK1FN_56XX</t>
+          <t>SJH_RHL1BL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>511.65999999999997</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>511.65999999999997</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-10-20T12:26:24.223Z</t>
+          <t>2025-11-10T14:43:09.194Z</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Viktor Chagas</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-10-13T12:45:43.188Z</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-11-03T15:08:36.141Z</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2665,52 +2669,44 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>MzQ2NDM2Nzo1NzAxNg==</t>
+          <t>MzkzMzA3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H16WCCZPEG</t>
+          <t>SK1FN_56XX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
+          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>1172.55</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2720,7 +2716,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-10-14T18:12:15.015Z</t>
+          <t>2025-10-20T12:26:24.223Z</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2733,12 +2729,12 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2025-10-07T18:22:28.553Z</t>
+          <t>2025-10-13T12:45:43.188Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2758,7 +2754,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>MzQ2NDM2Nzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -2770,66 +2766,70 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BYDFGIWKZG</t>
+          <t>H16WCCZPEG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+          <t>FRANCESCO DE TOMMASO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1047.65</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-11T15:57:22.457Z</t>
+          <t>2025-10-14T18:12:15.015Z</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Marcos</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/e9de7ba0-386a-464d-8581-a8798001ad78/signatures/a05c1641-9b6c-465a-90ae-a4510b4e3986.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-11-04T15:57:50.841Z</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+          <t>2025-10-07T18:22:28.553Z</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>NDgyNTIyNjo1NzAxNg==</t>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
@@ -2925,119 +2925,115 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OTlhNzk3NzYtZGMzZC00MzBjLTlkY2MtNTQ4YzQ4MGE2YWQ1OjU3MDE2</t>
+          <t>MTZhZjRmN2MtYTIzMC00OWFiLWIzNzAtMmFiZmRjMGMyZGM0OjU3MDE2</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>300</v>
+        <v>6445</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NzQ3ZWZjY2YtNzk1MC00ZTI3LWI0NjItOTJmYWQ2YmQzOTY4OjU3MDE2</t>
+          <t>NjliMThkYjktMTc0Yy00OTg4LTg3OWMtNzEyZThiNjgyM2QzOjU3MDE2</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>600</v>
+        <v>6445</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MTc3NWUyYTAtZjAxNy00NWQwLTg2ZTMtYWFiZjYzMzZhOWUzOjU3MDE2</t>
+          <t>MjY4ZDZjNjItYzY0Mi00MzliLWJjYzEtM2E5ZjY1NTFiMjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>680</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>6232</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>ZjViZmRhN2QtZTFkMi00NmU4LWI4MjAtMDliMWEwODkwZTY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>680</v>
+        <v>3116</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NGMwNTQyYWMtNGNjZC00NjljLThlZWItMDYxMjg2NzkzMmJhOjU3MDE2</t>
+          <t>NGM2OWY4ZDUtOGZhNC00OWVlLTgyOTAtNmE1MDQ5ZDc0YzVmOjU3MDE2</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>855</v>
+        <v>350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+          <t>Hora de trabalho ECO</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>855</v>
+        <v>350</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3046,42 +3042,38 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NGRlMTM3N2EtNzUwNC00YmUyLThmZjItMDQxZTc1ZDNjODRiOjU3MDE2</t>
+          <t>Y2VjYzM3NTEtMTNjMi00OGEzLTlhMjMtZGM1OThiOTVkMWE4OjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>18025</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TROCADO EM GARANTIA</t>
-        </is>
-      </c>
+        <v>1875</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>OGIxODU3NTgtMGQwNS00YjNmLThmYTMtMDI1ZjZlNWM0OTMzOjU3MDE2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>18025</v>
+        <v>1875</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3090,162 +3082,170 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NmQ1MDliODYtNGYyYy00YTNiLTk1YWEtYmM0MTZhNDBkNTY1OjU3MDE2</t>
+          <t>OTlhNzk3NzYtZGMzZC00MzBjLTlkY2MtNTQ4YzQ4MGE2YWQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>350</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TROCADO EM GARANTIA</t>
-        </is>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>NzQ3ZWZjY2YtNzk1MC00ZTI3LWI0NjItOTJmYWQ2YmQzOTY4OjU3MDE2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MDFmODQ2OWUtMmMyMC00NzEwLWE4NTEtMmFkOWFjYjRlYjQ2OjU3MDE2</t>
+          <t>MTc3NWUyYTAtZjAxNy00NWQwLTg2ZTMtYWFiZjYzMzZhOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NDUwZmFlOTEtODg1My00ZTcwLWIwOTgtZWM2Nzc3MzgzNjgyOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>680</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MjhmNDNmYjAtZjgzMi00MThiLWEyNTAtZWVlODc0ZjQxYzliOjU3MDE2</t>
+          <t>NGMwNTQyYWMtNGNjZC00NjljLThlZWItMDYxMjg2NzkzMmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1365</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1365</v>
+        <v>855</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MmQyOGU2OWYtM2IzOS00ZjYwLWJmYTctYmViYTY2M2UxNzdjOjU3MDE2</t>
+          <t>NGRlMTM3N2EtNzUwNC00YmUyLThmZjItMDQxZTc1ZDNjODRiOjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>375</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>18025</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TROCADO EM GARANTIA</t>
+        </is>
+      </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>375</v>
+        <v>18025</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -3254,38 +3254,42 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MzVjNDRmYjctMTI1My00NDg3LThlNmUtOWZhN2YyYWMyNjg3OjU3MDE2</t>
+          <t>NmQ1MDliODYtNGYyYy00YTNiLTk1YWEtYmM0MTZhNDBkNTY1OjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1.152e+16</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TROCADO EM GARANTIA</t>
+        </is>
+      </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NDM0MjA4NTAtZjAwOC00YzMyLWJlM2QtODFlMzljMjE0OTk4OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.152e+16</v>
+        <v>350</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3294,21 +3298,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NDNkMGNjZmMtMjFmMS00NjQyLWI4OWYtYTk4ODg2NjkxMjcwOjU3MDE2</t>
+          <t>MDFmODQ2OWUtMmMyMC00NzEwLWE4NTEtMmFkOWFjYjRlYjQ2OjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
@@ -3321,15 +3325,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+          <t>NDUwZmFlOTEtODg1My00ZTcwLWIwOTgtZWM2Nzc3MzgzNjgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3341,14 +3345,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NDRlYzI5NjAtMTZmYi00MzM3LWEzZTEtNGJmOTg0Y2Y1MzFhOjU3MDE2</t>
+          <t>MjhmNDNmYjAtZjgzMi00MThiLWEyNTAtZWVlODc0ZjQxYzliOjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>700</v>
+        <v>1365</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
@@ -3361,15 +3365,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>350</v>
+        <v>1365</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3381,14 +3385,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N2NjNjliYTAtNTVlZi00NjNmLThkMmUtZGMzYzIyZjRhM2FiOjU3MDE2</t>
+          <t>MmQyOGU2OWYtM2IzOS00ZjYwLWJmYTctYmViYTY2M2UxNzdjOjU3MDE2</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
@@ -3401,11 +3405,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -3421,14 +3425,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OTg0ZDY5MWUtZTJiZS00NmM0LTg1OGMtNDQ1ZTMwMmY2MWE3OjU3MDE2</t>
+          <t>MzVjNDRmYjctMTI1My00NDg3LThlNmUtOWZhN2YyYWMyNjg3OjU3MDE2</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>1.152e+16</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
@@ -3441,11 +3445,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>NDM0MjA4NTAtZjAwOC00YzMyLWJlM2QtODFlMzljMjE0OTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>85</v>
+        <v>1.152e+16</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -3461,14 +3465,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OWRkMWJkNWQtMjE5Yy00OTY0LWExNzYtZTI4YzkyN2Q4ODdlOjU3MDE2</t>
+          <t>NDNkMGNjZmMtMjFmMS00NjQyLWI4OWYtYTk4ODg2NjkxMjcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
@@ -3481,15 +3485,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Y2FjZGRiY2YtOTQ5NS00NDIyLWE4ODctYjk4ZGUxNjU1MzMyOjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3501,14 +3505,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>YTAxNDZjNzgtMDljZi00ZGQ4LTkwOTItZmM5N2QyNzM3MGEwOjU3MDE2</t>
+          <t>NDRlYzI5NjAtMTZmYi00MzM3LWEzZTEtNGJmOTg0Y2Y1MzFhOjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>18025</v>
+        <v>700</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
@@ -3521,15 +3525,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3541,14 +3545,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>YTM1YmFkNmQtN2EzNS00Njk0LTliNTMtNmZiMjAwNzQ5NzFkOjU3MDE2</t>
+          <t>N2NjNjliYTAtNTVlZi00NjNmLThkMmUtZGMzYzIyZjRhM2FiOjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>25625</v>
+        <v>350</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
@@ -3561,11 +3565,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MTdjYWQ5ZTAtMmQ3YS00OTM0LWIyOGEtYzMxYjY1ODZkNDIzOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>25625</v>
+        <v>350</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3581,14 +3585,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>YzFlYTExODctMmJkNy00N2RhLThiMTQtZTVjMTY0NWY1Y2Y5OjU3MDE2</t>
+          <t>OTg0ZDY5MWUtZTJiZS00NmM0LTg1OGMtNDQ1ZTMwMmY2MWE3OjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>182225</v>
+        <v>85</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
@@ -3601,11 +3605,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>OWU3NmYwYWEtZWNhZi00YTBiLWE2NTUtNjE5NTkwNDIwZDNjOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>182225</v>
+        <v>85</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3621,14 +3625,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>YzRiYzAxZjEtOWY2Zi00ZWQ0LWJmMjgtZmYxY2RjNjY1OTBiOjU3MDE2</t>
+          <t>OWRkMWJkNWQtMjE5Yy00OTY0LWExNzYtZTI4YzkyN2Q4ODdlOjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>9940000000000000</v>
+        <v>72</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
@@ -3641,11 +3645,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>OWMxNWU5ZjUtOWI3Ny00ZmYyLWExMWYtM2RkYzA3ZWFjYzU5OjU3MDE2</t>
+          <t>Y2FjZGRiY2YtOTQ5NS00NDIyLWE4ODctYjk4ZGUxNjU1MzMyOjU3MDE2</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9940000000000000</v>
+        <v>18</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3661,14 +3665,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ZGMxMDhlMDAtNmY3Ni00OWE1LTg0MDMtZjVmNjUyZGVkNzZlOjU3MDE2</t>
+          <t>YTAxNDZjNzgtMDljZi00ZGQ4LTkwOTItZmM5N2QyNzM3MGEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>2073</v>
+        <v>18025</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
@@ -3681,11 +3685,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2073</v>
+        <v>18025</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3701,14 +3705,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZjczNzc1Y2UtNGU2Mi00NGEzLTk5NWUtYzRlZmRjMzFhMTI2OjU3MDE2</t>
+          <t>YTM1YmFkNmQtN2EzNS00Njk0LTliNTMtNmZiMjAwNzQ5NzFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>36</v>
+        <v>25625</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
@@ -3721,11 +3725,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ZmQ5YTY2ZWEtZDM4NS00MWMwLWI0NWYtODI3ZjAxNzRjNzE1OjU3MDE2</t>
+          <t>MTdjYWQ5ZTAtMmQ3YS00OTM0LWIyOGEtYzMxYjY1ODZkNDIzOjU3MDE2</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>25625</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3741,14 +3745,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ZmQ3OWNiYjEtZmY3Yi00MjVkLWJhODgtYjA3NjQyZWY1MzYwOjU3MDE2</t>
+          <t>YzFlYTExODctMmJkNy00N2RhLThiMTQtZTVjMTY0NWY1Y2Y5OjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1578</v>
+        <v>182225</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
@@ -3761,11 +3765,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Y2I2NzA1MTItNDc5NS00ZWVmLWJkOTktY2JlZmJiZTNmNTFlOjU3MDE2</t>
+          <t>OWU3NmYwYWEtZWNhZi00YTBiLWE2NTUtNjE5NTkwNDIwZDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1578</v>
+        <v>182225</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3781,71 +3785,71 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MTE0NDUwMGUtM2ZiMi00OWQ1LWFmY2EtMzNjNzZmNjBhMTVmOjU3MDE2</t>
+          <t>YzRiYzAxZjEtOWY2Zi00ZWQ0LWJmMjgtZmYxY2RjNjY1OTBiOjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>350</v>
+        <v>9940000000000000</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>OWMxNWU5ZjUtOWI3Ny00ZmYyLWExMWYtM2RkYzA3ZWFjYzU5OjU3MDE2</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>350</v>
+        <v>9940000000000000</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NWM5YzAxYzktMTIwMS00ZjhkLWJjOGMtN2U3NDlmOTlmMzRkOjU3MDE2</t>
+          <t>ZGMxMDhlMDAtNmY3Ni00OWE1LTg0MDMtZjVmNjUyZGVkNzZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3854,38 +3858,38 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NjRmMDVhODItNmU2Mi00ZDRhLTk5NmItNzM2ODI0YjE2MjRmOjU3MDE2</t>
+          <t>ZjczNzc1Y2UtNGU2Mi00NGEzLTk5NWUtYzRlZmRjMzFhMTI2OjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>1365</v>
+        <v>36</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+          <t>ZmQ5YTY2ZWEtZDM4NS00MWMwLWI0NWYtODI3ZjAxNzRjNzE1OjU3MDE2</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1365</v>
+        <v>9</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3894,38 +3898,38 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OGUzMjVkZDYtOTA3Yi00MjFjLWFjYzgtOWVlMGI3MjJkNjIzOjU3MDE2</t>
+          <t>ZmQ3OWNiYjEtZmY3Yi00MjVkLWJhODgtYjA3NjQyZWY1MzYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>350</v>
+        <v>1578</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>Y2I2NzA1MTItNDc5NS00ZWVmLWJkOTktY2JlZmJiZTNmNTFlOjU3MDE2</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>350</v>
+        <v>1578</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3934,21 +3938,21 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Yjk2YzIwMDktMzVkMy00ZGRjLWIwOTYtOTJjOWFlMjZiM2FhOjU3MDE2</t>
+          <t>MTE0NDUwMGUtM2ZiMi00OWQ1LWFmY2EtMzNjNzZmNjBhMTVmOjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
@@ -3961,15 +3965,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3981,14 +3985,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ZTA0MDdkOTgtNjJjMi00ZTgyLWFmMzEtYzg4MzdkYzhjYmMzOjU3MDE2</t>
+          <t>NWM5YzAxYzktMTIwMS00ZjhkLWJjOGMtN2U3NDlmOTlmMzRkOjU3MDE2</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>2073</v>
+        <v>85</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
@@ -4001,11 +4005,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2073</v>
+        <v>85</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4021,31 +4025,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MDhmZjQ1YWQtNTY2Yi00YTlkLWIyMWEtZDI5Y2RkYThlODAwOjU3MDE2</t>
+          <t>NjRmMDVhODItNmU2Mi00ZDRhLTk5NmItNzM2ODI0YjE2MjRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>1365</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>1365</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4054,38 +4058,38 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>N2EyYTQzZjktNzgxZi00Mzk2LWEyNzMtODM0NmViMTE4MWE2OjU3MDE2</t>
+          <t>OGUzMjVkZDYtOTA3Yi00MjFjLWFjYzgtOWVlMGI3MjJkNjIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4094,78 +4098,78 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OWIyYjYwOTktYTg5MC00ZjRhLWEzOGMtNDI3YTE2MTA1NTI1OjU3MDE2</t>
+          <t>Yjk2YzIwMDktMzVkMy00ZGRjLWIwOTYtOTJjOWFlMjZiM2FhOjU3MDE2</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>700</v>
+        <v>375</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>YTJjM2ExNTAtOWExYi00Mzk1LWE1N2MtM2JkYTU3MDBiMzhlOjU3MDE2</t>
+          <t>ZTA0MDdkOTgtNjJjMi00ZTgyLWFmMzEtYzg4MzdkYzhjYmMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>375</v>
+        <v>2073</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>375</v>
+        <v>2073</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -4174,21 +4178,21 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>YTYxMjU3ODEtZjY4ZS00MDQyLTg5YmItYzg1YTA3YTdmZmY5OjU3MDE2</t>
+          <t>MDhmZjQ1YWQtNTY2Yi00YTlkLWIyMWEtZDI5Y2RkYThlODAwOjU3MDE2</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>350</v>
+        <v>9</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
@@ -4201,11 +4205,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>350</v>
+        <v>9</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -4221,14 +4225,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>YTg1ZmQyOGMtNDZkOC00YTgwLWJhODUtOGI5OTA5ZDliZjg1OjU3MDE2</t>
+          <t>N2EyYTQzZjktNzgxZi00Mzk2LWEyNzMtODM0NmViMTE4MWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>8399999999999999</v>
+        <v>85</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
@@ -4241,11 +4245,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>8399999999999999</v>
+        <v>85</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -4261,14 +4265,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>YTlhNDQ1NWItMWI4OS00ZGM0LThiOTgtMzZlOTcxNTE0NzcyOjU3MDE2</t>
+          <t>OWIyYjYwOTktYTg5MC00ZjRhLWEzOGMtNDI3YTE2MTA1NTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>2073</v>
+        <v>700</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
@@ -4281,15 +4285,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4301,14 +4305,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ZTZmYzJiNjEtYzBjNS00NjM2LWI0YmEtNzZlMGE1NWI2ODIwOjU3MDE2</t>
+          <t>YTJjM2ExNTAtOWExYi00Mzk1LWE1N2MtM2JkYTU3MDBiMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>2502</v>
+        <v>375</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
@@ -4321,11 +4325,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2502</v>
+        <v>375</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -4341,14 +4345,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ZWQ1NDY3MTUtZjAxMC00OTM2LTljZDctNzBmMjRlZjVhYTQwOjU3MDE2</t>
+          <t>YTYxMjU3ODEtZjY4ZS00MDQyLTg5YmItYzg1YTA3YTdmZmY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>6325</v>
+        <v>350</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
@@ -4361,11 +4365,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6325</v>
+        <v>350</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4381,31 +4385,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NjA1ZWIxZDMtNWMxMC00NGE2LWEzZjEtYTZkZjM1MWVhNjQwOjU3MDE2</t>
+          <t>YTg1ZmQyOGMtNDZkOC00YTgwLWJhODUtOGI5OTA5ZDliZjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>1793</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NjdjMzI5NDAtMmU1Mi00MjQ1LTgxNGQtNjUyNWI3ZTQyNDU4OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1793</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4414,82 +4418,78 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OTFkMjc2ZDEtOTkxOC00OGZlLWEyMWYtZGEwNDg3MDFiNzkxOjU3MDE2</t>
+          <t>YTlhNDQ1NWItMWI4OS00ZGM0LThiOTgtMzZlOTcxNTE0NzcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>350</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>2073</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>350</v>
+        <v>2073</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>YTlhMGVhYzMtYjJhZS00OWUwLTg5YWQtNjdjYzIyMWUyZDZmOjU3MDE2</t>
+          <t>ZTZmYzJiNjEtYzBjNS00NjM2LWI0YmEtNzZlMGE1NWI2ODIwOjU3MDE2</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>2841</v>
+        <v>2502</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MGQ3YTYzZmEtOGQyZS00YWNiLTljMWYtNTNiM2JkMzRmOTYwOjU3MDE2</t>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2841</v>
+        <v>2502</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4498,38 +4498,38 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MjA0Mzk0M2ItOWI2Ni00Y2NkLWJlNjgtOTUwNjdmMjVkM2Y3OjU3MDE2</t>
+          <t>ZWQ1NDY3MTUtZjAxMC00OTM2LTljZDctNzBmMjRlZjVhYTQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>350</v>
+        <v>6325</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>350</v>
+        <v>6325</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4538,38 +4538,38 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NDUwYmZhOGUtMTA3Ni00MmY2LWFhMjgtNWY5YzNmNzMzMWQ1OjU3MDE2</t>
+          <t>NjA1ZWIxZDMtNWMxMC00NGE2LWEzZjEtYTZkZjM1MWVhNjQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>18025</v>
+        <v>1793</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>NjdjMzI5NDAtMmU1Mi00MjQ1LTgxNGQtNjUyNWI3ZTQyNDU4OjU3MDE2</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>18025</v>
+        <v>1793</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4578,23 +4578,187 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>OTFkMjc2ZDEtOTkxOC00OGZlLWEyMWYtZGEwNDg3MDFiNzkxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>350</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>350</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>YTlhMGVhYzMtYjJhZS00OWUwLTg5YWQtNjdjYzIyMWUyZDZmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2841</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>MGQ3YTYzZmEtOGQyZS00YWNiLTljMWYtNTNiM2JkMzRmOTYwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>2841</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MjA0Mzk0M2ItOWI2Ni00Y2NkLWJlNjgtOTUwNjdmMjVkM2Y3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>350</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>350</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NDUwYmZhOGUtMTA3Ni00MmY2LWFhMjgtNWY5YzNmNzMzMWQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>18025</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>18025</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
         <v>1700</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -4602,126 +4766,126 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E47" t="n">
         <v>2</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="H47" t="n">
         <v>1700</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="n">
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
         <v>47370</v>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="n">
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
         <v>2</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="H48" t="n">
         <v>47370</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="n">
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
         <v>1050</v>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="n">
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
         <v>3</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="H49" t="n">
         <v>1050</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="n">
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
         <v>494677</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -4739,204 +4903,44 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E50" t="n">
         <v>3</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="H50" t="n">
         <v>494677</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="n">
-        <v>350</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="n">
-        <v>6</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>350</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="n">
-        <v>6</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>2073</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="n">
-        <v>7375</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="n">
-        <v>6</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>7375</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="n">
-        <v>6</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
@@ -4949,15 +4953,15 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4969,119 +4973,111 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>680</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>2073</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>680</v>
+        <v>2073</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>855</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>7375</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>855</v>
+        <v>7375</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>43</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>43</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5090,38 +5086,38 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -5130,210 +5126,206 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>350</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>350</v>
+        <v>680</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>10000</v>
+        <v>855</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>10000</v>
+        <v>855</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>680</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>680</v>
+        <v>43</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>855</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>855</v>
+        <v>85</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>96</v>
+        <v>350</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>48</v>
+        <v>350</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5342,38 +5334,42 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>6000000000000001</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+        </is>
+      </c>
       <c r="E61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6000000000000001</v>
+        <v>10000</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5382,101 +5378,109 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>3.8825e+16</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.8825e+16</v>
+        <v>680</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>2.1e+16</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2.1e+16</v>
+        <v>855</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>3e+16</v>
+        <v>96</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
@@ -5489,11 +5493,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>3e+16</v>
+        <v>48</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5509,75 +5513,71 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>47370</v>
+        <v>6000000000000001</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>47370</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
-        </is>
-      </c>
+        <v>3.8825e+16</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>3.8825e+16</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5586,23 +5586,187 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" t="n">
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
         <v>1700</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -5610,46 +5774,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E71" t="n">
         <v>2</v>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H67" t="n">
+      <c r="H71" t="n">
         <v>1700</v>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" t="n">
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
         <v>494677</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -5667,233 +5831,61 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E68" t="n">
+      <c r="E72" t="n">
         <v>3</v>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H68" t="n">
+      <c r="H72" t="n">
         <v>494677</v>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="n">
-        <v>3</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" t="n">
-        <v>3.2215e+16</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="n">
-        <v>5</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>3.2215e+16</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" t="n">
-        <v>823</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>310Km</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>5</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>2</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" t="n">
-        <v>70</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Enviado por Sedex10 de SP para DF</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>5</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>43</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>908</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>1050</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>350</v>
+        <v>1050</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5902,38 +5894,38 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
+          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>6000000000000001</v>
+        <v>3.2215e+16</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>6000000000000001</v>
+        <v>3.2215e+16</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5942,78 +5934,86 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MTE2ZmIzMDUtYWVlNC00N2M1LWI2YWEtYmQ4ZmZmNDMyY2M5OjU3MDE2</t>
+          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
+        <v>823</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>310Km</t>
+        </is>
+      </c>
       <c r="E75" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>8399999999999999</v>
+        <v>2</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>M2E2MGI3YzMtNmIxZi00NGM4LWEyMzctNWUyNzcxODM0ZWM5OjU3MDE2</t>
+          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>117</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Enviado por Sedex10 de SP para DF</t>
+        </is>
+      </c>
       <c r="E76" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6022,61 +6022,65 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NGI5MDNkYWQtNzdhZC00NTM4LTgxNGItNzE4NDRjZWNlYmYxOjU3MDE2</t>
+          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>9000000000000001</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
+        <v>908</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E77" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>3e+16</v>
+        <v>350</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NTM1MTUxMDQtZGQxYi00ODQ4LWE2YmYtNGZkNDgxY2RlOWU2OjU3MDE2</t>
+          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>825</v>
+        <v>6000000000000001</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
@@ -6089,11 +6093,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>OTUzMmM4MTUtMjYxYy00ZjI2LThkMDAtMjc0MzkyYjRjYjY2OjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>825</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6109,14 +6113,14 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NTQ5YjVkYWItMzYyOS00ODg5LWIwOWEtODVjZDhlMWY3N2FkOjU3MDE2</t>
+          <t>MTE2ZmIzMDUtYWVlNC00N2M1LWI2YWEtYmQ4ZmZmNDMyY2M5OjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>717</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
@@ -6129,11 +6133,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>717</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6149,14 +6153,14 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NWE2NzVhZjgtYTQ5OC00NjgxLTkxNmYtNzc4YWZhMjZjZTNlOjU3MDE2</t>
+          <t>M2E2MGI3YzMtNmIxZi00NGM4LWEyMzctNWUyNzcxODM0ZWM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>7375</v>
+        <v>117</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
@@ -6169,11 +6173,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>7375</v>
+        <v>117</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -6189,14 +6193,14 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NjM4Y2JlY2EtMTNjZS00ZmRkLWJjMTQtZTU2OTZkMGE1NTM2OjU3MDE2</t>
+          <t>NGI5MDNkYWQtNzdhZC00NTM4LTgxNGItNzE4NDRjZWNlYmYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>96</v>
+        <v>9000000000000001</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
@@ -6209,11 +6213,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>48</v>
+        <v>3e+16</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6229,20 +6233,16 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>N2I3ZTkxNTUtMWY0NC00MjhhLWIxZDctYWMxZTFhZWYxOGYxOjU3MDE2</t>
+          <t>NTM1MTUxMDQtZGQxYi00ODQ4LWE2YmYtNGZkNDgxY2RlOWU2OjU3MDE2</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>43</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Troca do Balde via correio</t>
-        </is>
-      </c>
+        <v>825</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
         <v>16</v>
       </c>
@@ -6253,11 +6253,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>OTUzMmM4MTUtMjYxYy00ZjI2LThkMDAtMjc0MzkyYjRjYjY2OjU3MDE2</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>43</v>
+        <v>825</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -6273,14 +6273,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>YTdmOGYzMDctZDg5ZS00MGYyLWFkMzAtMTEzNzkzNmI5MjZmOjU3MDE2</t>
+          <t>NTQ5YjVkYWItMzYyOS00ODg5LWIwOWEtODVjZDhlMWY3N2FkOjU3MDE2</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>3.33e+16</v>
+        <v>717</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
@@ -6293,11 +6293,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ODEwYWQzODUtY2JhYy00NmM5LWE5M2UtYzQ1MDMyY2JmZjNlOjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1.11e+16</v>
+        <v>717</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6313,14 +6313,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>YWVhMDUwNDEtMWZjMy00MGY0LTliMjEtZmQ0Njc2ZmYxMmRiOjU3MDE2</t>
+          <t>NWE2NzVhZjgtYTQ5OC00NjgxLTkxNmYtNzc4YWZhMjZjZTNlOjU3MDE2</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>2525</v>
+        <v>7375</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
@@ -6333,11 +6333,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>YTI5MDAxYjctNzYxNS00Yzc0LTk1MWItYWJjMDg5NWJiN2QzOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>2525</v>
+        <v>7375</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6353,14 +6353,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>YzczZTA5NTktMzAzNS00NWE1LWJiYWUtNWQ5YWYzOTcwOTYwOjU3MDE2</t>
+          <t>NjM4Y2JlY2EtMTNjZS00ZmRkLWJjMTQtZTU2OTZkMGE1NTM2OjU3MDE2</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>1.89e+16</v>
+        <v>96</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
@@ -6373,11 +6373,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>2.1e+16</v>
+        <v>48</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6393,16 +6393,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ZDk0OTlmM2UtNGFlYy00MzM3LWFiY2UtYzRmMjBhYjFiN2ZiOjU3MDE2</t>
+          <t>N2I3ZTkxNTUtMWY0NC00MjhhLWIxZDctYWMxZTFhZWYxOGYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>6449999999999999</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Troca do Balde via correio</t>
+        </is>
+      </c>
       <c r="E86" t="n">
         <v>16</v>
       </c>
@@ -6413,11 +6417,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>6449999999999999</v>
+        <v>43</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6433,14 +6437,14 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ZDk1OWFkMjYtZGJkZi00OWRkLWI5ZTktMjJiOTZlN2VlYzBkOjU3MDE2</t>
+          <t>YTdmOGYzMDctZDg5ZS00MGYyLWFkMzAtMTEzNzkzNmI5MjZmOjU3MDE2</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>3</v>
       </c>
       <c r="C87" t="n">
-        <v>1.26e+16</v>
+        <v>3.33e+16</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
@@ -6453,11 +6457,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+          <t>ODEwYWQzODUtY2JhYy00NmM5LWE5M2UtYzQ1MDMyY2JmZjNlOjU3MDE2</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>4.2e+16</v>
+        <v>1.11e+16</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6473,14 +6477,14 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ZTk0MDQ3MTktYzcwMy00ZTU5LTg5MjMtOGU3MDllYTg0MjAyOjU3MDE2</t>
+          <t>YWVhMDUwNDEtMWZjMy00MGY0LTliMjEtZmQ0Njc2ZmYxMmRiOjU3MDE2</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>1725</v>
+        <v>2525</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
@@ -6493,11 +6497,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+          <t>YTI5MDAxYjctNzYxNS00Yzc0LTk1MWItYWJjMDg5NWJiN2QzOjU3MDE2</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1725</v>
+        <v>2525</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6513,31 +6517,31 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
+          <t>YzczZTA5NTktMzAzNS00NWE1LWJiYWUtNWQ5YWYzOTcwOTYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C89" t="n">
-        <v>99</v>
+        <v>1.89e+16</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>33</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -6546,38 +6550,38 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
+          <t>ZDk0OTlmM2UtNGFlYy00MzM3LWFiY2UtYzRmMjBhYjFiN2ZiOjU3MDE2</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>38656</v>
+        <v>6449999999999999</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
+          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>6449999999999999</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -6586,38 +6590,38 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
+          <t>ZDk1OWFkMjYtZGJkZi00OWRkLWI5ZTktMjJiOTZlN2VlYzBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C91" t="n">
-        <v>350</v>
+        <v>1.26e+16</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>350</v>
+        <v>4.2e+16</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6626,38 +6630,38 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
+          <t>ZTk0MDQ3MTktYzcwMy00ZTU5LTg5MjMtOGU3MDllYTg0MjAyOjU3MDE2</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>85</v>
+        <v>1725</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>85</v>
+        <v>1725</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6666,21 +6670,21 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
+          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93" t="n">
-        <v>350</v>
+        <v>99</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
@@ -6693,15 +6697,15 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>350</v>
+        <v>33</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6713,31 +6717,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
+          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>1086</v>
+        <v>38656</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1086</v>
+        <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -6746,14 +6750,14 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
+          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -6764,11 +6768,11 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6786,38 +6790,38 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
+          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>4050000000000001</v>
+        <v>85</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>4050000000000001</v>
+        <v>85</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6826,61 +6830,61 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
+          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>3795</v>
+        <v>350</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>3795</v>
+        <v>350</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ODg5MGUyMTItOTI1MC00OTY0LWE1ODItODZjOWQ0M2RmYzQwOjU3MDE2</t>
+          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>350</v>
+        <v>1086</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
@@ -6893,15 +6897,15 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>350</v>
+        <v>1086</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6913,14 +6917,14 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>YTVhMDdmMzQtMzFmZi00Y2ExLThlZTctODU2N2EwYzFjNGQ4OjU3MDE2</t>
+          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
@@ -6933,11 +6937,11 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6953,14 +6957,14 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>YTcwZWEzNDAtMDc4MC00ZGYzLWIxZjItMWY3ZmQ1MTJkOGEyOjU3MDE2</t>
+          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>1.68e+16</v>
+        <v>4050000000000001</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
@@ -6973,11 +6977,11 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>2.1e+16</v>
+        <v>4050000000000001</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6993,31 +6997,31 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MzA4MjgxOWUtMzhjMi00NjI1LTllYjctZDU2ZjU3ZTM0YjQ1OjU3MDE2</t>
+          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>6000000000000001</v>
+        <v>3795</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>6000000000000001</v>
+        <v>3795</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7026,7 +7030,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>ZTlkZTdiYTAtMzg2YS00NjRkLTg1ODEtYTg3OTgwMDFhZDc4OjU3MDE2</t>
+          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -1971,22 +1971,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>BJ0FAVCKBL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>MAQUINA 01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>Autorizado por João</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1995,46 +1995,42 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2025-11-13T15:27:58.539Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>rffccfc</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
-        </is>
-      </c>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>2025-11-06T15:28:06.348Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2052,67 +2048,79 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BKMVCD56XX</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-10-20T12:54:09.917Z</t>
+          <t>2025-09-04T16:07:52.834Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-10-13T13:10:02.576Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2133,75 +2141,67 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>NDgyNTIyNjo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>BKMVCD56XX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Substituição de 3 compressores</t>
-        </is>
-      </c>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
+          <t>2025-10-20T12:54:09.917Z</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-10-13T13:10:02.576Z</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2222,74 +2222,78 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2307,32 +2311,117 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2340,7 +2429,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2348,106 +2437,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2470,10 +2470,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2491,7 +2495,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2503,22 +2507,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SYSJ0HARXL</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
+          <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -2527,12 +2531,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2542,20 +2546,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-04T13:33:37.491Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-10-28T14:06:21.222Z</t>
+          <t>2025-09-08T21:59:15.256Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2576,7 +2580,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>NDgyMTM3Mjo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2588,22 +2592,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SJH_RHL1BL</t>
+          <t>BKODRN5YZX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
+          <t>MAQUINA 03</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+          <t>Autorizado por João</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -2612,46 +2616,42 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>511.65999999999997</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>511.65999999999997</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-10T14:43:09.194Z</t>
+          <t>2025-11-13T15:27:36.746Z</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Viktor Chagas</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-11-03T15:08:36.141Z</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>2025-11-06T15:27:46.917Z</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2669,44 +2669,48 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>MzkzMzA3Mjo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SK1FN_56XX</t>
+          <t>SYSJ0HARXL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>34875175825 - FERNANDA FIGUEIRA DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>2123.15</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1172.55</t>
+          <t>2123.15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2716,27 +2720,23 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-10-20T12:26:24.223Z</t>
+          <t>2025-11-04T13:33:37.491Z</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2025-10-13T12:45:43.188Z</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>MjkyMTJlNzYtODY0OC00NTBhLTg0OTUtOThlZGQ5YzM1MDdiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-10-28T14:06:21.222Z</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>MzQ2NDM2Nzo1NzAxNg==</t>
+          <t>NDgyMTM3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -2766,70 +2766,70 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H16WCCZPEG</t>
+          <t>SJH_RHL1BL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
+          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
-        </is>
-      </c>
+          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>511.65999999999997</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>511.65999999999997</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-10-14T18:12:15.015Z</t>
+          <t>2025-11-10T14:43:09.194Z</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Viktor Chagas</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-10-07T18:22:28.553Z</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-11-03T15:08:36.141Z</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>MzkzMzA3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5385,119 +5385,111 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>680</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>680</v>
+        <v>9</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>855</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>6325</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>855</v>
+        <v>6325</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>96</v>
+        <v>375</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>48</v>
+        <v>375</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5506,38 +5498,38 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>6000000000000001</v>
+        <v>350</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>6000000000000001</v>
+        <v>350</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5546,38 +5538,38 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>3.8825e+16</v>
+        <v>2502</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>3.8825e+16</v>
+        <v>2502</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5586,38 +5578,38 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>2.1e+16</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.1e+16</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5626,38 +5618,38 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>3e+16</v>
+        <v>2073</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>3e+16</v>
+        <v>2073</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5666,107 +5658,475 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>47370</v>
+        <v>85</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>47370</v>
+        <v>85</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
-        </is>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>350</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>680</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>680</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>855</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>855</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" t="n">
+        <v>96</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>48</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>6</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>6</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" t="n">
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="n">
         <v>1700</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -5774,46 +6134,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="E80" t="n">
         <v>2</v>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H71" t="n">
+      <c r="H80" t="n">
         <v>1700</v>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" t="n">
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
         <v>494677</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -5831,473 +6191,101 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E72" t="n">
+      <c r="E81" t="n">
         <v>3</v>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H72" t="n">
+      <c r="H81" t="n">
         <v>494677</v>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="n">
-        <v>3</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>1</v>
-      </c>
-      <c r="C74" t="n">
-        <v>3.2215e+16</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="n">
-        <v>5</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>3.2215e+16</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>1</v>
-      </c>
-      <c r="C75" t="n">
-        <v>823</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>310Km</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>5</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>2</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C76" t="n">
-        <v>70</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Enviado por Sedex10 de SP para DF</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>5</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>43</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" t="n">
-        <v>908</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>5</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>350</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>1</v>
-      </c>
-      <c r="C78" t="n">
-        <v>6000000000000001</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="n">
-        <v>16</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>6000000000000001</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>MTE2ZmIzMDUtYWVlNC00N2M1LWI2YWEtYmQ4ZmZmNDMyY2M5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="n">
-        <v>16</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>M2E2MGI3YzMtNmIxZi00NGM4LWEyMzctNWUyNzcxODM0ZWM5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>1</v>
-      </c>
-      <c r="C80" t="n">
-        <v>117</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="n">
-        <v>16</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>117</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>NGI5MDNkYWQtNzdhZC00NTM4LTgxNGItNzE4NDRjZWNlYmYxOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>3</v>
-      </c>
-      <c r="C81" t="n">
-        <v>9000000000000001</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="n">
-        <v>16</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>3e+16</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NTM1MTUxMDQtZGQxYi00ODQ4LWE2YmYtNGZkNDgxY2RlOWU2OjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>825</v>
+        <v>1050</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>OTUzMmM4MTUtMjYxYy00ZjI2LThkMDAtMjc0MzkyYjRjYjY2OjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>825</v>
+        <v>1050</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NTQ5YjVkYWItMzYyOS00ODg5LWIwOWEtODVjZDhlMWY3N2FkOjU3MDE2</t>
+          <t>NTdmZWE4N2QtMTU1Zi00OWNhLWJlMTItOGM0NDlhOGEzM2I0OjU3MDE2</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>717</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>717</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6306,38 +6294,38 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NWE2NzVhZjgtYTQ5OC00NjgxLTkxNmYtNzc4YWZhMjZjZTNlOjU3MDE2</t>
+          <t>NjdlODg4ZTMtZThiOC00MjM3LWE4ZGUtNjk4MWVlYzhiZDk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>7375</v>
+        <v>375</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>7375</v>
+        <v>375</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6346,38 +6334,38 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NjM4Y2JlY2EtMTNjZS00ZmRkLWJjMTQtZTU2OTZkMGE1NTM2OjU3MDE2</t>
+          <t>ODI1NWRlYjYtYTg0Yy00ZDhlLTk0MmEtZjNkYWEzZWYyYTVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>96</v>
+        <v>7375</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>48</v>
+        <v>7375</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6386,82 +6374,78 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>N2I3ZTkxNTUtMWY0NC00MjhhLWIxZDctYWMxZTFhZWYxOGYxOjU3MDE2</t>
+          <t>YjljMTRhODUtYzlmZC00ZjBhLWExZjMtYmExMTY2YzMzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>43</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Troca do Balde via correio</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>43</v>
+        <v>350</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>YTdmOGYzMDctZDg5ZS00MGYyLWFkMzAtMTEzNzkzNmI5MjZmOjU3MDE2</t>
+          <t>ZWM2ZTEzNTktN2U5My00MjJiLWEwNmYtZmQ3ZTIxNTg1ZWNhOjU3MDE2</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>3.33e+16</v>
+        <v>2073</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ODEwYWQzODUtY2JhYy00NmM5LWE5M2UtYzQ1MDMyY2JmZjNlOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1.11e+16</v>
+        <v>2073</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6470,38 +6454,38 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>YWVhMDUwNDEtMWZjMy00MGY0LTliMjEtZmQ0Njc2ZmYxMmRiOjU3MDE2</t>
+          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>2525</v>
+        <v>3.2215e+16</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>YTI5MDAxYjctNzYxNS00Yzc0LTk1MWItYWJjMDg5NWJiN2QzOjU3MDE2</t>
+          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>2525</v>
+        <v>3.2215e+16</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6510,78 +6494,86 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>YzczZTA5NTktMzAzNS00NWE1LWJiYWUtNWQ5YWYzOTcwOTYwOjU3MDE2</t>
+          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>1.89e+16</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
+        <v>823</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>310Km</t>
+        </is>
+      </c>
       <c r="E89" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>2.1e+16</v>
+        <v>2</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ZDk0OTlmM2UtNGFlYy00MzM3LWFiY2UtYzRmMjBhYjFiN2ZiOjU3MDE2</t>
+          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>6449999999999999</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Enviado por Sedex10 de SP para DF</t>
+        </is>
+      </c>
       <c r="E90" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MGFmNjg5ODYtODc1ZC00YmFjLWE1MDgtMTE3YWU5MjExMzVkOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>6449999999999999</v>
+        <v>43</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -6590,61 +6582,65 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ZDk1OWFkMjYtZGJkZi00OWRkLWI5ZTktMjJiOTZlN2VlYzBkOjU3MDE2</t>
+          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>1.26e+16</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
+        <v>908</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E91" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>NGRmZWRlNWQtYjFlNi00N2Q2LTkxZDItMDBmZjM2MzVhMTUxOjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>4.2e+16</v>
+        <v>350</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ZTk0MDQ3MTktYzcwMy00ZTU5LTg5MjMtOGU3MDllYTg0MjAyOjU3MDE2</t>
+          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>1725</v>
+        <v>6000000000000001</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
@@ -6657,11 +6653,11 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ODJmMjkxYjEtMDdiOC00YjFiLWEyZmMtMjExYjg2YjIwYjgyOjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1725</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6677,31 +6673,31 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MWFlZWU2YmYtYzRkNS00ZmUyLWI4YzYtZmUwZmUwNTA4NmFlOjU3MDE2</t>
+          <t>MTE2ZmIzMDUtYWVlNC00N2M1LWI2YWEtYmQ4ZmZmNDMyY2M5OjU3MDE2</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>99</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>NWQ0NDE1MTgtNmExOS00ZTg0LWI1OTYtYjI1NWJjYjM3OTcxOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>33</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6710,38 +6706,38 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MjgyNTVkNDktZWZiOS00YzIyLTg2MmItNzBhNWJjMjBjZGYwOjU3MDE2</t>
+          <t>M2E2MGI3YzMtNmIxZi00NGM4LWEyMzctNWUyNzcxODM0ZWM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>38656</v>
+        <v>117</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MGI1NzMzYTAtNWFhNC00MGJhLWE2ZTgtNzUzYWExYTUyMzhiOjU3MDE2</t>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -6750,38 +6746,38 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NTFlY2QyY2MtN2EwNy00MDY5LWIwZmYtYWNlNzE3ODA2MWMzOjU3MDE2</t>
+          <t>NGI5MDNkYWQtNzdhZC00NTM4LTgxNGItNzE4NDRjZWNlYmYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95" t="n">
-        <v>350</v>
+        <v>9000000000000001</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>350</v>
+        <v>3e+16</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -6790,38 +6786,38 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NjQyN2Y0NDYtM2JiMi00YjczLWI3YjYtOTEyNWJkZTdjMmFhOjU3MDE2</t>
+          <t>NTM1MTUxMDQtZGQxYi00ODQ4LWE2YmYtNGZkNDgxY2RlOWU2OjU3MDE2</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>85</v>
+        <v>825</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>OTUzMmM4MTUtMjYxYy00ZjI2LThkMDAtMjc0MzkyYjRjYjY2OjU3MDE2</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>85</v>
+        <v>825</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6830,78 +6826,78 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OTVlMDFhMGEtZGQ2NC00OWM5LWE1OGYtYjY1YjQ3NGNjMTk1OjU3MDE2</t>
+          <t>NTQ5YjVkYWItMzYyOS00ODg5LWIwOWEtODVjZDhlMWY3N2FkOjU3MDE2</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>350</v>
+        <v>717</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>350</v>
+        <v>717</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>ZTNkOTJlYTUtYjVkZC00YjFhLWFkNjMtZGU2ODIyMDYxOTY5OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NTdmNTJiMjAtNjUzMy00ZTg1LTg2NDQtMGUxYmNiMzQzODcxOjU3MDE2</t>
+          <t>NWE2NzVhZjgtYTQ5OC00NjgxLTkxNmYtNzc4YWZhMjZjZTNlOjU3MDE2</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>1086</v>
+        <v>7375</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1086</v>
+        <v>7375</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6910,38 +6906,38 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NmMyNmYyM2EtMDI5ZS00NjYzLWIzODYtZjA2YWUxMjMzMjY3OjU3MDE2</t>
+          <t>NjM4Y2JlY2EtMTNjZS00ZmRkLWJjMTQtZTU2OTZkMGE1NTM2OjU3MDE2</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>350</v>
+        <v>96</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>350</v>
+        <v>48</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6950,38 +6946,42 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>N2I0N2YwNGQtMjg2ZC00NTJlLTliMTUtMzc4ZDYwNDZjNmRjOjU3MDE2</t>
+          <t>N2I3ZTkxNTUtMWY0NC00MjhhLWIxZDctYWMxZTFhZWYxOGYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>4050000000000001</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Troca do Balde via correio</t>
+        </is>
+      </c>
       <c r="E100" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>4050000000000001</v>
+        <v>43</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6990,38 +6990,38 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ODQ1NjM4ZTUtZWFlZi00MGE2LWFlNTMtZTkyMzMzZDRiMjJmOjU3MDE2</t>
+          <t>YTdmOGYzMDctZDg5ZS00MGYyLWFkMzAtMTEzNzkzNmI5MjZmOjU3MDE2</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C101" t="n">
-        <v>3795</v>
+        <v>3.33e+16</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+          <t>ODEwYWQzODUtY2JhYy00NmM5LWE5M2UtYzQ1MDMyY2JmZjNlOjU3MDE2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>3795</v>
+        <v>1.11e+16</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>ZTVhYzhjYzQtMjFjNi00MjA4LTkwYTktNjk5ODViNzI5MWE0OjU3MDE2</t>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,50 +1247,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BYCZRKIPEL</t>
+          <t>SY9I6QSJBE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>62730134620 - FRANCISCO DE LUCCA JUNIOR</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>GARANTIA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>garantia</t>
-        </is>
-      </c>
+          <t>45246402000532 - CENTER NORTE S/A CONSTRUCA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="b">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>660.525</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>660.525</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-10-17T12:48:39.389Z</t>
+          <t>2025-11-14T16:10:10.258Z</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1303,12 +1295,12 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-10-10T13:07:18.487Z</t>
+          <t>2025-11-07T16:26:09.914Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
+          <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1328,32 +1320,125 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NDgyMzMyODo1NzAxNg==</t>
+          <t>NDE3MTYzNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BYCZRKIPEL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>62730134620 - FRANCISCO DE LUCCA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GARANTIA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>garantia</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>530.25</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>530.25</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2025-10-17T12:48:39.389Z</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-10T13:07:18.487Z</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>NDgyMzMyODo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1362,7 +1447,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1371,106 +1456,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1480,20 +1476,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
+          <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1514,7 +1510,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1526,36 +1522,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SJBLZ0HQLG</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OUTBACK MORUMBI</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1565,27 +1565,23 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:27:17.728Z</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1603,7 +1599,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1615,32 +1611,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1663,12 +1663,12 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
+          <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1700,40 +1700,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1743,7 +1735,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1756,10 +1748,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1777,7 +1773,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1789,46 +1785,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R1R8PTIYBL</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>orçamento</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-11-10T19:48:40.136Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1841,14 +1841,10 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2025-11-03T19:49:41.839Z</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-28T16:05:56.490Z</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1866,82 +1862,78 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NDgyMzkyMzo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>R1R8PTIYBL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>orçamento</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-11-10T19:48:40.136Z</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+          <t>2025-11-03T19:49:41.839Z</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1949,88 +1941,92 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDgyMzkyMzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BJ0FAVCKBL</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Autorizado por João</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:58.539Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>jose da silva</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>HENRIQUE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-11-06T15:28:06.348Z</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2023-05-31T21:56:50.448Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2038,44 +2034,44 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>BJ0FAVCKBL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>MAQUINA 01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>Autorizado por João</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -2084,46 +2080,42 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2025-11-13T15:27:58.539Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>rffccfc</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
-        </is>
-      </c>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>2025-11-06T15:28:06.348Z</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2141,67 +2133,79 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BKMVCD56XX</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-10-20T12:54:09.917Z</t>
+          <t>2025-09-04T16:07:52.834Z</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-10-13T13:10:02.576Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2222,75 +2226,67 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>NDgyNTIyNjo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>BKMVCD56XX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Substituição de 3 compressores</t>
-        </is>
-      </c>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
+          <t>2025-10-20T12:54:09.917Z</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-10-13T13:10:02.576Z</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2311,74 +2307,78 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2396,32 +2396,117 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2429,7 +2514,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2437,106 +2522,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2546,7 +2542,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -2559,10 +2555,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2592,22 +2592,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BKODRN5YZX</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Autorizado por João</t>
+          <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -2616,42 +2616,38 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:36.746Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-11-06T15:27:46.917Z</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-09-08T21:59:15.256Z</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2669,34 +2665,34 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SYSJ0HARXL</t>
+          <t>BKODRN5YZX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
+          <t>MAQUINA 03</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
+          <t>Autorizado por João</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -2705,22 +2701,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-11-04T13:33:37.491Z</t>
+          <t>2025-11-13T15:27:36.746Z</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2733,10 +2729,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2025-10-28T14:06:21.222Z</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
+          <t>2025-11-06T15:27:46.917Z</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2754,34 +2754,34 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>NDgyMTM3Mjo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SJH_RHL1BL</t>
+          <t>SYSJ0HARXL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
+          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -2790,43 +2790,35 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>511.65999999999997</t>
+          <t>2123.15</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>511.65999999999997</t>
+          <t>2123.15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-10T14:43:09.194Z</t>
+          <t>2025-11-04T13:33:37.491Z</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Viktor Chagas</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-11-03T15:08:36.141Z</t>
+          <t>2025-10-28T14:06:21.222Z</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2847,10 +2839,103 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
+          <t>NDgyMTM3Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SJH_RHL1BL</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>511.65999999999997</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>511.65999999999997</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Aprovada</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2025-11-10T14:43:09.194Z</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Viktor Chagas</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2025-11-03T15:08:36.141Z</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>MzkzMzA3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -4669,31 +4754,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MjA0Mzk0M2ItOWI2Ni00Y2NkLWJlNjgtOTUwNjdmMjVkM2Y3OjU3MDE2</t>
+          <t>YmUzOThhOTAtNGYyYi00YmViLWJmYzUtNDJmYTA2NDg0OGRhOjU3MDE2</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>350</v>
+        <v>660525</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MGY5YWI3Y2UtNWJiMC00ZWMwLTgyZjktNzU4Zjc0YmUyZDg3OjU3MDE2</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>350</v>
+        <v>660525</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4702,21 +4787,21 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NDUwYmZhOGUtMTA3Ni00MmY2LWFhMjgtNWY5YzNmNzMzMWQ1OjU3MDE2</t>
+          <t>MjA0Mzk0M2ItOWI2Ni00Y2NkLWJlNjgtOTUwNjdmMjVkM2Y3OjU3MDE2</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
@@ -4729,11 +4814,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4749,16 +4834,56 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>NDUwYmZhOGUtMTA3Ni00MmY2LWFhMjgtNWY5YzNmNzMzMWQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>18025</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>18025</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="n">
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
         <v>1700</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -4766,61 +4891,21 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>1700</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
         <v>2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+          <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>47370</v>
+        <v>1700</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4829,38 +4914,38 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+          <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
+          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>1050</v>
+        <v>47370</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1050</v>
+        <v>47370</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4869,23 +4954,63 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="n">
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
         <v>494677</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -4903,84 +5028,44 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="E51" t="n">
         <v>3</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="H51" t="n">
         <v>494677</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="n">
-        <v>350</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="n">
-        <v>6</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>350</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
@@ -4993,15 +5078,15 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5013,14 +5098,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>7375</v>
+        <v>2073</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
@@ -5033,11 +5118,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>7375</v>
+        <v>2073</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5053,14 +5138,14 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>8399999999999999</v>
+        <v>7375</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
@@ -5073,11 +5158,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>8399999999999999</v>
+        <v>7375</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5093,14 +5178,14 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>375</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
@@ -5113,11 +5198,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>375</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -5133,62 +5218,58 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>680</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>680</v>
+        <v>375</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -5201,11 +5282,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -5221,54 +5302,58 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>43</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>43</v>
+        <v>855</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
+          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
@@ -5281,11 +5366,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -5301,14 +5386,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
+          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
@@ -5321,11 +5406,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5341,35 +5426,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>10000</v>
+        <v>350</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5378,38 +5459,42 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+        </is>
+      </c>
       <c r="E62" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>9</v>
+        <v>10000</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5418,21 +5503,21 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
+          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>6325</v>
+        <v>9</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
@@ -5445,11 +5530,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>6325</v>
+        <v>9</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5465,14 +5550,14 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
+          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>375</v>
+        <v>6325</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
@@ -5485,11 +5570,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>375</v>
+        <v>6325</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5505,14 +5590,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
+          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
@@ -5525,11 +5610,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5545,14 +5630,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
+          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>2502</v>
+        <v>350</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
@@ -5565,11 +5650,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2502</v>
+        <v>350</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5585,14 +5670,14 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
+          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>8399999999999999</v>
+        <v>2502</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
@@ -5605,11 +5690,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>8399999999999999</v>
+        <v>2502</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5625,14 +5710,14 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
+          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>2073</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
@@ -5645,11 +5730,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>2073</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5665,14 +5750,14 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
+          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
@@ -5685,11 +5770,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5705,14 +5790,14 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
+          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
@@ -5725,15 +5810,15 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5745,35 +5830,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="n">
-        <v>680</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>680</v>
+        <v>350</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5782,25 +5863,25 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -5813,11 +5894,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5833,54 +5914,58 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>96</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>48</v>
+        <v>855</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>6000000000000001</v>
+        <v>96</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
@@ -5893,11 +5978,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>6000000000000001</v>
+        <v>48</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5913,14 +5998,14 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>3.8825e+16</v>
+        <v>6000000000000001</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
@@ -5933,11 +6018,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>3.8825e+16</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5953,14 +6038,14 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>2.1e+16</v>
+        <v>3.8825e+16</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
@@ -5973,11 +6058,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>2.1e+16</v>
+        <v>3.8825e+16</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -5993,14 +6078,14 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>3e+16</v>
+        <v>2.1e+16</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
@@ -6013,11 +6098,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>3e+16</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6033,100 +6118,140 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>47370</v>
+        <v>3e+16</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>47370</v>
+        <v>3e+16</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
-        </is>
-      </c>
+        <v>47370</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
         <v>2</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>47370</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>1</v>
-      </c>
-      <c r="C80" t="n">
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
         <v>1700</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -6134,46 +6259,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E80" t="n">
+      <c r="E81" t="n">
         <v>2</v>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H80" t="n">
+      <c r="H81" t="n">
         <v>1700</v>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" t="n">
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="n">
         <v>494677</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -6191,46 +6316,6 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E81" t="n">
-        <v>3</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>494677</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
         <v>3</v>
       </c>
@@ -6241,15 +6326,15 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+          <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1050</v>
+        <v>494677</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6261,54 +6346,54 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NTdmZWE4N2QtMTU1Zi00OWNhLWJlMTItOGM0NDlhOGEzM2I0OjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>8399999999999999</v>
+        <v>1050</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>8399999999999999</v>
+        <v>1050</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NjdlODg4ZTMtZThiOC00MjM3LWE4ZGUtNjk4MWVlYzhiZDk4OjU3MDE2</t>
+          <t>NTdmZWE4N2QtMTU1Zi00OWNhLWJlMTItOGM0NDlhOGEzM2I0OjU3MDE2</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>375</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
@@ -6321,11 +6406,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>375</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6341,14 +6426,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ODI1NWRlYjYtYTg0Yy00ZDhlLTk0MmEtZjNkYWEzZWYyYTVjOjU3MDE2</t>
+          <t>NjdlODg4ZTMtZThiOC00MjM3LWE4ZGUtNjk4MWVlYzhiZDk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>7375</v>
+        <v>375</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
@@ -6361,11 +6446,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>7375</v>
+        <v>375</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6381,14 +6466,14 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>YjljMTRhODUtYzlmZC00ZjBhLWExZjMtYmExMTY2YzMzZWFiOjU3MDE2</t>
+          <t>ODI1NWRlYjYtYTg0Yy00ZDhlLTk0MmEtZjNkYWEzZWYyYTVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>350</v>
+        <v>7375</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
@@ -6401,15 +6486,15 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>350</v>
+        <v>7375</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -6421,14 +6506,14 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ZWM2ZTEzNTktN2U5My00MjJiLWEwNmYtZmQ3ZTIxNTg1ZWNhOjU3MDE2</t>
+          <t>YjljMTRhODUtYzlmZC00ZjBhLWExZjMtYmExMTY2YzMzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
@@ -6441,15 +6526,15 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6461,31 +6546,31 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
+          <t>ZWM2ZTEzNTktN2U5My00MjJiLWEwNmYtZmQ3ZTIxNTg1ZWNhOjU3MDE2</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>3.2215e+16</v>
+        <v>2073</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>3.2215e+16</v>
+        <v>2073</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6494,27 +6579,23 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
+          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>823</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>310Km</t>
-        </is>
-      </c>
+        <v>3.2215e+16</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
         <v>5</v>
       </c>
@@ -6525,15 +6606,15 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>3.2215e+16</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6545,18 +6626,18 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
+          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>70</v>
+        <v>823</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Enviado por Sedex10 de SP para DF</t>
+          <t>310Km</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -6569,15 +6650,15 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6589,18 +6670,18 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
+          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>908</v>
+        <v>70</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Hora de trabalho ECO</t>
+          <t>Enviado por Sedex10 de SP para DF</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -6613,15 +6694,15 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>350</v>
+        <v>43</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6633,54 +6714,58 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
+          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>6000000000000001</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
+        <v>908</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E92" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>6000000000000001</v>
+        <v>350</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MTE2ZmIzMDUtYWVlNC00N2M1LWI2YWEtYmQ4ZmZmNDMyY2M5OjU3MDE2</t>
+          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>8399999999999999</v>
+        <v>6000000000000001</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
@@ -6693,11 +6778,11 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>8399999999999999</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6713,14 +6798,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>M2E2MGI3YzMtNmIxZi00NGM4LWEyMzctNWUyNzcxODM0ZWM5OjU3MDE2</t>
+          <t>MTE2ZmIzMDUtYWVlNC00N2M1LWI2YWEtYmQ4ZmZmNDMyY2M5OjU3MDE2</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>117</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
@@ -6733,11 +6818,11 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>117</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -6753,14 +6838,14 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NGI5MDNkYWQtNzdhZC00NTM4LTgxNGItNzE4NDRjZWNlYmYxOjU3MDE2</t>
+          <t>M2E2MGI3YzMtNmIxZi00NGM4LWEyMzctNWUyNzcxODM0ZWM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>9000000000000001</v>
+        <v>117</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
@@ -6773,11 +6858,11 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>3e+16</v>
+        <v>117</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -6793,14 +6878,14 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NTM1MTUxMDQtZGQxYi00ODQ4LWE2YmYtNGZkNDgxY2RlOWU2OjU3MDE2</t>
+          <t>NGI5MDNkYWQtNzdhZC00NTM4LTgxNGItNzE4NDRjZWNlYmYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C96" t="n">
-        <v>825</v>
+        <v>9000000000000001</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
@@ -6813,11 +6898,11 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>OTUzMmM4MTUtMjYxYy00ZjI2LThkMDAtMjc0MzkyYjRjYjY2OjU3MDE2</t>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>825</v>
+        <v>3e+16</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6833,14 +6918,14 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NTQ5YjVkYWItMzYyOS00ODg5LWIwOWEtODVjZDhlMWY3N2FkOjU3MDE2</t>
+          <t>NTM1MTUxMDQtZGQxYi00ODQ4LWE2YmYtNGZkNDgxY2RlOWU2OjU3MDE2</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>717</v>
+        <v>825</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
@@ -6853,11 +6938,11 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>OTUzMmM4MTUtMjYxYy00ZjI2LThkMDAtMjc0MzkyYjRjYjY2OjU3MDE2</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>717</v>
+        <v>825</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6873,14 +6958,14 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NWE2NzVhZjgtYTQ5OC00NjgxLTkxNmYtNzc4YWZhMjZjZTNlOjU3MDE2</t>
+          <t>NTQ5YjVkYWItMzYyOS00ODg5LWIwOWEtODVjZDhlMWY3N2FkOjU3MDE2</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>7375</v>
+        <v>717</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
@@ -6893,11 +6978,11 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>7375</v>
+        <v>717</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6913,14 +6998,14 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NjM4Y2JlY2EtMTNjZS00ZmRkLWJjMTQtZTU2OTZkMGE1NTM2OjU3MDE2</t>
+          <t>NWE2NzVhZjgtYTQ5OC00NjgxLTkxNmYtNzc4YWZhMjZjZTNlOjU3MDE2</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>96</v>
+        <v>7375</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
@@ -6933,11 +7018,11 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>48</v>
+        <v>7375</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6953,20 +7038,16 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>N2I3ZTkxNTUtMWY0NC00MjhhLWIxZDctYWMxZTFhZWYxOGYxOjU3MDE2</t>
+          <t>NjM4Y2JlY2EtMTNjZS00ZmRkLWJjMTQtZTU2OTZkMGE1NTM2OjU3MDE2</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100" t="n">
-        <v>43</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Troca do Balde via correio</t>
-        </is>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
         <v>16</v>
       </c>
@@ -6977,11 +7058,11 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6997,16 +7078,20 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>YTdmOGYzMDctZDg5ZS00MGYyLWFkMzAtMTEzNzkzNmI5MjZmOjU3MDE2</t>
+          <t>N2I3ZTkxNTUtMWY0NC00MjhhLWIxZDctYWMxZTFhZWYxOGYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>3.33e+16</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Troca do Balde via correio</t>
+        </is>
+      </c>
       <c r="E101" t="n">
         <v>16</v>
       </c>
@@ -7017,11 +7102,11 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ODEwYWQzODUtY2JhYy00NmM5LWE5M2UtYzQ1MDMyY2JmZjNlOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1.11e+16</v>
+        <v>43</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -1908,7 +1908,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,36 +539,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
+          <t>MTRmZDUxYzItZjNjMi00NDk2LWE4MTUtZWM3ZWZmMzNhYjlkOjU3MDE2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SYXJ3ADJZX</t>
+          <t>SYDL1KWLBE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7722118000140 - FUND DE APOIO AO ENSINO PESQ E ASSISTENCIA HCFMRPUSP</t>
+          <t>64858525007824 - MONSANTO DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Preventiva já foi paga que o atendimento de limpeza da maquina, somente estamos cobrando as peças e 01 hora do técnico</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>64858525007824 - MONSANTO DO BRASIL LTDA
+CACHOEIRA DOURADA MG</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO CONTEMPLANDO A VISITA TÉCNICA DE UM DIA PARA MANUTENÇÃO DA RECICLADORA
+O VALOR PODE SER ALTERADO CASO PRECISE DE MAIS TEMPO PARA A MANUTENÇÃO
+PEÇAS NÃO ESTÃO INCLUSAS NESTE ORÇAMENTO. CASO SEJA NECESSÁRIO, SERA ADICIONADO NO VALOR FINAL
+Manunteçao recicladora R$ 4.000,00
+Peças poderão ser inclusas no orçamento apos diagnostico 
+1. Dados Monsanto
+Monsanto do Brasil LTDA
+End: Rod DCD 360 Córrego da Escondida S/N
+Zona Rural, Cachoeira Dourada MG
+CEP: 38.370-000
+CNPJ: 64.858.525/0078-24
+2. Dados fornecedor:
+09.209.220/0001-02
+3. Data da cotação:
+11/11/2025
+4. Valores da cotação, incluindo valor total:
+Produto de Estoque
+5. Impostos:
+ICMS (12%)
+6. Condições de pagamento (Mínimo 30 dias):
+Faturamento para 30 dias
+7. NCM (em caso de material):
+Não tem matertial nessa proposta
+8. Código de serviço (em caso de serviço):
+14.01 / 14.01.c - Demais Casos
+9. Validade da proposta (mínimo 15 dias):
+15 Dias</t>
+        </is>
+      </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1056.4</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1056.4</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -578,7 +609,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-11-12T12:52:46.887Z</t>
+          <t>2025-11-18T15:58:38.481Z</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -591,12 +622,12 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2025-11-05T13:06:35.085Z</t>
+          <t>2025-11-11T16:06:07.949Z</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ZWMwNWE3NTgtODkyOC00ZjE5LWI0YTgtYjY0NmYwMDY2OGIwOjU3MDE2</t>
+          <t>NTYyNjA5ODctODA0MS00ODJlLWE1MTQtOTY0ZTQyZWRjOTYwOjU3MDE2</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -616,7 +647,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>NDE2MTc1Nzo1NzAxNg==</t>
+          <t>NDgyMzQxODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -628,17 +659,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B1IJGVB5A</t>
+          <t>RJ0AQCEX-G</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R6IHIJPUZR</t>
+          <t>11025814886 - EDINA KIYOMI OSAKI MISHIMA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -648,40 +679,40 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>964.85</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>964.85</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2024-08-14T17:42:21.925Z</t>
+          <t>2025-11-18T15:45:15.510Z</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>IRACILDA LOPES</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2024-08-07T17:45:02.123Z</t>
+          <t>2025-11-11T15:48:38.327Z</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ZDM4ZDY1NjMtN2E5Yy00ZDQ3LWFlMDktYzUwYzk4NDQ4NWY1OjU3MDE2</t>
+          <t>OTRkZmU3YjYtNDc4OC00OWJlLTk2OWMtYmQ5Y2Q4ZWRiMTY3OjU3MDE2</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -701,82 +732,78 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>MzMxMDM0OTo1NzAxNg==</t>
+          <t>NDgzNDgwNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKB8DXCYGE</t>
+          <t>SYXJ3ADJZX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dilmatec</t>
+          <t>7722118000140 - FUND DE APOIO AO ENSINO PESQ E ASSISTENCIA HCFMRPUSP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Diagnostico e resoluçao problema em 02 equipamentos que nao estavam atingindo temperatura</t>
+          <t>Preventiva já foi paga que o atendimento de limpeza da maquina, somente estamos cobrando as peças e 01 hora do técnico</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1056.4</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1056.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-09-04T15:24:13.519Z</t>
+          <t>2025-11-12T12:52:46.887Z</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Rafael Machado Barboza</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/2a7e8c69-1223-41d3-967d-474788d2fb01/signatures/51c1ade7-ff37-4ee9-b84d-46ee75381607.png</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-08-28T15:35:41.479Z</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
+          <t>2025-11-05T13:06:35.085Z</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ZWMwNWE3NTgtODkyOC00ZjE5LWI0YTgtYjY0NmYwMDY2OGIwOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -794,29 +821,29 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>NDE2MTc1Nzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RYUVNWH3EG</t>
+          <t>B1IJGVB5A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GARANTIA/61012019000142 - ASSOCIAÇÃO BRASILEIRA IJCSUD</t>
+          <t>R6IHIJPUZR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -826,12 +853,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -841,25 +868,25 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-10-09T21:18:04.630Z</t>
+          <t>2024-08-14T17:42:21.925Z</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>IRACILDA LOPES</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-10-02T21:19:25.794Z</t>
+          <t>2024-08-07T17:45:02.123Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
+          <t>ZDM4ZDY1NjMtN2E5Yy00ZDQ3LWFlMDktYzUwYzk4NDQ4NWY1OjU3MDE2</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -879,7 +906,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>NDcxNTkzODo1NzAxNg==</t>
+          <t>MzMxMDM0OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -891,40 +918,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HJ0GXQO2EG</t>
+          <t>SKB8DXCYGE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JOANA DARC OLIVEIRA</t>
+          <t>Dilmatec</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Orçamento  para reforma de TFK 02 kg</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Reforma</t>
-        </is>
-      </c>
+          <t>Diagnostico e resoluçao problema em 02 equipamentos que nao estavam atingindo temperatura</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2167.29</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2167.29</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -934,13 +957,13 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-10-06T13:42:48.402Z</t>
+          <t>2025-09-04T15:24:13.519Z</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joana D’Arc Oliveira </t>
+          <t>Rafael Machado Barboza</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -950,19 +973,15 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
+          <t>accounts/57016/quotations/2a7e8c69-1223-41d3-967d-474788d2fb01/signatures/51c1ade7-ff37-4ee9-b84d-46ee75381607.png</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2025-09-29T15:17:10.234Z</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-28T15:35:41.479Z</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -980,7 +999,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>MzM3ODI5ODo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -992,17 +1011,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HYTE7IDHEX</t>
+          <t>RYUVNWH3EG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MAQUINA 02</t>
+          <t>GARANTIA/61012019000142 - ASSOCIAÇÃO BRASILEIRA IJCSUD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1012,12 +1031,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>979.73</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>979.73</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1027,7 +1046,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-10-06T18:41:42.725Z</t>
+          <t>2025-10-09T21:18:04.630Z</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1040,12 +1059,12 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-09-29T18:42:56.833Z</t>
+          <t>2025-10-02T21:19:25.794Z</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1065,7 +1084,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDcxNTkzODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1077,60 +1096,76 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SYLVG8O3EG</t>
+          <t>HJ0GXQO2EG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>JOANA DARC OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Orçamento  para reforma de TFK 02 kg</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Reforma</t>
+        </is>
+      </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>2167.29</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>2167.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-10-06T18:34:31.188Z</t>
+          <t>2025-10-06T13:42:48.402Z</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joana D’Arc Oliveira </t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-09-29T18:38:37.635Z</t>
+          <t>2025-09-29T15:17:10.234Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1150,29 +1185,29 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzM3ODI5ODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BJFPMUNTXG</t>
+          <t>HYTE7IDHEX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MIX SOLUCOES AMBIENTAIS LTDA</t>
+          <t>MAQUINA 02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1182,12 +1217,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>979.73</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>979.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1197,7 +1232,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-10-15T21:09:42.233Z</t>
+          <t>2025-10-06T18:41:42.725Z</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1210,12 +1245,12 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-10-08T21:12:33.362Z</t>
+          <t>2025-09-29T18:42:56.833Z</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1235,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>NDgzNDc2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1247,17 +1282,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SY9I6QSJBE</t>
+          <t>SYLVG8O3EG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>45246402000532 - CENTER NORTE S/A CONSTRUCA</t>
+          <t>MAQUINA 01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1267,22 +1302,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>660.525</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>660.525</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-11-14T16:10:10.258Z</t>
+          <t>2025-10-06T18:34:31.188Z</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1295,12 +1330,12 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-11-07T16:26:09.914Z</t>
+          <t>2025-09-29T18:38:37.635Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1320,52 +1355,44 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NDE3MTYzNjo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BYCZRKIPEL</t>
+          <t>BJFPMUNTXG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>62730134620 - FRANCISCO DE LUCCA JUNIOR</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>GARANTIA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>garantia</t>
-        </is>
-      </c>
+          <t>MIX SOLUCOES AMBIENTAIS LTDA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="b">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1375,7 +1402,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-10-17T12:48:39.389Z</t>
+          <t>2025-10-15T21:09:42.233Z</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1388,12 +1415,12 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-10-10T13:07:18.487Z</t>
+          <t>2025-10-08T21:12:33.362Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
+          <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1413,7 +1440,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NDgyMzMyODo1NzAxNg==</t>
+          <t>NDgzNDc2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1425,20 +1452,198 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SY9I6QSJBE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>45246402000532 - CENTER NORTE S/A CONSTRUCA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>660.525</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>660.525</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2025-11-14T16:10:10.258Z</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-11-07T16:26:09.914Z</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>NDE3MTYzNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BYCZRKIPEL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>62730134620 - FRANCISCO DE LUCCA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GARANTIA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>garantia</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>530.25</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>530.25</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2025-10-17T12:48:39.389Z</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-10-10T13:07:18.487Z</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>NDgyMzMyODo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1447,7 +1652,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1456,191 +1661,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>47370</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>47370</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2025-08-15T18:25:59.379Z</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>RAFAEL BARBOZA</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:27:17.728Z</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SJBLZ0HQLG</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="b">
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1650,7 +1681,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1663,14 +1694,10 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-09-02T14:09:17.339Z</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1688,7 +1715,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1700,32 +1727,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>Salobo 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1735,27 +1770,23 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:27:17.728Z</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1773,7 +1804,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1785,40 +1816,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1828,7 +1855,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1841,10 +1868,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>2025-09-08T22:01:45.251Z</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1862,7 +1893,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1874,36 +1905,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R1R8PTIYBL</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>orçamento</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1913,7 +1940,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-10T19:48:40.136Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1926,12 +1953,12 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2025-11-03T19:49:41.839Z</t>
+          <t>2025-09-29T18:44:47.397Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1951,7 +1978,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NDgyMzkyMzo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1963,67 +1990,63 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
+          <t>2025-08-28T16:05:56.490Z</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2034,44 +2057,44 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BJ0FAVCKBL</t>
+          <t>R1R8PTIYBL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
+          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Autorizado por João</t>
+          <t>orçamento</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -2080,40 +2103,40 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:58.539Z</t>
+          <t>2025-11-10T19:48:40.136Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-11-06T15:28:06.348Z</t>
+          <t>2025-11-03T19:49:41.839Z</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2133,48 +2156,48 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDgyMzkyMzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2184,28 +2207,28 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>rffccfc</t>
+          <t>jose da silva</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>HENRIQUE</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
+          <t>2023-05-31T21:56:50.448Z</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2216,17 +2239,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2238,42 +2261,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKMVCD56XX</t>
+          <t>BJ0FAVCKBL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>MAQUINA 01</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Autorizado por João</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-10-20T12:54:09.917Z</t>
+          <t>2025-11-13T15:27:58.539Z</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2286,10 +2313,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-10-13T13:10:02.576Z</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>2025-11-06T15:28:06.348Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2307,34 +2338,34 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NDgyNTIyNjo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
+          <t>teste</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Substituição de 3 compressores</t>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -2343,39 +2374,43 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>2025-09-04T16:07:52.834Z</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2396,29 +2431,29 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>BKMVCD56XX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>123456</t>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2428,12 +2463,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2443,27 +2478,23 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
+          <t>2025-10-20T12:54:09.917Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-10-13T13:10:02.576Z</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2481,7 +2512,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2493,20 +2524,194 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HYICEAM_GE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>47370</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>47370</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Recusada</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>RAFAEL BARBOZA</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2514,7 +2719,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2522,219 +2727,45 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>5996.77</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>5996.77</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2025-09-15T21:48:09.008Z</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BKODRN5YZX</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Autorizado por João</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:36.746Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2025-11-06T15:27:46.917Z</t>
+          <t>2025-09-02T14:01:32.021Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2754,34 +2785,34 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SYSJ0HARXL</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
+          <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -2790,12 +2821,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2805,20 +2836,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-04T13:33:37.491Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-10-28T14:06:21.222Z</t>
+          <t>2025-09-08T21:59:15.256Z</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2839,7 +2870,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>NDgyMTM3Mjo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -2851,22 +2882,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SJH_RHL1BL</t>
+          <t>BKODRN5YZX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
+          <t>MAQUINA 03</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+          <t>Autorizado por João</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -2875,67 +2906,241 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>490.38</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>490.38</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2025-11-13T15:27:36.746Z</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2025-11-06T15:27:46.917Z</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SYSJ0HARXL</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2123.15</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2123.15</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2025-11-04T13:33:37.491Z</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2025-10-28T14:06:21.222Z</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>NDgyMTM3Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SJH_RHL1BL</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>511.65999999999997</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>511.65999999999997</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Aprovada</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>2025-11-10T14:43:09.194Z</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>Viktor Chagas</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>2025-11-03T15:08:36.141Z</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>MzkzMzA3Mjo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
@@ -3010,71 +3215,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MTZhZjRmN2MtYTIzMC00OWFiLWIzNzAtMmFiZmRjMGMyZGM0OjU3MDE2</t>
+          <t>OTExZjhhZDUtNzE4OC00NjZjLWIyZWUtMjRiNThjOWNiNDU0OjU3MDE2</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6445</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>4000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MANUNTENÇAO RECICLADORA-NAO INCULSO PEÇAS</t>
+        </is>
+      </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
+          <t>MTRmZDUxYzItZjNjMi00NDk2LWE4MTUtZWM3ZWZmMzNhYjlkOjU3MDE2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NjliMThkYjktMTc0Yy00OTg4LTg3OWMtNzEyZThiNjgyM2QzOjU3MDE2</t>
+          <t>OGI0OTMyNmYtYzM4MC00NzllLWFiMGQtNmFiMTI3Y2UwMTFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6445</v>
+        <v>4000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
+          <t>MTRmZDUxYzItZjNjMi00NDk2LWE4MTUtZWM3ZWZmMzNhYjlkOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MjY4ZDZjNjItYzY0Mi00MzliLWJjYzEtM2E5ZjY1NTFiMjM5OjU3MDE2</t>
+          <t>MDQ3NjBjMzQtM2Y3ZS00M2JiLTljYTQtMjY1ZGQ2MTEwMjg4OjU3MDE2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>6232</v>
+        <v>350</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ZjViZmRhN2QtZTFkMi00NmU4LWI4MjAtMDliMWEwODkwZTY0OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3116</v>
+        <v>350</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3083,82 +3292,78 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NGM2OWY4ZDUtOGZhNC00OWVlLTgyOTAtNmE1MDQ5ZDc0YzVmOjU3MDE2</t>
+          <t>N2RkY2JhMTgtZTdiOC00MWVlLTkxOGYtMTNhNzUwYWIwMWNmOjU3MDE2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>350</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>YmVjYmU1OWUtZDQ0Zi00ZWNlLTgxZWMtNDA5MDk3NjNlMGM0OjU3MDE2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>350</v>
+        <v>15</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Y2VjYzM3NTEtMTNjMi00OGEzLTlhMjMtZGM1OThiOTVkMWE4OjU3MDE2</t>
+          <t>OTA4NmRmOTktNTYwOS00NzIwLWI5YzAtNjI5MTU0NTZhZGE0OjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1875</v>
+        <v>2.52e+16</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>OGIxODU3NTgtMGQwNS00YjNmLThmYTMtMDI1ZjZlNWM0OTMzOjU3MDE2</t>
+          <t>NDRhZmYxYjItOTQxZi00NTQ1LTk2M2MtMzEzYzY2ODdjODgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1875</v>
+        <v>2.52e+16</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3167,82 +3372,78 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OTlhNzk3NzYtZGMzZC00MzBjLTlkY2MtNTQ4YzQ4MGE2YWQ1OjU3MDE2</t>
+          <t>YjliMTk0ZmItMjE1NS00ZThlLTllZmQtZGE2YzJjMzlhZjhkOjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>9</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NzQ3ZWZjY2YtNzk1MC00ZTI3LWI0NjItOTJmYWQ2YmQzOTY4OjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>600</v>
+        <v>9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MTc3NWUyYTAtZjAxNy00NWQwLTg2ZTMtYWFiZjYzMzZhOWUzOjU3MDE2</t>
+          <t>YzhjOTU5ZmQtZGI4NS00ODE3LWEzOGYtYzNmODQwYmIyZjk0OjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>680</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>680</v>
+        <v>350</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3251,58 +3452,54 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NGMwNTQyYWMtNGNjZC00NjljLThlZWItMDYxMjg2NzkzMmJhOjU3MDE2</t>
+          <t>ZGE1ZTU2ZDgtMTE3OC00OTZhLTg2ZmYtM2QzMDBkODIxMjlmOjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>855</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>ZTg2MzY3YjMtNGQ4Ni00MjViLWJhODQtNzk5OWM5NDgwY2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>855</v>
+        <v>204</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NGRlMTM3N2EtNzUwNC00YmUyLThmZjItMDQxZTc1ZDNjODRiOjU3MDE2</t>
+          <t>ZGU0YThiMzgtYjY1ZC00Y2I2LWI3MWItZjlkYjllN2Y1MzQ3OjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3311,17 +3508,13 @@
       <c r="C9" t="n">
         <v>18025</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TROCADO EM GARANTIA</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3339,42 +3532,38 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MTc3NGYwMDMtMzE3NS00YmU4LTgwMWMtYzdlOTU4YWYxOWE4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NmQ1MDliODYtNGYyYy00YTNiLTk1YWEtYmM0MTZhNDBkNTY1OjU3MDE2</t>
+          <t>MTZhZjRmN2MtYTIzMC00OWFiLWIzNzAtMmFiZmRjMGMyZGM0OjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>350</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TROCADO EM GARANTIA</t>
-        </is>
-      </c>
+        <v>6445</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>NjliMThkYjktMTc0Yy00OTg4LTg3OWMtNzEyZThiNjgyM2QzOjU3MDE2</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>350</v>
+        <v>6445</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -3383,38 +3572,38 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MDFmODQ2OWUtMmMyMC00NzEwLWE4NTEtMmFkOWFjYjRlYjQ2OjU3MDE2</t>
+          <t>MjY4ZDZjNjItYzY0Mi00MzliLWJjYzEtM2E5ZjY1NTFiMjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>6232</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NDUwZmFlOTEtODg1My00ZTcwLWIwOTgtZWM2Nzc3MzgzNjgyOjU3MDE2</t>
+          <t>ZjViZmRhN2QtZTFkMi00NmU4LWI4MjAtMDliMWEwODkwZTY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
+        <v>3116</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3423,78 +3612,82 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MjhmNDNmYjAtZjgzMi00MThiLWEyNTAtZWVlODc0ZjQxYzliOjU3MDE2</t>
+          <t>NGM2OWY4ZDUtOGZhNC00OWVlLTgyOTAtNmE1MDQ5ZDc0YzVmOjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1365</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1365</v>
+        <v>350</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MmQyOGU2OWYtM2IzOS00ZjYwLWJmYTctYmViYTY2M2UxNzdjOjU3MDE2</t>
+          <t>Y2VjYzM3NTEtMTNjMi00OGEzLTlhMjMtZGM1OThiOTVkMWE4OjU3MDE2</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>375</v>
+        <v>1875</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>OGIxODU3NTgtMGQwNS00YjNmLThmYTMtMDI1ZjZlNWM0OTMzOjU3MDE2</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>375</v>
+        <v>1875</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -3503,78 +3696,82 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MjFiNmI2MzctZGJjZS00NmYyLWI2YTQtMGU0NjE1NjgzZWFiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MzVjNDRmYjctMTI1My00NDg3LThlNmUtOWZhN2YyYWMyNjg3OjU3MDE2</t>
+          <t>OTlhNzk3NzYtZGMzZC00MzBjLTlkY2MtNTQ4YzQ4MGE2YWQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1.152e+16</v>
+        <v>300</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NDM0MjA4NTAtZjAwOC00YzMyLWJlM2QtODFlMzljMjE0OTk4OjU3MDE2</t>
+          <t>NzQ3ZWZjY2YtNzk1MC00ZTI3LWI0NjItOTJmYWQ2YmQzOTY4OjU3MDE2</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.152e+16</v>
+        <v>600</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>Mjk3ZTYxNWMtNGVjYy00MjQ4LWEwNmYtZDY1NTBjMDg1NGYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NDNkMGNjZmMtMjFmMS00NjQyLWI4OWYtYTk4ODg2NjkxMjcwOjU3MDE2</t>
+          <t>MTc3NWUyYTAtZjAxNy00NWQwLTg2ZTMtYWFiZjYzMzZhOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>168</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>680</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -3583,38 +3780,42 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NDRlYzI5NjAtMTZmYi00MzM3LWEzZTEtNGJmOTg0Y2Y1MzFhOjU3MDE2</t>
+          <t>NGMwNTQyYWMtNGNjZC00NjljLThlZWItMDYxMjg2NzkzMmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>700</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>350</v>
+        <v>855</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -3623,38 +3824,42 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmE3ZThjNjktMTIyMy00MWQzLTk2N2QtNDc0Nzg4ZDJmYjAxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N2NjNjliYTAtNTVlZi00NjNmLThkMmUtZGMzYzIyZjRhM2FiOjU3MDE2</t>
+          <t>NGRlMTM3N2EtNzUwNC00YmUyLThmZjItMDQxZTc1ZDNjODRiOjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>350</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>18025</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TROCADO EM GARANTIA</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>350</v>
+        <v>18025</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3663,38 +3868,42 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OTg0ZDY5MWUtZTJiZS00NmM0LTg1OGMtNDQ1ZTMwMmY2MWE3OjU3MDE2</t>
+          <t>NmQ1MDliODYtNGYyYy00YTNiLTk1YWEtYmM0MTZhNDBkNTY1OjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>85</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TROCADO EM GARANTIA</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3703,21 +3912,21 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OWRkMWJkNWQtMjE5Yy00OTY0LWExNzYtZTI4YzkyN2Q4ODdlOjU3MDE2</t>
+          <t>MDFmODQ2OWUtMmMyMC00NzEwLWE4NTEtMmFkOWFjYjRlYjQ2OjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
@@ -3730,11 +3939,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Y2FjZGRiY2YtOTQ5NS00NDIyLWE4ODctYjk4ZGUxNjU1MzMyOjU3MDE2</t>
+          <t>NDUwZmFlOTEtODg1My00ZTcwLWIwOTgtZWM2Nzc3MzgzNjgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3750,14 +3959,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>YTAxNDZjNzgtMDljZi00ZGQ4LTkwOTItZmM5N2QyNzM3MGEwOjU3MDE2</t>
+          <t>MjhmNDNmYjAtZjgzMi00MThiLWEyNTAtZWVlODc0ZjQxYzliOjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>18025</v>
+        <v>1365</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
@@ -3770,11 +3979,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>18025</v>
+        <v>1365</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3790,14 +3999,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>YTM1YmFkNmQtN2EzNS00Njk0LTliNTMtNmZiMjAwNzQ5NzFkOjU3MDE2</t>
+          <t>MmQyOGU2OWYtM2IzOS00ZjYwLWJmYTctYmViYTY2M2UxNzdjOjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>25625</v>
+        <v>375</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
@@ -3810,11 +4019,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MTdjYWQ5ZTAtMmQ3YS00OTM0LWIyOGEtYzMxYjY1ODZkNDIzOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>25625</v>
+        <v>375</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3830,14 +4039,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>YzFlYTExODctMmJkNy00N2RhLThiMTQtZTVjMTY0NWY1Y2Y5OjU3MDE2</t>
+          <t>MzVjNDRmYjctMTI1My00NDg3LThlNmUtOWZhN2YyYWMyNjg3OjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>182225</v>
+        <v>1.152e+16</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
@@ -3850,11 +4059,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>OWU3NmYwYWEtZWNhZi00YTBiLWE2NTUtNjE5NTkwNDIwZDNjOjU3MDE2</t>
+          <t>NDM0MjA4NTAtZjAwOC00YzMyLWJlM2QtODFlMzljMjE0OTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>182225</v>
+        <v>1.152e+16</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3870,14 +4079,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>YzRiYzAxZjEtOWY2Zi00ZWQ0LWJmMjgtZmYxY2RjNjY1OTBiOjU3MDE2</t>
+          <t>NDNkMGNjZmMtMjFmMS00NjQyLWI4OWYtYTk4ODg2NjkxMjcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C23" t="n">
-        <v>9940000000000000</v>
+        <v>168</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
@@ -3890,15 +4099,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>OWMxNWU5ZjUtOWI3Ny00ZmYyLWExMWYtM2RkYzA3ZWFjYzU5OjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>9940000000000000</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3910,14 +4119,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZGMxMDhlMDAtNmY3Ni00OWE1LTg0MDMtZjVmNjUyZGVkNzZlOjU3MDE2</t>
+          <t>NDRlYzI5NjAtMTZmYi00MzM3LWEzZTEtNGJmOTg0Y2Y1MzFhOjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>2073</v>
+        <v>700</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
@@ -3930,15 +4139,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3950,14 +4159,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZjczNzc1Y2UtNGU2Mi00NGEzLTk5NWUtYzRlZmRjMzFhMTI2OjU3MDE2</t>
+          <t>N2NjNjliYTAtNTVlZi00NjNmLThkMmUtZGMzYzIyZjRhM2FiOjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>36</v>
+        <v>350</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
@@ -3970,11 +4179,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ZmQ5YTY2ZWEtZDM4NS00MWMwLWI0NWYtODI3ZjAxNzRjNzE1OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>9</v>
+        <v>350</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3990,14 +4199,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZmQ3OWNiYjEtZmY3Yi00MjVkLWJhODgtYjA3NjQyZWY1MzYwOjU3MDE2</t>
+          <t>OTg0ZDY5MWUtZTJiZS00NmM0LTg1OGMtNDQ1ZTMwMmY2MWE3OjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1578</v>
+        <v>85</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
@@ -4010,11 +4219,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Y2I2NzA1MTItNDc5NS00ZWVmLWJkOTktY2JlZmJiZTNmNTFlOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1578</v>
+        <v>85</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -4030,71 +4239,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MTE0NDUwMGUtM2ZiMi00OWQ1LWFmY2EtMzNjNzZmNjBhMTVmOjU3MDE2</t>
+          <t>OWRkMWJkNWQtMjE5Yy00OTY0LWExNzYtZTI4YzkyN2Q4ODdlOjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>350</v>
+        <v>72</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>Y2FjZGRiY2YtOTQ5NS00NDIyLWE4ODctYjk4ZGUxNjU1MzMyOjU3MDE2</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>350</v>
+        <v>18</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NWM5YzAxYzktMTIwMS00ZjhkLWJjOGMtN2U3NDlmOTlmMzRkOjU3MDE2</t>
+          <t>YTAxNDZjNzgtMDljZi00ZGQ4LTkwOTItZmM5N2QyNzM3MGEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>85</v>
+        <v>18025</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>85</v>
+        <v>18025</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4103,38 +4312,38 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NjRmMDVhODItNmU2Mi00ZDRhLTk5NmItNzM2ODI0YjE2MjRmOjU3MDE2</t>
+          <t>YTM1YmFkNmQtN2EzNS00Njk0LTliNTMtNmZiMjAwNzQ5NzFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1365</v>
+        <v>25625</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+          <t>MTdjYWQ5ZTAtMmQ3YS00OTM0LWIyOGEtYzMxYjY1ODZkNDIzOjU3MDE2</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1365</v>
+        <v>25625</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4143,38 +4352,38 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OGUzMjVkZDYtOTA3Yi00MjFjLWFjYzgtOWVlMGI3MjJkNjIzOjU3MDE2</t>
+          <t>YzFlYTExODctMmJkNy00N2RhLThiMTQtZTVjMTY0NWY1Y2Y5OjU3MDE2</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>350</v>
+        <v>182225</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>OWU3NmYwYWEtZWNhZi00YTBiLWE2NTUtNjE5NTkwNDIwZDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>350</v>
+        <v>182225</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4183,38 +4392,38 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Yjk2YzIwMDktMzVkMy00ZGRjLWIwOTYtOTJjOWFlMjZiM2FhOjU3MDE2</t>
+          <t>YzRiYzAxZjEtOWY2Zi00ZWQ0LWJmMjgtZmYxY2RjNjY1OTBiOjU3MDE2</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>375</v>
+        <v>9940000000000000</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>OWMxNWU5ZjUtOWI3Ny00ZmYyLWExMWYtM2RkYzA3ZWFjYzU5OjU3MDE2</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>375</v>
+        <v>9940000000000000</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4223,14 +4432,14 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ZTA0MDdkOTgtNjJjMi00ZTgyLWFmMzEtYzg4MzdkYzhjYmMzOjU3MDE2</t>
+          <t>ZGMxMDhlMDAtNmY3Ni00OWE1LTg0MDMtZjVmNjUyZGVkNzZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -4241,11 +4450,11 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4263,34 +4472,34 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MDhmZjQ1YWQtNTY2Yi00YTlkLWIyMWEtZDI5Y2RkYThlODAwOjU3MDE2</t>
+          <t>ZjczNzc1Y2UtNGU2Mi00NGEzLTk5NWUtYzRlZmRjMzFhMTI2OjU3MDE2</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>ZmQ5YTY2ZWEtZDM4NS00MWMwLWI0NWYtODI3ZjAxNzRjNzE1OjU3MDE2</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -4303,38 +4512,38 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>N2EyYTQzZjktNzgxZi00Mzk2LWEyNzMtODM0NmViMTE4MWE2OjU3MDE2</t>
+          <t>ZmQ3OWNiYjEtZmY3Yi00MjVkLWJhODgtYjA3NjQyZWY1MzYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>85</v>
+        <v>1578</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>Y2I2NzA1MTItNDc5NS00ZWVmLWJkOTktY2JlZmJiZTNmNTFlOjU3MDE2</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>85</v>
+        <v>1578</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -4343,29 +4552,29 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OWIyYjYwOTktYTg5MC00ZjRhLWEzOGMtNDI3YTE2MTA1NTI1OjU3MDE2</t>
+          <t>MTE0NDUwMGUtM2ZiMi00OWQ1LWFmY2EtMzNjNzZmNjBhMTVmOjU3MDE2</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4383,38 +4592,38 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>YTJjM2ExNTAtOWExYi00Mzk1LWE1N2MtM2JkYTU3MDBiMzhlOjU3MDE2</t>
+          <t>NWM5YzAxYzktMTIwMS00ZjhkLWJjOGMtN2U3NDlmOTlmMzRkOjU3MDE2</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>375</v>
+        <v>85</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>375</v>
+        <v>85</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -4423,38 +4632,38 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>YTYxMjU3ODEtZjY4ZS00MDQyLTg5YmItYzg1YTA3YTdmZmY5OjU3MDE2</t>
+          <t>NjRmMDVhODItNmU2Mi00ZDRhLTk5NmItNzM2ODI0YjE2MjRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>350</v>
+        <v>1365</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>350</v>
+        <v>1365</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4463,38 +4672,38 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>YTg1ZmQyOGMtNDZkOC00YTgwLWJhODUtOGI5OTA5ZDliZjg1OjU3MDE2</t>
+          <t>OGUzMjVkZDYtOTA3Yi00MjFjLWFjYzgtOWVlMGI3MjJkNjIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>8399999999999999</v>
+        <v>350</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8399999999999999</v>
+        <v>350</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4503,38 +4712,38 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>YTlhNDQ1NWItMWI4OS00ZGM0LThiOTgtMzZlOTcxNTE0NzcyOjU3MDE2</t>
+          <t>Yjk2YzIwMDktMzVkMy00ZGRjLWIwOTYtOTJjOWFlMjZiM2FhOjU3MDE2</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>2073</v>
+        <v>375</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2073</v>
+        <v>375</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4543,38 +4752,38 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ZTZmYzJiNjEtYzBjNS00NjM2LWI0YmEtNzZlMGE1NWI2ODIwOjU3MDE2</t>
+          <t>ZTA0MDdkOTgtNjJjMi00ZTgyLWFmMzEtYzg4MzdkYzhjYmMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>2502</v>
+        <v>2073</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2502</v>
+        <v>2073</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4583,21 +4792,21 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ZWQ1NDY3MTUtZjAxMC00OTM2LTljZDctNzBmMjRlZjVhYTQwOjU3MDE2</t>
+          <t>MDhmZjQ1YWQtNTY2Yi00YTlkLWIyMWEtZDI5Y2RkYThlODAwOjU3MDE2</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>6325</v>
+        <v>9</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
@@ -4610,11 +4819,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6325</v>
+        <v>9</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4630,31 +4839,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NjA1ZWIxZDMtNWMxMC00NGE2LWEzZjEtYTZkZjM1MWVhNjQwOjU3MDE2</t>
+          <t>N2EyYTQzZjktNzgxZi00Mzk2LWEyNzMtODM0NmViMTE4MWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>1793</v>
+        <v>85</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>NjdjMzI5NDAtMmU1Mi00MjQ1LTgxNGQtNjUyNWI3ZTQyNDU4OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1793</v>
+        <v>85</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4663,38 +4872,34 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OTFkMjc2ZDEtOTkxOC00OGZlLWEyMWYtZGEwNDg3MDFiNzkxOjU3MDE2</t>
+          <t>OWIyYjYwOTktYTg5MC00ZjRhLWEzOGMtNDI3YTE2MTA1NTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>350</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -4707,38 +4912,38 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>YTlhMGVhYzMtYjJhZS00OWUwLTg5YWQtNjdjYzIyMWUyZDZmOjU3MDE2</t>
+          <t>YTJjM2ExNTAtOWExYi00Mzk1LWE1N2MtM2JkYTU3MDBiMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>2841</v>
+        <v>375</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MGQ3YTYzZmEtOGQyZS00YWNiLTljMWYtNTNiM2JkMzRmOTYwOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2841</v>
+        <v>375</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4747,38 +4952,38 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>YmUzOThhOTAtNGYyYi00YmViLWJmYzUtNDJmYTA2NDg0OGRhOjU3MDE2</t>
+          <t>YTYxMjU3ODEtZjY4ZS00MDQyLTg5YmItYzg1YTA3YTdmZmY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>660525</v>
+        <v>350</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MGY5YWI3Y2UtNWJiMC00ZWMwLTgyZjktNzU4Zjc0YmUyZDg3OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>660525</v>
+        <v>350</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4787,38 +4992,38 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MjA0Mzk0M2ItOWI2Ni00Y2NkLWJlNjgtOTUwNjdmMjVkM2Y3OjU3MDE2</t>
+          <t>YTg1ZmQyOGMtNDZkOC00YTgwLWJhODUtOGI5OTA5ZDliZjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>350</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>350</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4827,38 +5032,38 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NDUwYmZhOGUtMTA3Ni00MmY2LWFhMjgtNWY5YzNmNzMzMWQ1OjU3MDE2</t>
+          <t>YTlhNDQ1NWItMWI4OS00ZGM0LThiOTgtMzZlOTcxNTE0NzcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>18025</v>
+        <v>2073</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>18025</v>
+        <v>2073</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4867,23 +5072,347 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>ZTZmYzJiNjEtYzBjNS00NjM2LWI0YmEtNzZlMGE1NWI2ODIwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2502</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>2502</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ZWQ1NDY3MTUtZjAxMC00OTM2LTljZDctNzBmMjRlZjVhYTQwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6325</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>6325</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NjA1ZWIxZDMtNWMxMC00NGE2LWEzZjEtYTZkZjM1MWVhNjQwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1793</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>NjdjMzI5NDAtMmU1Mi00MjQ1LTgxNGQtNjUyNWI3ZTQyNDU4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1793</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>OTFkMjc2ZDEtOTkxOC00OGZlLWEyMWYtZGEwNDg3MDFiNzkxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>350</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>350</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>YTlhMGVhYzMtYjJhZS00OWUwLTg5YWQtNjdjYzIyMWUyZDZmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2841</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>MGQ3YTYzZmEtOGQyZS00YWNiLTljMWYtNTNiM2JkMzRmOTYwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>2841</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>YmUzOThhOTAtNGYyYi00YmViLWJmYzUtNDJmYTA2NDg0OGRhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>660525</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>MGY5YWI3Y2UtNWJiMC00ZWMwLTgyZjktNzU4Zjc0YmUyZDg3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>660525</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MjA0Mzk0M2ItOWI2Ni00Y2NkLWJlNjgtOTUwNjdmMjVkM2Y3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>350</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>350</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NDUwYmZhOGUtMTA3Ni00MmY2LWFhMjgtNWY5YzNmNzMzMWQ1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>18025</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>18025</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="n">
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
         <v>1700</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -4891,126 +5420,126 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E56" t="n">
         <v>2</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="H56" t="n">
         <v>1700</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="n">
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
         <v>47370</v>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="n">
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
         <v>2</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="H57" t="n">
         <v>47370</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="n">
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
         <v>1050</v>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="n">
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
         <v>3</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="H58" t="n">
         <v>1050</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="n">
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
         <v>494677</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -5028,429 +5557,101 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E59" t="n">
         <v>3</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="H59" t="n">
         <v>494677</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" t="n">
-        <v>350</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="n">
-        <v>6</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>350</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="n">
-        <v>6</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>2073</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="n">
-        <v>7375</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="n">
-        <v>6</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>7375</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="n">
-        <v>6</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="n">
-        <v>375</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="n">
-        <v>6</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>375</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="n">
-        <v>680</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>3</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>680</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="n">
-        <v>855</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>3</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>855</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="n">
-        <v>43</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="n">
-        <v>4</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>43</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>350</v>
+        <v>2073</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>350</v>
+        <v>2073</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5459,42 +5660,38 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
-        </is>
-      </c>
+        <v>7375</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>10000</v>
+        <v>7375</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5503,38 +5700,38 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>9</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5543,38 +5740,38 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>6325</v>
+        <v>375</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>6325</v>
+        <v>375</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5583,118 +5780,126 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>375</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E65" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>375</v>
+        <v>680</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>350</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>350</v>
+        <v>855</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
+          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>2502</v>
+        <v>43</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2502</v>
+        <v>43</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5703,38 +5908,38 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
+          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>8399999999999999</v>
+        <v>85</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>8399999999999999</v>
+        <v>85</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5743,38 +5948,38 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
+          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5783,38 +5988,42 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>85</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+        </is>
+      </c>
       <c r="E70" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>85</v>
+        <v>10000</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5823,21 +6032,21 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
+          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>700</v>
+        <v>9</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
@@ -5850,15 +6059,15 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>350</v>
+        <v>9</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5870,119 +6079,111 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>680</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>6325</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>680</v>
+        <v>6325</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>855</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>855</v>
+        <v>375</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>96</v>
+        <v>350</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>48</v>
+        <v>350</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5991,38 +6192,38 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>6000000000000001</v>
+        <v>2502</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>6000000000000001</v>
+        <v>2502</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -6031,38 +6232,38 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>3.8825e+16</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>3.8825e+16</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6071,38 +6272,38 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>2.1e+16</v>
+        <v>2073</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2.1e+16</v>
+        <v>2073</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6111,38 +6312,38 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>3e+16</v>
+        <v>85</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>3e+16</v>
+        <v>85</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6151,38 +6352,38 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>47370</v>
+        <v>700</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>47370</v>
+        <v>350</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6191,67 +6392,395 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>680</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>680</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>855</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>3</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>855</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" t="n">
+        <v>96</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="n">
+        <v>6</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>48</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" t="n">
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="n">
         <v>1700</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -6259,46 +6788,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="E89" t="n">
         <v>2</v>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H81" t="n">
+      <c r="H89" t="n">
         <v>1700</v>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" t="n">
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
         <v>494677</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -6316,473 +6845,141 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E82" t="n">
+      <c r="E90" t="n">
         <v>3</v>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H82" t="n">
+      <c r="H90" t="n">
         <v>494677</v>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>1</v>
-      </c>
-      <c r="C83" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="n">
-        <v>3</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H83" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>NTdmZWE4N2QtMTU1Zi00OWNhLWJlMTItOGM0NDlhOGEzM2I0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="n">
-        <v>6</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>NjdlODg4ZTMtZThiOC00MjM3LWE4ZGUtNjk4MWVlYzhiZDk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" t="n">
-        <v>375</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="n">
-        <v>6</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>375</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>ODI1NWRlYjYtYTg0Yy00ZDhlLTk0MmEtZjNkYWEzZWYyYTVjOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" t="n">
-        <v>7375</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="n">
-        <v>6</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>7375</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>YjljMTRhODUtYzlmZC00ZjBhLWExZjMtYmExMTY2YzMzZWFiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" t="n">
-        <v>350</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="n">
-        <v>6</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
-        <v>350</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>ZWM2ZTEzNTktN2U5My00MjJiLWEwNmYtZmQ3ZTIxNTg1ZWNhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="n">
-        <v>6</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>2073</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" t="n">
-        <v>3.2215e+16</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="n">
-        <v>5</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
-        <v>3.2215e+16</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" t="n">
-        <v>823</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>310Km</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>5</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H90" t="n">
-        <v>2</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>70</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Enviado por Sedex10 de SP para DF</t>
-        </is>
-      </c>
+        <v>1050</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>43</v>
+        <v>1050</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
+          <t>NTdmZWE4N2QtMTU1Zi00OWNhLWJlMTItOGM0NDlhOGEzM2I0OjU3MDE2</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>908</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>8399999999999999</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>350</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
+          <t>NjdlODg4ZTMtZThiOC00MjM3LWE4ZGUtNjk4MWVlYzhiZDk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>6000000000000001</v>
+        <v>375</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>6000000000000001</v>
+        <v>375</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6791,38 +6988,38 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MTE2ZmIzMDUtYWVlNC00N2M1LWI2YWEtYmQ4ZmZmNDMyY2M5OjU3MDE2</t>
+          <t>ODI1NWRlYjYtYTg0Yy00ZDhlLTk0MmEtZjNkYWEzZWYyYTVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>8399999999999999</v>
+        <v>7375</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>8399999999999999</v>
+        <v>7375</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -6831,78 +7028,78 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>M2E2MGI3YzMtNmIxZi00NGM4LWEyMzctNWUyNzcxODM0ZWM5OjU3MDE2</t>
+          <t>YjljMTRhODUtYzlmZC00ZjBhLWExZjMtYmExMTY2YzMzZWFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>117</v>
+        <v>350</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>YTQ3NzcxODMtYTBkNS00ZWUzLWJlYTQtYjMyNzI5MTRmODhhOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>117</v>
+        <v>350</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NGI5MDNkYWQtNzdhZC00NTM4LTgxNGItNzE4NDRjZWNlYmYxOjU3MDE2</t>
+          <t>ZWM2ZTEzNTktN2U5My00MjJiLWEwNmYtZmQ3ZTIxNTg1ZWNhOjU3MDE2</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>9000000000000001</v>
+        <v>2073</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>3e+16</v>
+        <v>2073</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6911,38 +7108,38 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NTM1MTUxMDQtZGQxYi00ODQ4LWE2YmYtNGZkNDgxY2RlOWU2OjU3MDE2</t>
+          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>825</v>
+        <v>3.2215e+16</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>OTUzMmM4MTUtMjYxYy00ZjI2LThkMDAtMjc0MzkyYjRjYjY2OjU3MDE2</t>
+          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>825</v>
+        <v>3.2215e+16</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6951,78 +7148,86 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NTQ5YjVkYWItMzYyOS00ODg5LWIwOWEtODVjZDhlMWY3N2FkOjU3MDE2</t>
+          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>717</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
+        <v>823</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>310Km</t>
+        </is>
+      </c>
       <c r="E98" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>OWQzZDUyMzctNGVhYS00ZDcwLWIxYzQtNjJjM2VjYTEzYjJmOjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>717</v>
+        <v>2</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NWE2NzVhZjgtYTQ5OC00NjgxLTkxNmYtNzc4YWZhMjZjZTNlOjU3MDE2</t>
+          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>7375</v>
-      </c>
-      <c r="D99" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Enviado por Sedex10 de SP para DF</t>
+        </is>
+      </c>
       <c r="E99" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>7375</v>
+        <v>43</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7031,67 +7236,67 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NjM4Y2JlY2EtMTNjZS00ZmRkLWJjMTQtZTU2OTZkMGE1NTM2OjU3MDE2</t>
+          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>96</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
+        <v>908</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E100" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>48</v>
+        <v>350</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>N2I3ZTkxNTUtMWY0NC00MjhhLWIxZDctYWMxZTFhZWYxOGYxOjU3MDE2</t>
+          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>43</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Troca do Balde via correio</t>
-        </is>
-      </c>
+        <v>6000000000000001</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
         <v>16</v>
       </c>
@@ -7102,11 +7307,11 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>43</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -698,13 +698,21 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Edina K O Mishima</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/1774f003-3175-4be8-801c-c7e958af19a8/signatures/650d7c22-e91c-4757-9ac9-9ad5beab0def.png</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>2025-11-11T15:48:38.327Z</t>
@@ -737,7 +745,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3267,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MDQ3NjBjMzQtM2Y3ZS00M2JiLTljYTQtMjY1ZGQ2MTEwMjg4OjU3MDE2</t>
+          <t>MDU3Zjg5ODMtM2E3Mi00NDM4LWIyODctOGNkNDhiZTkyZjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -3299,14 +3307,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N2RkY2JhMTgtZTdiOC00MWVlLTkxOGYtMTNhNzUwYWIwMWNmOjU3MDE2</t>
+          <t>MDgwZWUyMTktODkzYi00ZTlmLTkwYmEtMjkzOTdiZDA0YWM1OjU3MDE2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
@@ -3319,11 +3327,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>YmVjYmU1OWUtZDQ0Zi00ZWNlLTgxZWMtNDA5MDk3NjNlMGM0OjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3339,14 +3347,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OTA4NmRmOTktNTYwOS00NzIwLWI5YzAtNjI5MTU0NTZhZGE0OjU3MDE2</t>
+          <t>MGE0MDEzNzktZGQyZi00NTllLWIwMmMtOWVmZDEwODUyZmU3OjU3MDE2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>2.52e+16</v>
+        <v>30</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
@@ -3359,11 +3367,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NDRhZmYxYjItOTQxZi00NTQ1LTk2M2MtMzEzYzY2ODdjODgyOjU3MDE2</t>
+          <t>YmVjYmU1OWUtZDQ0Zi00ZWNlLTgxZWMtNDA5MDk3NjNlMGM0OjU3MDE2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.52e+16</v>
+        <v>15</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3379,14 +3387,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>YjliMTk0ZmItMjE1NS00ZThlLTllZmQtZGE2YzJjMzlhZjhkOjU3MDE2</t>
+          <t>NmI4ZjZmNGQtODZhYi00YmRkLTk5NWEtNjk3YjdkOTA4YmRkOjU3MDE2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>2.52e+16</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
@@ -3399,11 +3407,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>NDRhZmYxYjItOTQxZi00NTQ1LTk2M2MtMzEzYzY2ODdjODgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>2.52e+16</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3419,14 +3427,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>YzhjOTU5ZmQtZGI4NS00ODE3LWEzOGYtYzNmODQwYmIyZjk0OjU3MDE2</t>
+          <t>OWVmOTBjMjAtMDY3Zi00YWEyLWFjMjEtNGE3YmRkMjY3ZWQ5OjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>204</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
@@ -3439,15 +3447,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ZTg2MzY3YjMtNGQ4Ni00MjViLWJhODQtNzk5OWM5NDgwY2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>350</v>
+        <v>204</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3459,14 +3467,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZGE1ZTU2ZDgtMTE3OC00OTZhLTg2ZmYtM2QzMDBkODIxMjlmOjU3MDE2</t>
+          <t>ZDU2NGE2M2EtYmE1OS00ZjRmLThhNDgtMjIxMjYzNzliNDZhOjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>204</v>
+        <v>350</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
@@ -3479,15 +3487,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ZTg2MzY3YjMtNGQ4Ni00MjViLWJhODQtNzk5OWM5NDgwY2Q3OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>204</v>
+        <v>350</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3499,7 +3507,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ZGU0YThiMzgtYjY1ZC00Y2I2LWI3MWItZjlkYjllN2Y1MzQ3OjU3MDE2</t>
+          <t>ZTZlYTVkODUtZTkwMy00MWE0LWJiNmYtYTM0NGM4NGM2YTkyOjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="n">

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -1490,7 +1490,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1638,20 +1638,113 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SYHCI3OLWE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FRANCESCO DE TOMMASO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1047.65</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1047.65</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2025-11-24T15:13:20.559Z</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-11-17T15:14:20.735Z</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1660,7 +1753,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1669,106 +1762,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1778,20 +1782,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
+          <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1812,7 +1816,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1824,36 +1828,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SJBLZ0HQLG</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OUTBACK MORUMBI</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1863,27 +1871,23 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:27:17.728Z</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1901,7 +1905,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1913,32 +1917,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1948,7 +1956,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1961,12 +1969,12 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
+          <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1986,7 +1994,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1998,40 +2006,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2054,10 +2054,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2075,7 +2079,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2087,36 +2091,40 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R1R8PTIYBL</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>orçamento</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2126,7 +2134,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-11-10T19:48:40.136Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2139,14 +2147,10 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-11-03T19:49:41.839Z</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-28T16:05:56.490Z</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2164,7 +2168,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>NDgyMzkyMzo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2176,70 +2180,66 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>R1R8PTIYBL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>orçamento</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-11-10T19:48:40.136Z</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>2025-11-03T19:49:41.839Z</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2247,88 +2247,92 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDgyMzkyMzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BJ0FAVCKBL</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Autorizado por João</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:58.539Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>jose da silva</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>HENRIQUE</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-11-06T15:28:06.348Z</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2023-05-31T21:56:50.448Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2336,44 +2340,44 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>BJ0FAVCKBL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>MAQUINA 01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>Autorizado por João</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -2382,46 +2386,42 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2025-11-13T15:27:58.539Z</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>rffccfc</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
-        </is>
-      </c>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>2025-11-06T15:28:06.348Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2439,67 +2439,79 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BKMVCD56XX</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-10-20T12:54:09.917Z</t>
+          <t>2025-09-04T16:07:52.834Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-10-13T13:10:02.576Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2520,75 +2532,67 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>NDgyNTIyNjo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>BKMVCD56XX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Substituição de 3 compressores</t>
-        </is>
-      </c>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
+          <t>2025-10-20T12:54:09.917Z</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-10-13T13:10:02.576Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2609,74 +2613,78 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2694,32 +2702,117 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2727,7 +2820,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2735,106 +2828,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2844,7 +2848,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2857,10 +2861,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2878,7 +2886,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -2890,22 +2898,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BKODRN5YZX</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Autorizado por João</t>
+          <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -2914,12 +2922,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2929,27 +2937,23 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:36.746Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2025-11-06T15:27:46.917Z</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-09-08T21:59:15.256Z</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2967,7 +2971,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -2979,22 +2983,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SYSJ0HARXL</t>
+          <t>BKODRN5YZX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RIO 40 BANQUETERIA &amp; SERVICOS DE LOGISTICA LTDA</t>
+          <t>MAQUINA 03</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Necessário a troca da fonte, diagnostico realizado pelo Eduardo Delphino.</t>
+          <t>Autorizado por João</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -3003,12 +3007,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2123.15</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3018,7 +3022,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-11-04T13:33:37.491Z</t>
+          <t>2025-11-13T15:27:36.746Z</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3031,10 +3035,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2025-10-28T14:06:21.222Z</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
+          <t>2025-11-06T15:27:46.917Z</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -3052,105 +3060,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>NDgyMTM3Mjo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>SJH_RHL1BL</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>08857771741 - VIKTOR CHAGAS Orçamento para balde TFK 2Kg</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Faremos o envio de um novo balde e componentes para TFK 2kg</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>511.65999999999997</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>511.65999999999997</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Aprovada</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2025-11-10T14:43:09.194Z</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Viktor Chagas</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/cd11dd30-d3a2-4b5d-86e1-b7227ae83528/signatures/a288c6fe-a015-4ab6-8ff4-5716e239b3f1.png</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2025-11-03T15:08:36.141Z</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>MzkzMzA3Mjo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>approved</t>
         </is>
       </c>
     </row>
@@ -5411,16 +5326,296 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>MTY2NjMxNTAtYWUyMi00YzY2LTgwNDYtYTkzZTgzODgxNGQ4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>350</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>350</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MWM2N2JjOTQtYTFlYy00YjM5LTg5MjctNThkNjNhNGVkNWRkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1086</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>8</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1086</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NjYzOTVlNjEtODVjOC00YmY4LTljNjEtODljNGZjNDM5OWY2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>350</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>8</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>350</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NmY5NWU4YjctMTU4NC00NzJiLTgwODctMjkyYjg3NGY5ODU3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3795</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>8</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>3795</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Yzg5MTQ4NTgtZjZhZS00M2VjLWI2OGItNGY0ZTA3YzYwM2E4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>18025</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>8</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>18025</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ZGI4ODAzMmQtZTAzYS00YmQ5LWJmMjUtNjk1ZGUwODliNzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>8</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1.68e+16</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>8</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ZjQ5NjJjZjctN2U2ZS00ZWE3LTkwY2ItZWIxNjFlODE2YzNkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4050000000000001</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>8</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>4050000000000001</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="n">
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
         <v>1700</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -5428,126 +5623,126 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="E63" t="n">
         <v>2</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H56" t="n">
+      <c r="H63" t="n">
         <v>1700</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="n">
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
         <v>47370</v>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="n">
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
         <v>2</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="H64" t="n">
         <v>47370</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="n">
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
         <v>1050</v>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="n">
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
         <v>3</v>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H58" t="n">
+      <c r="H65" t="n">
         <v>1050</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="n">
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="n">
         <v>494677</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -5565,389 +5760,101 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E59" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>494677</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="n">
-        <v>350</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="n">
-        <v>6</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>350</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="n">
-        <v>6</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>2073</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" t="n">
-        <v>7375</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="n">
-        <v>6</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>7375</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="n">
-        <v>6</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" t="n">
-        <v>375</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="n">
-        <v>6</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>375</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" t="n">
-        <v>680</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>3</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>680</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" t="n">
-        <v>855</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
       <c r="E66" t="n">
         <v>3</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>855</v>
+        <v>494677</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>43</v>
+        <v>350</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>43</v>
+        <v>350</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5956,38 +5863,38 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>350</v>
+        <v>7375</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>350</v>
+        <v>7375</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5996,42 +5903,38 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
-        </is>
-      </c>
+        <v>8399999999999999</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>10000</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -6040,38 +5943,38 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>375</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>9</v>
+        <v>375</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -6080,118 +5983,126 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>6325</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E72" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>6325</v>
+        <v>680</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>375</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E73" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>375</v>
+        <v>855</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
+          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>350</v>
+        <v>43</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>350</v>
+        <v>43</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6200,38 +6111,38 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
+          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>2502</v>
+        <v>85</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>2502</v>
+        <v>85</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -6240,38 +6151,38 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
+          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>8399999999999999</v>
+        <v>350</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>8399999999999999</v>
+        <v>350</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6280,38 +6191,42 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+        </is>
+      </c>
       <c r="E77" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2073</v>
+        <v>10000</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6320,21 +6235,21 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
+          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
@@ -6347,11 +6262,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6367,14 +6282,14 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
+          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>700</v>
+        <v>6325</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
@@ -6387,15 +6302,15 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>350</v>
+        <v>6325</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6407,119 +6322,111 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>680</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>680</v>
+        <v>375</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>855</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>855</v>
+        <v>350</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>96</v>
+        <v>2502</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>48</v>
+        <v>2502</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -6528,38 +6435,38 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>6000000000000001</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>6000000000000001</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6568,38 +6475,38 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>3.8825e+16</v>
+        <v>2073</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>3.8825e+16</v>
+        <v>2073</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6608,38 +6515,38 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>2.1e+16</v>
+        <v>85</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>2.1e+16</v>
+        <v>85</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6648,78 +6555,82 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86" t="n">
-        <v>3e+16</v>
+        <v>700</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>3e+16</v>
+        <v>350</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>47370</v>
+        <v>680</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6728,67 +6639,351 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>855</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>855</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" t="n">
+        <v>96</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>48</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>6000000000000001</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>3.8825e+16</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="n">
+        <v>6</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>3e+16</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" t="n">
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
         <v>1700</v>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -6796,46 +6991,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E89" t="n">
+      <c r="E96" t="n">
         <v>2</v>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H89" t="n">
+      <c r="H96" t="n">
         <v>1700</v>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" t="n">
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
         <v>494677</v>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -6853,345 +7048,61 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E90" t="n">
+      <c r="E97" t="n">
         <v>3</v>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H90" t="n">
+      <c r="H97" t="n">
         <v>494677</v>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="n">
-        <v>3</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H91" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>NTdmZWE4N2QtMTU1Zi00OWNhLWJlMTItOGM0NDlhOGEzM2I0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="n">
-        <v>6</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>NjdlODg4ZTMtZThiOC00MjM3LWE4ZGUtNjk4MWVlYzhiZDk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>1</v>
-      </c>
-      <c r="C93" t="n">
-        <v>375</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="n">
-        <v>6</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H93" t="n">
-        <v>375</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>ODI1NWRlYjYtYTg0Yy00ZDhlLTk0MmEtZjNkYWEzZWYyYTVjOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" t="n">
-        <v>7375</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="n">
-        <v>6</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H94" t="n">
-        <v>7375</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>YjljMTRhODUtYzlmZC00ZjBhLWExZjMtYmExMTY2YzMzZWFiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" t="n">
-        <v>350</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="n">
-        <v>6</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H95" t="n">
-        <v>350</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>ZWM2ZTEzNTktN2U5My00MjJiLWEwNmYtZmQ3ZTIxNTg1ZWNhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="n">
-        <v>6</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H96" t="n">
-        <v>2073</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>MTQxOTJiNWMtNDEzNy00OGRjLWI0MTAtYzVmNjc5MzMxMTc0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" t="n">
-        <v>3.2215e+16</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="n">
-        <v>5</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>YzE3ODc3ODEtMmY2MC00ZTQzLWI4MjgtYThhOTUwNDcwOTg3OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H97" t="n">
-        <v>3.2215e+16</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>YjVlY2MzNWMtYmFjNS00ZjE4LWE3MGItMTliMzcxNjBlZGUwOjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>823</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>310Km</t>
-        </is>
-      </c>
+        <v>1050</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>1050</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7200,42 +7111,38 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ZGVmNWU3MTktM2EyZC00YzU1LTk5NjAtMDgwMzBlMzllMTQ1OjU3MDE2</t>
+          <t>NTdmZWE4N2QtMTU1Zi00OWNhLWJlMTItOGM0NDlhOGEzM2I0OjU3MDE2</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>70</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Enviado por Sedex10 de SP para DF</t>
-        </is>
-      </c>
+        <v>8399999999999999</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>43</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7244,82 +7151,78 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ZjY0OGYwYmMtYjJhZS00OGU4LTlhZGYtOGExMjBjOTczMjFiOjU3MDE2</t>
+          <t>NjdlODg4ZTMtZThiOC00MjM3LWE4ZGUtNjk4MWVlYzhiZDk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>908</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Y2NiZmExNzEtYmRiYy00Mzg3LWIyYjgtZjUzZDU0NGE1MGQzOjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MDBjZmRmOTktOTUwZC00YzM2LTg0N2MtZGNkNGNlZGQ5YWM4OjU3MDE2</t>
+          <t>ODI1NWRlYjYtYTg0Yy00ZDhlLTk0MmEtZjNkYWEzZWYyYTVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>6000000000000001</v>
+        <v>7375</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>6000000000000001</v>
+        <v>7375</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7328,7 +7231,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Y2QxMWRkMzAtZDNhMi00YjVkLTg2ZTEtYjcyMjdhZTgzNTI4OjU3MDE2</t>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,7 +604,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
@@ -1731,20 +1731,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SKD1SV5XZX</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PREFEITURA MUNICIPAL DE ROSANA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Referente a  transformação de 1 maquina composteira no valor total de R$ 3.000,00, de tensão 380V- trifasico, para 220V/trifasico. 
+As outras 02 são 220v</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2025-11-25T21:47:25.554Z</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-11-18T21:53:35.934Z</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NjYwZjY1NTAtNjFmZS00N2NmLTlmZTktMzY2ZWVjNmViZGJmOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>NTgwMDkyOTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1753,7 +1843,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1762,106 +1852,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1871,20 +1872,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
+          <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1905,7 +1906,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1917,36 +1918,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SJBLZ0HQLG</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OUTBACK MORUMBI</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1956,27 +1961,23 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:27:17.728Z</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -1994,7 +1995,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2006,32 +2007,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2041,7 +2046,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2054,12 +2059,12 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
+          <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2079,7 +2084,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2091,40 +2096,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2134,7 +2131,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2147,10 +2144,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2168,7 +2169,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2180,36 +2181,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R1R8PTIYBL</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>orçamento</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2219,7 +2224,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-11-10T19:48:40.136Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2232,14 +2237,10 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-11-03T19:49:41.839Z</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-28T16:05:56.490Z</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2257,7 +2258,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>NDgyMzkyMzo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2269,70 +2270,66 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>R1R8PTIYBL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>orçamento</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-11-10T19:48:40.136Z</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>2025-11-03T19:49:41.839Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2340,88 +2337,92 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDgyMzkyMzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BJ0FAVCKBL</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Autorizado por João</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:58.539Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>jose da silva</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>HENRIQUE</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-11-06T15:28:06.348Z</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2023-05-31T21:56:50.448Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2429,44 +2430,44 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>BJ0FAVCKBL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>MAQUINA 01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>Autorizado por João</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -2475,46 +2476,42 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2025-11-13T15:27:58.539Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>rffccfc</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
-        </is>
-      </c>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
+          <t>2025-11-06T15:28:06.348Z</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2532,67 +2529,79 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BKMVCD56XX</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="b">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-10-20T12:54:09.917Z</t>
+          <t>2025-09-04T16:07:52.834Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-10-13T13:10:02.576Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2613,75 +2622,67 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>NDgyNTIyNjo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>BKMVCD56XX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Substituição de 3 compressores</t>
-        </is>
-      </c>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
+          <t>2025-10-20T12:54:09.917Z</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-10-13T13:10:02.576Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2702,74 +2703,78 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2787,32 +2792,117 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2820,7 +2910,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2828,106 +2918,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2937,7 +2938,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2950,10 +2951,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2971,7 +2976,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -2983,22 +2988,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BKODRN5YZX</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Autorizado por João</t>
+          <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -3007,12 +3012,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3022,48 +3027,133 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:36.746Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
+          <t>2025-09-08T21:59:15.256Z</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BKODRN5YZX</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Autorizado por João</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>490.38</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>490.38</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-11-13T15:27:36.746Z</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
           <t>2025-11-06T15:27:46.917Z</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
@@ -5606,16 +5696,60 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>MzkwMmU1MjMtZGQ5ZC00ZjEzLWIxZjItNTM4MThiODRhODY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Transformaçao 380V- trifasico, para 220V/trifasico</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NDk0NTM0YTgtOGM0MC00ZTYwLWJhNDAtMzMxNDRiZjA3ZGY4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" t="n">
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
         <v>1700</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -5623,61 +5757,21 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>2</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>1700</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
         <v>2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+          <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>47370</v>
+        <v>1700</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5686,38 +5780,38 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+          <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
+          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>1050</v>
+        <v>47370</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1050</v>
+        <v>47370</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5726,23 +5820,63 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" t="n">
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
         <v>494677</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -5760,84 +5894,44 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="E67" t="n">
         <v>3</v>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H66" t="n">
+      <c r="H67" t="n">
         <v>494677</v>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" t="n">
-        <v>350</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="n">
-        <v>6</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>350</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
@@ -5850,15 +5944,15 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5870,14 +5964,14 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>7375</v>
+        <v>2073</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
@@ -5890,11 +5984,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>7375</v>
+        <v>2073</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5910,14 +6004,14 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>8399999999999999</v>
+        <v>7375</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
@@ -5930,11 +6024,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>8399999999999999</v>
+        <v>7375</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5950,14 +6044,14 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>375</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
@@ -5970,11 +6064,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>375</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5990,62 +6084,58 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>680</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>680</v>
+        <v>375</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -6058,11 +6148,11 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -6078,54 +6168,58 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>43</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>43</v>
+        <v>855</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
+          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
@@ -6138,11 +6232,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -6158,14 +6252,14 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
+          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
@@ -6178,11 +6272,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6198,35 +6292,31 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>10000</v>
+        <v>350</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6235,38 +6325,42 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+        </is>
+      </c>
       <c r="E78" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>9</v>
+        <v>10000</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6275,21 +6369,21 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
+          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>6325</v>
+        <v>9</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
@@ -6302,11 +6396,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>6325</v>
+        <v>9</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6322,14 +6416,14 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
+          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>375</v>
+        <v>6325</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
@@ -6342,11 +6436,11 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>375</v>
+        <v>6325</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -6362,14 +6456,14 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
+          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
@@ -6382,11 +6476,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6402,14 +6496,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
+          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>2502</v>
+        <v>350</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
@@ -6422,11 +6516,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>2502</v>
+        <v>350</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -6442,14 +6536,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
+          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>8399999999999999</v>
+        <v>2502</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
@@ -6462,11 +6556,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>8399999999999999</v>
+        <v>2502</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6482,14 +6576,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
+          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>2073</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
@@ -6502,11 +6596,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>2073</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6522,14 +6616,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
+          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
@@ -6542,11 +6636,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6562,14 +6656,14 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
+          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
@@ -6582,15 +6676,15 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -6602,35 +6696,31 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>680</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>680</v>
+        <v>350</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6639,25 +6729,25 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -6670,11 +6760,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>855</v>
+        <v>680</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6690,54 +6780,58 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>96</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>48</v>
+        <v>855</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>6000000000000001</v>
+        <v>96</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
@@ -6750,11 +6844,11 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>6000000000000001</v>
+        <v>48</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -6770,14 +6864,14 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>3.8825e+16</v>
+        <v>6000000000000001</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
@@ -6790,11 +6884,11 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>3.8825e+16</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6810,14 +6904,14 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>2.1e+16</v>
+        <v>3.8825e+16</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
@@ -6830,11 +6924,11 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>2.1e+16</v>
+        <v>3.8825e+16</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6850,14 +6944,14 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>3e+16</v>
+        <v>2.1e+16</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
@@ -6870,11 +6964,11 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>3e+16</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6890,100 +6984,140 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>47370</v>
+        <v>3e+16</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>47370</v>
+        <v>3e+16</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
-        </is>
-      </c>
+        <v>47370</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
         <v>2</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>47370</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" t="n">
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
         <v>1700</v>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -6991,46 +7125,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>2</v>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H96" t="n">
+      <c r="H97" t="n">
         <v>1700</v>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" t="n">
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="n">
         <v>494677</v>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -7048,46 +7182,6 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E97" t="n">
-        <v>3</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H97" t="n">
-        <v>494677</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
         <v>3</v>
       </c>
@@ -7098,15 +7192,15 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+          <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1050</v>
+        <v>494677</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -7118,54 +7212,54 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NTdmZWE4N2QtMTU1Zi00OWNhLWJlMTItOGM0NDlhOGEzM2I0OjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>8399999999999999</v>
+        <v>1050</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>8399999999999999</v>
+        <v>1050</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NjdlODg4ZTMtZThiOC00MjM3LWE4ZGUtNjk4MWVlYzhiZDk4OjU3MDE2</t>
+          <t>NTdmZWE4N2QtMTU1Zi00OWNhLWJlMTItOGM0NDlhOGEzM2I0OjU3MDE2</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>375</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
@@ -7178,11 +7272,11 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>375</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7198,14 +7292,14 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ODI1NWRlYjYtYTg0Yy00ZDhlLTk0MmEtZjNkYWEzZWYyYTVjOjU3MDE2</t>
+          <t>NjdlODg4ZTMtZThiOC00MjM3LWE4ZGUtNjk4MWVlYzhiZDk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>7375</v>
+        <v>375</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
@@ -7218,11 +7312,11 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>7375</v>
+        <v>375</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -1676,7 +1676,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1684,7 +1684,11 @@
           <t>2025-11-24T15:13:20.559Z</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-11-24T14:45:19.000Z</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
@@ -1724,7 +1728,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>refused</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -1770,7 +1770,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>expired</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -2011,22 +2011,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SJBLZ0HQLG</t>
+          <t>HJCRTZS--G</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OUTBACK MORUMBI</t>
+          <t>31415680817 - DOUGLAS HIROMITSU TFK 2Kg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Reforma de Estufa Airflow danificada</t>
+          <t>Parafuso (Pino) que sustenta raspador quebrou, iremos fazer uma visita técnica para descobrir se há mais defeitos. 11 96619-3370</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -2035,42 +2035,38 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>484</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-12-08T12:21:25.404Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-12-01T12:28:02.404Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2088,44 +2084,48 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDUwNzM2Mzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2148,12 +2148,12 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
+          <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2185,40 +2185,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2228,7 +2220,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2241,10 +2233,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2262,7 +2258,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2274,36 +2270,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R1R8PTIYBL</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>orçamento</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-11-10T19:48:40.136Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2326,14 +2326,10 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-11-03T19:49:41.839Z</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-28T16:05:56.490Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2351,7 +2347,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NDgyMzkyMzo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2363,70 +2359,66 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>R1R8PTIYBL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>orçamento</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-11-10T19:48:40.136Z</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>2025-11-03T19:49:41.839Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2434,88 +2426,92 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDgyMzkyMzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BJ0FAVCKBL</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Autorizado por João</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:58.539Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>jose da silva</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>HENRIQUE</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-11-06T15:28:06.348Z</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2023-05-31T21:56:50.448Z</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2523,44 +2519,44 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>BJ0FAVCKBL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>MAQUINA 01</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>Autorizado por João</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -2569,46 +2565,42 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2025-11-13T15:27:58.539Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>rffccfc</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
-        </is>
-      </c>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
+          <t>2025-11-06T15:28:06.348Z</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2626,67 +2618,79 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BKMVCD56XX</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-10-20T12:54:09.917Z</t>
+          <t>2025-09-04T16:07:52.834Z</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-10-13T13:10:02.576Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2707,75 +2711,67 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>NDgyNTIyNjo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>BKMVCD56XX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Substituição de 3 compressores</t>
-        </is>
-      </c>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
+          <t>2025-10-20T12:54:09.917Z</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-10-13T13:10:02.576Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2796,74 +2792,78 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2881,32 +2881,117 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SK7IYQDNA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Expirada</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2024-09-12T20:48:10.536Z</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2024-09-05T20:49:15.417Z</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>NDIxMTExMTo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>HJE6OUN5LE</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2914,7 +2999,7 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -2922,106 +3007,17 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3031,7 +3027,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-09-15T21:48:09.008Z</t>
+          <t>2025-09-09T13:53:17.012Z</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3044,10 +3040,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
+          <t>2025-09-02T14:01:32.021Z</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3077,22 +3077,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BKODRN5YZX</t>
+          <t>BYOHBAHQXX</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
+          <t>OUTBACK MORUMBI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Autorizado por João</t>
+          <t>Reforma de Estufa Airflow danificada</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3116,27 +3116,23 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:36.746Z</t>
+          <t>2025-09-15T21:48:09.008Z</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2025-11-06T15:27:46.917Z</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-09-08T21:59:15.256Z</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -3154,7 +3150,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -5831,31 +5827,35 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
+          <t>NzVmMDU4ODAtZTJiMi00MmFlLTgzZmItYTJlYmYwY2EyNTgxOjU3MDE2</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="C66" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>67Km de distancia</t>
+        </is>
+      </c>
       <c r="E66" t="n">
         <v>3</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1050</v>
+        <v>2</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5864,23 +5864,107 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>ZDQ0NDkzNjgtNjE2MS00YjRkLWEyNWUtOTdkOGFiMjFiMjVjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>350</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Visita técnica</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>NWVmNmQ0MDEtNzBmMy00Yzg3LWFlZDAtYzJiYTM1MTc4OWNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>350</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" t="n">
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
         <v>494677</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -5898,124 +5982,44 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E69" t="n">
         <v>3</v>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H67" t="n">
+      <c r="H69" t="n">
         <v>494677</v>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" t="n">
-        <v>350</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="n">
-        <v>6</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>350</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="n">
-        <v>6</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>2073</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>7375</v>
+        <v>350</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
@@ -6028,15 +6032,15 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>7375</v>
+        <v>350</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6048,14 +6052,14 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>8399999999999999</v>
+        <v>2073</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
@@ -6068,11 +6072,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>8399999999999999</v>
+        <v>2073</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -6088,14 +6092,14 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>375</v>
+        <v>7375</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
@@ -6108,11 +6112,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>375</v>
+        <v>7375</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -6128,182 +6132,182 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>680</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>8399999999999999</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>680</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>855</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>855</v>
+        <v>375</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>43</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>43</v>
+        <v>680</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>85</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>85</v>
+        <v>855</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
+          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>350</v>
+        <v>43</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
@@ -6316,11 +6320,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>350</v>
+        <v>43</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6336,35 +6340,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
-        </is>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>10000</v>
+        <v>85</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6373,38 +6373,38 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
+          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>350</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>9</v>
+        <v>350</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6413,38 +6413,42 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>6325</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+        </is>
+      </c>
       <c r="E80" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>6325</v>
+        <v>10000</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -6453,21 +6457,21 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
+          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>375</v>
+        <v>9</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
@@ -6480,11 +6484,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>375</v>
+        <v>9</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6500,14 +6504,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
+          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>350</v>
+        <v>6325</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
@@ -6520,11 +6524,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>350</v>
+        <v>6325</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -6540,14 +6544,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
+          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>2502</v>
+        <v>375</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
@@ -6560,11 +6564,11 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>2502</v>
+        <v>375</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6580,14 +6584,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
+          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>8399999999999999</v>
+        <v>350</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
@@ -6600,11 +6604,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>8399999999999999</v>
+        <v>350</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6620,14 +6624,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
+          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>2073</v>
+        <v>2502</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
@@ -6640,11 +6644,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>2073</v>
+        <v>2502</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6660,14 +6664,14 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
+          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>85</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
@@ -6680,11 +6684,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>85</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6700,14 +6704,14 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
+          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>700</v>
+        <v>2073</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
@@ -6720,15 +6724,15 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>350</v>
+        <v>2073</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6740,79 +6744,71 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>680</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>680</v>
+        <v>85</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>855</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>855</v>
+        <v>350</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -6821,101 +6817,109 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>96</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>48</v>
+        <v>680</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>6000000000000001</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>6000000000000001</v>
+        <v>855</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92" t="n">
-        <v>3.8825e+16</v>
+        <v>96</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
@@ -6928,11 +6932,11 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>3.8825e+16</v>
+        <v>48</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6948,14 +6952,14 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>2.1e+16</v>
+        <v>6000000000000001</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
@@ -6968,11 +6972,11 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>2.1e+16</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6988,14 +6992,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>3e+16</v>
+        <v>3.8825e+16</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
@@ -7008,11 +7012,11 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>3e+16</v>
+        <v>3.8825e+16</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7028,75 +7032,71 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>47370</v>
+        <v>2.1e+16</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>47370</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
-        </is>
-      </c>
+        <v>3e+16</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>3e+16</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7105,23 +7105,107 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ORCAMENTO REALIZADO PELO BLING</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" t="n">
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="n">
         <v>1700</v>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -7129,46 +7213,46 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E97" t="n">
+      <c r="E99" t="n">
         <v>2</v>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H97" t="n">
+      <c r="H99" t="n">
         <v>1700</v>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" t="n">
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="n">
         <v>494677</v>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -7186,150 +7270,70 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E98" t="n">
+      <c r="E100" t="n">
         <v>3</v>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H98" t="n">
+      <c r="H100" t="n">
         <v>494677</v>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="n">
-        <v>3</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H99" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>NTdmZWE4N2QtMTU1Zi00OWNhLWJlMTItOGM0NDlhOGEzM2I0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>1</v>
-      </c>
-      <c r="C100" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="n">
-        <v>6</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H100" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NjdlODg4ZTMtZThiOC00MjM3LWE4ZGUtNjk4MWVlYzhiZDk4OjU3MDE2</t>
+          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>375</v>
+        <v>1050</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>375</v>
+        <v>1050</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>YjAxZDM1OWMtMzEzYi00NzFkLWFlNmEtOTQ2NmY4N2NiZGU2OjU3MDE2</t>
+          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -2045,7 +2045,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2054,13 +2054,21 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>douglas simao</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/6b2b07ff-cb70-450b-bc03-538da26b5fb0/signatures/82045e1d-cc6f-45af-a3f3-2c6a0906455d.png</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>2025-12-01T12:28:02.404Z</t>
@@ -2089,7 +2097,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,42 +1019,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RYUVNWH3EG</t>
+          <t>SKYBOA3Z-G</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GARANTIA/61012019000142 - ASSOCIAÇÃO BRASILEIRA IJCSUD</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>FRANCESCO DE TOMMASO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>988.85</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>988.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-10-09T21:18:04.630Z</t>
+          <t>2025-12-09T21:20:29.860Z</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1067,12 +1075,12 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-10-02T21:19:25.794Z</t>
+          <t>2025-12-02T21:20:54.686Z</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1092,88 +1100,72 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>NDcxNTkzODo1NzAxNg==</t>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HJ0GXQO2EG</t>
+          <t>RYUVNWH3EG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JOANA DARC OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Orçamento  para reforma de TFK 02 kg</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Reforma</t>
-        </is>
-      </c>
+          <t>GARANTIA/61012019000142 - ASSOCIAÇÃO BRASILEIRA IJCSUD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2167.29</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2167.29</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-10-06T13:42:48.402Z</t>
+          <t>2025-10-09T21:18:04.630Z</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Joana D’Arc Oliveira </t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-09-29T15:17:10.234Z</t>
+          <t>2025-10-02T21:19:25.794Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
+          <t>OGUzZjA5OGMtMTdlNy00MDY3LTllYjQtMzhmMWNhZGM4NjNmOjU3MDE2</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1193,72 +1185,88 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>MzM3ODI5ODo1NzAxNg==</t>
+          <t>NDcxNTkzODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HYTE7IDHEX</t>
+          <t>HJ0GXQO2EG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MAQUINA 02</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>JOANA DARC OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Orçamento  para reforma de TFK 02 kg</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Reforma</t>
+        </is>
+      </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>979.73</t>
+          <t>2167.29</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>979.73</t>
+          <t>2167.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-10-06T18:41:42.725Z</t>
+          <t>2025-10-06T13:42:48.402Z</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joana D’Arc Oliveira </t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/336279a3-e397-43dd-b3ef-8d0f677e97af/signatures/e23e6b48-ded8-4f36-a055-55d66d4bbb0d.png</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-09-29T18:42:56.833Z</t>
+          <t>2025-09-29T15:17:10.234Z</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>YTExMmFkNDktMjYyZi00NWVhLWE0Y2YtMjIyZGY1MDc0MjJhOjU3MDE2</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1278,29 +1286,29 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzM3ODI5ODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SYLVG8O3EG</t>
+          <t>HYTE7IDHEX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
+          <t>MAQUINA 02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1310,12 +1318,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>979.73</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>979.73</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1325,7 +1333,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-10-06T18:34:31.188Z</t>
+          <t>2025-10-06T18:41:42.725Z</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1338,7 +1346,7 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-09-29T18:38:37.635Z</t>
+          <t>2025-09-29T18:42:56.833Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1375,17 +1383,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BJFPMUNTXG</t>
+          <t>SYLVG8O3EG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MIX SOLUCOES AMBIENTAIS LTDA</t>
+          <t>MAQUINA 01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1395,12 +1403,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1410,7 +1418,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-10-15T21:09:42.233Z</t>
+          <t>2025-10-06T18:34:31.188Z</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1423,12 +1431,12 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-10-08T21:12:33.362Z</t>
+          <t>2025-09-29T18:38:37.635Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1448,7 +1456,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NDgzNDc2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1460,17 +1468,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SY9I6QSJBE</t>
+          <t>BJFPMUNTXG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>45246402000532 - CENTER NORTE S/A CONSTRUCA</t>
+          <t>MIX SOLUCOES AMBIENTAIS LTDA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1480,12 +1488,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>660.525</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>660.525</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1495,7 +1503,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-14T16:10:10.258Z</t>
+          <t>2025-10-15T21:09:42.233Z</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1508,12 +1516,12 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-11-07T16:26:09.914Z</t>
+          <t>2025-10-08T21:12:33.362Z</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
+          <t>OTUxMWZiNzEtYjliOC00NTg4LWE5MTAtZmI2ZmQxZmZlZmNlOjU3MDE2</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1533,7 +1541,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>NDE3MTYzNjo1NzAxNg==</t>
+          <t>NDgzNDc2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1545,40 +1553,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BYCZRKIPEL</t>
+          <t>SY9I6QSJBE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>62730134620 - FRANCISCO DE LUCCA JUNIOR</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>GARANTIA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>garantia</t>
-        </is>
-      </c>
+          <t>45246402000532 - CENTER NORTE S/A CONSTRUCA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="b">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>660.525</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>530.25</t>
+          <t>660.525</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-10-17T12:48:39.389Z</t>
+          <t>2025-11-14T16:10:10.258Z</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1601,12 +1601,12 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2025-10-10T13:07:18.487Z</t>
+          <t>2025-11-07T16:26:09.914Z</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
+          <t>ZjA3NDk4MWMtM2JiMy00YjVkLTliNTgtYjE3ODFjNjczYmQzOjU3MDE2</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>NDgyMzMyODo1NzAxNg==</t>
+          <t>NDE3MTYzNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1638,27 +1638,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SYHCI3OLWE</t>
+          <t>BYCZRKIPEL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FRANCESCO DE TOMMASO</t>
+          <t>62730134620 - FRANCISCO DE LUCCA JUNIOR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+          <t>GARANTIA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+          <t>garantia</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1666,29 +1666,25 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1047.65</t>
+          <t>530.25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-11-24T15:13:20.559Z</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-24T14:45:19.000Z</t>
-        </is>
-      </c>
+          <t>2025-10-17T12:48:39.389Z</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
@@ -1698,12 +1694,12 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2025-11-17T15:14:20.735Z</t>
+          <t>2025-10-10T13:07:18.487Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+          <t>NGNkMDM2YWEtZDRlMy00NjIwLThiOGMtYmVmNGM1MGMyN2ZkOjU3MDE2</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1723,122 +1719,219 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>MzI2OTMyNjo1NzAxNg==</t>
+          <t>NDgyMzMyODo1NzAxNg==</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SYHCI3OLWE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FRANCESCO DE TOMMASO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>descriçao do problema:maquinba de 02 kilos, chegou com os conectores da resistencia queimados, comprometendo o aquecimento.</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1047.65</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1047.65</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Recusada</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2025-11-24T15:13:20.559Z</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-11-24T14:45:19.000Z</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-11-17T15:14:20.735Z</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>ODZlODFiMWItM2FiOC00YmY2LWJiOTktMTExOWE5YzVjMDBjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>MzI2OTMyNjo1NzAxNg==</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>SKD1SV5XZX</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>PREFEITURA MUNICIPAL DE ROSANA</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Referente a  transformação de 1 maquina composteira no valor total de R$ 3.000,00, de tensão 380V- trifasico, para 220V/trifasico. 
 As outras 02 são 220v</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="b">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="b">
         <v>0</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Expirada</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>2025-11-25T21:47:25.554Z</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>Adriana Vieira Masini</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>2025-11-18T21:53:35.934Z</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>NjYwZjY1NTAtNjFmZS00N2NmLTlmZTktMzY2ZWVjNmViZGJmOjU3MDE2</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>NTgwMDkyOTo1NzAxNg==</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>expired</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>HYS55O45GG</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Bayer Uberlandia</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1847,7 +1940,7 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -1856,106 +1949,17 @@
 OBSERVAÇAO IMPORTANTE : TECNICO NA UNIDADE PODEMOS REALIZAR O SERVIÇO HOJE</t>
         </is>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2025-09-09T14:06:34.278Z</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:09:17.339Z</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SKRTB67OEL</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Salobo 2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1965,20 +1969,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-08-15T18:25:59.379Z</t>
+          <t>2025-09-09T14:06:34.278Z</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Adriana Vieira Masini</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2025-08-08T18:27:17.728Z</t>
+          <t>2025-09-02T14:09:17.339Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1999,7 +2003,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyMzQxNzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2011,67 +2015,63 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HJCRTZS--G</t>
+          <t>SKRTB67OEL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>31415680817 - DOUGLAS HIROMITSU TFK 2Kg</t>
+          <t>Salobo 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Parafuso (Pino) que sustenta raspador quebrou, iremos fazer uma visita técnica para descobrir se há mais defeitos. 11 96619-3370</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-12-08T12:21:25.404Z</t>
+          <t>2025-08-15T18:25:59.379Z</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>douglas simao</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/6b2b07ff-cb70-450b-bc03-538da26b5fb0/signatures/82045e1d-cc6f-45af-a3f3-2c6a0906455d.png</t>
-        </is>
-      </c>
+          <t>RAFAEL BARBOZA</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-12-01T12:28:02.404Z</t>
+          <t>2025-08-08T18:27:17.728Z</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2092,34 +2092,34 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NDUwNzM2Mzo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SJBLZ0HQLG</t>
+          <t>HJCRTZS--G</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OUTBACK MORUMBI</t>
+          <t>31415680817 - DOUGLAS HIROMITSU TFK 2Kg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Reforma de Estufa Airflow danificada</t>
+          <t>Parafuso (Pino) que sustenta raspador quebrou, iremos fazer uma visita técnica para descobrir se há mais defeitos. 11 96619-3370</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -2128,42 +2128,46 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5996.77</t>
+          <t>484</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-09-15T22:01:12.237Z</t>
+          <t>2025-12-08T12:21:25.404Z</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>douglas simao</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/6b2b07ff-cb70-450b-bc03-538da26b5fb0/signatures/82045e1d-cc6f-45af-a3f3-2c6a0906455d.png</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-09-08T22:01:45.251Z</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-12-01T12:28:02.404Z</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2181,44 +2185,48 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
+          <t>NDUwNzM2Mzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>SJBLZ0HQLG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>OUTBACK MORUMBI</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Reforma de Estufa Airflow danificada</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="b">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>5996.77</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2228,7 +2236,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-09-15T22:01:12.237Z</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2241,12 +2249,12 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
+          <t>2025-09-08T22:01:45.251Z</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>ODA0YmUwYWMtMjQ5Ny00MGM4LTgxY2ItYzE2NjBhYzk4MmQxOjU3MDE2</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2266,7 +2274,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>NDIwNTU3Mjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2278,40 +2286,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2334,10 +2334,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2355,7 +2359,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2367,36 +2371,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R1R8PTIYBL</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>orçamento</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2406,7 +2414,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-11-10T19:48:40.136Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2419,14 +2427,10 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-11-03T19:49:41.839Z</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-28T16:05:56.490Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2444,7 +2448,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>NDgyMzkyMzo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2456,70 +2460,66 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>R1R8PTIYBL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>orçamento</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-11-10T19:48:40.136Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
+          <t>2025-11-03T19:49:41.839Z</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2527,88 +2527,92 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDgyMzkyMzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BJ0FAVCKBL</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Autorizado por João</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:58.539Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>jose da silva</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>HENRIQUE</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-11-06T15:28:06.348Z</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2023-05-31T21:56:50.448Z</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2616,44 +2620,44 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>BJ0FAVCKBL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>MAQUINA 01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>Autorizado por João</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -2662,46 +2666,42 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2025-11-13T15:27:58.539Z</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>rffccfc</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
-        </is>
-      </c>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-08-28T16:10:11.398Z</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>2025-11-06T15:28:06.348Z</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2719,67 +2719,79 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BKMVCD56XX</t>
+          <t>S1SWKWAKXG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>40.894999999999996</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-10-20T12:54:09.917Z</t>
+          <t>2025-09-04T16:07:52.834Z</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>rffccfc</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/970cf169-2b55-4eed-b7bc-c418d38522f4/signatures/7a22a671-9310-4602-ba1e-f1006682889f.png</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2025-10-13T13:10:02.576Z</t>
+          <t>2025-08-28T16:10:11.398Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2800,75 +2812,67 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>NDgyNTIyNjo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HYICEAM_GE</t>
+          <t>BKMVCD56XX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Compressores Salobo</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Substituição de 3 compressores</t>
-        </is>
-      </c>
+          <t>MARCOS ROBINSON MARTINS DE SOUZA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>40.894999999999996</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Recusada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-08-15T18:20:20.020Z</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>2025-08-08T18:24:47.000Z</t>
-        </is>
-      </c>
+          <t>2025-10-20T12:54:09.917Z</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>RAFAEL BARBOZA</t>
+          <t>Kaue Teixeira Caldeira Venâncio</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-08-08T18:23:10.037Z</t>
+          <t>2025-10-13T13:10:02.576Z</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2889,74 +2893,78 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>NDgzNTE2OTo1NzAxNg==</t>
+          <t>NDgyNTIyNjo1NzAxNg==</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SK7IYQDNA</t>
+          <t>HYICEAM_GE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Compressores Salobo</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Substituição de 3 compressores</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Recusada</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2024-09-12T20:48:10.536Z</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>2025-08-15T18:20:20.020Z</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2025-08-08T18:24:47.000Z</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Adriana Vieira Masini</t>
+          <t>RAFAEL BARBOZA</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2024-09-05T20:49:15.417Z</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Zjc2MWE3MWQtNDExOS00NDVmLWFkZmUtNzNlY2M3NmMwNGEyOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-08T18:23:10.037Z</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2974,196 +2982,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>NDIxMTExMTo1NzAxNg==</t>
+          <t>NDgzNTE2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>HJE6OUN5LE</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Bayer Uberlandia</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Cliente informa: equipamento nao gela
-Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
-Diagnostico do  tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo do  nitrogenio que vai utlizado + laudo de garrafa  maçarico e caneta (laudo )  para poder entrar com esses produtos para realizaçao do atendimento 
-senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Cliente informa: equipamento nao gela
-Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
-Diagnostico tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo nitrogenio, maçarico (laudo da garrafa) e caneta para poder entrar com esses produtos para realizaçao do atendimento 
-senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
-        </is>
-      </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2025-09-09T13:53:17.012Z</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2025-09-02T14:01:32.021Z</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>MTk4MjI5MTUtMDk1NC00NWFhLWE0NmEtMWJlMWZkYzdjMGVmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>NDgyMzQxNzo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>expired</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BYOHBAHQXX</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>OUTBACK MORUMBI</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Reforma de Estufa Airflow danificada</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>5996.77</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>5996.77</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Expirada</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2025-09-15T21:48:09.008Z</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Adriana Vieira Masini</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2025-09-08T21:59:15.256Z</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>NDIwNTU3Mjo1NzAxNg==</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>expired</t>
+          <t>refused</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3676,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NGRlMTM3N2EtNzUwNC00YmUyLThmZjItMDQxZTc1ZDNjODRiOjU3MDE2</t>
+          <t>Mzc3ZTNkYTUtZTdkZC00YjBlLWFmMjEtMjhhMDkzNDk0YzY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -3861,17 +3685,13 @@
       <c r="C17" t="n">
         <v>18025</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TROCADO EM GARANTIA</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3889,14 +3709,14 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NmQ1MDliODYtNGYyYy00YTNiLTk1YWEtYmM0MTZhNDBkNTY1OjU3MDE2</t>
+          <t>Njc1OGZkOTMtZmI5Ny00NDJiLWI1NzItOWE5OTYxYTgzMzE3OjU3MDE2</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -3905,17 +3725,13 @@
       <c r="C18" t="n">
         <v>350</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TROCADO EM GARANTIA</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3933,38 +3749,38 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MDFmODQ2OWUtMmMyMC00NzEwLWE4NTEtMmFkOWFjYjRlYjQ2OjU3MDE2</t>
+          <t>ZGZmZDFlYzMtNGE2Yi00YzFhLWI3YmYtM2Y5ZjBhMjhlMTIwOjU3MDE2</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
+        <v>1086</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NDUwZmFlOTEtODg1My00ZTcwLWIwOTgtZWM2Nzc3MzgzNjgyOjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>50</v>
+        <v>1086</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3973,78 +3789,82 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MjhmNDNmYjAtZjgzMi00MThiLWEyNTAtZWVlODc0ZjQxYzliOjU3MDE2</t>
+          <t>ZjRkMzBkN2ItMTVhNC00MGI0LWI0N2MtYzcyM2QzM2U3ZDkyOjU3MDE2</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1365</v>
+        <v>350</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1365</v>
+        <v>350</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MmVmNGI5OTItYjEwZC00ZTQyLTg5MTgtMDViOTJhNTc1MTI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MmQyOGU2OWYtM2IzOS00ZjYwLWJmYTctYmViYTY2M2UxNzdjOjU3MDE2</t>
+          <t>NGRlMTM3N2EtNzUwNC00YmUyLThmZjItMDQxZTc1ZDNjODRiOjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>375</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>18025</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TROCADO EM GARANTIA</t>
+        </is>
+      </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>375</v>
+        <v>18025</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -4053,38 +3873,42 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MzVjNDRmYjctMTI1My00NDg3LThlNmUtOWZhN2YyYWMyNjg3OjU3MDE2</t>
+          <t>NmQ1MDliODYtNGYyYy00YTNiLTk1YWEtYmM0MTZhNDBkNTY1OjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1.152e+16</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TROCADO EM GARANTIA</t>
+        </is>
+      </c>
       <c r="E22" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NDM0MjA4NTAtZjAwOC00YzMyLWJlM2QtODFlMzljMjE0OTk4OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.152e+16</v>
+        <v>350</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -4093,21 +3917,21 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
+          <t>MzIzZWEzMjQtNDVjMi00Zjg5LTg0NmUtYzBiZjYwMTE4NjhiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NDNkMGNjZmMtMjFmMS00NjQyLWI4OWYtYTk4ODg2NjkxMjcwOjU3MDE2</t>
+          <t>MDFmODQ2OWUtMmMyMC00NzEwLWE4NTEtMmFkOWFjYjRlYjQ2OjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
@@ -4120,15 +3944,15 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+          <t>NDUwZmFlOTEtODg1My00ZTcwLWIwOTgtZWM2Nzc3MzgzNjgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4140,14 +3964,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NDRlYzI5NjAtMTZmYi00MzM3LWEzZTEtNGJmOTg0Y2Y1MzFhOjU3MDE2</t>
+          <t>MjhmNDNmYjAtZjgzMi00MThiLWEyNTAtZWVlODc0ZjQxYzliOjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>700</v>
+        <v>1365</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
@@ -4160,15 +3984,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>350</v>
+        <v>1365</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4180,14 +4004,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N2NjNjliYTAtNTVlZi00NjNmLThkMmUtZGMzYzIyZjRhM2FiOjU3MDE2</t>
+          <t>MmQyOGU2OWYtM2IzOS00ZjYwLWJmYTctYmViYTY2M2UxNzdjOjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
@@ -4200,11 +4024,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -4220,14 +4044,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OTg0ZDY5MWUtZTJiZS00NmM0LTg1OGMtNDQ1ZTMwMmY2MWE3OjU3MDE2</t>
+          <t>MzVjNDRmYjctMTI1My00NDg3LThlNmUtOWZhN2YyYWMyNjg3OjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>85</v>
+        <v>1.152e+16</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
@@ -4240,11 +4064,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>NDM0MjA4NTAtZjAwOC00YzMyLWJlM2QtODFlMzljMjE0OTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>85</v>
+        <v>1.152e+16</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -4260,14 +4084,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OWRkMWJkNWQtMjE5Yy00OTY0LWExNzYtZTI4YzkyN2Q4ODdlOjU3MDE2</t>
+          <t>NDNkMGNjZmMtMjFmMS00NjQyLWI4OWYtYTk4ODg2NjkxMjcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="C27" t="n">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
@@ -4280,15 +4104,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Y2FjZGRiY2YtOTQ5NS00NDIyLWE4ODctYjk4ZGUxNjU1MzMyOjU3MDE2</t>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4300,14 +4124,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>YTAxNDZjNzgtMDljZi00ZGQ4LTkwOTItZmM5N2QyNzM3MGEwOjU3MDE2</t>
+          <t>NDRlYzI5NjAtMTZmYi00MzM3LWEzZTEtNGJmOTg0Y2Y1MzFhOjU3MDE2</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>18025</v>
+        <v>700</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
@@ -4320,15 +4144,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4340,14 +4164,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>YTM1YmFkNmQtN2EzNS00Njk0LTliNTMtNmZiMjAwNzQ5NzFkOjU3MDE2</t>
+          <t>N2NjNjliYTAtNTVlZi00NjNmLThkMmUtZGMzYzIyZjRhM2FiOjU3MDE2</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>25625</v>
+        <v>350</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
@@ -4360,11 +4184,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MTdjYWQ5ZTAtMmQ3YS00OTM0LWIyOGEtYzMxYjY1ODZkNDIzOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>25625</v>
+        <v>350</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4380,14 +4204,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>YzFlYTExODctMmJkNy00N2RhLThiMTQtZTVjMTY0NWY1Y2Y5OjU3MDE2</t>
+          <t>OTg0ZDY5MWUtZTJiZS00NmM0LTg1OGMtNDQ1ZTMwMmY2MWE3OjU3MDE2</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>182225</v>
+        <v>85</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
@@ -4400,11 +4224,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>OWU3NmYwYWEtZWNhZi00YTBiLWE2NTUtNjE5NTkwNDIwZDNjOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>182225</v>
+        <v>85</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4420,14 +4244,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>YzRiYzAxZjEtOWY2Zi00ZWQ0LWJmMjgtZmYxY2RjNjY1OTBiOjU3MDE2</t>
+          <t>OWRkMWJkNWQtMjE5Yy00OTY0LWExNzYtZTI4YzkyN2Q4ODdlOjU3MDE2</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>9940000000000000</v>
+        <v>72</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
@@ -4440,11 +4264,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>OWMxNWU5ZjUtOWI3Ny00ZmYyLWExMWYtM2RkYzA3ZWFjYzU5OjU3MDE2</t>
+          <t>Y2FjZGRiY2YtOTQ5NS00NDIyLWE4ODctYjk4ZGUxNjU1MzMyOjU3MDE2</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>9940000000000000</v>
+        <v>18</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4460,14 +4284,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ZGMxMDhlMDAtNmY3Ni00OWE1LTg0MDMtZjVmNjUyZGVkNzZlOjU3MDE2</t>
+          <t>YTAxNDZjNzgtMDljZi00ZGQ4LTkwOTItZmM5N2QyNzM3MGEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>2073</v>
+        <v>18025</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
@@ -4480,11 +4304,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2073</v>
+        <v>18025</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -4500,14 +4324,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ZjczNzc1Y2UtNGU2Mi00NGEzLTk5NWUtYzRlZmRjMzFhMTI2OjU3MDE2</t>
+          <t>YTM1YmFkNmQtN2EzNS00Njk0LTliNTMtNmZiMjAwNzQ5NzFkOjU3MDE2</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>36</v>
+        <v>25625</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
@@ -4520,11 +4344,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ZmQ5YTY2ZWEtZDM4NS00MWMwLWI0NWYtODI3ZjAxNzRjNzE1OjU3MDE2</t>
+          <t>MTdjYWQ5ZTAtMmQ3YS00OTM0LWIyOGEtYzMxYjY1ODZkNDIzOjU3MDE2</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>9</v>
+        <v>25625</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -4540,14 +4364,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ZmQ3OWNiYjEtZmY3Yi00MjVkLWJhODgtYjA3NjQyZWY1MzYwOjU3MDE2</t>
+          <t>YzFlYTExODctMmJkNy00N2RhLThiMTQtZTVjMTY0NWY1Y2Y5OjU3MDE2</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>1578</v>
+        <v>182225</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
@@ -4560,11 +4384,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Y2I2NzA1MTItNDc5NS00ZWVmLWJkOTktY2JlZmJiZTNmNTFlOjU3MDE2</t>
+          <t>OWU3NmYwYWEtZWNhZi00YTBiLWE2NTUtNjE5NTkwNDIwZDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1578</v>
+        <v>182225</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -4580,71 +4404,71 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MTE0NDUwMGUtM2ZiMi00OWQ1LWFmY2EtMzNjNzZmNjBhMTVmOjU3MDE2</t>
+          <t>YzRiYzAxZjEtOWY2Zi00ZWQ0LWJmMjgtZmYxY2RjNjY1OTBiOjU3MDE2</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>350</v>
+        <v>9940000000000000</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>OWMxNWU5ZjUtOWI3Ny00ZmYyLWExMWYtM2RkYzA3ZWFjYzU5OjU3MDE2</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>350</v>
+        <v>9940000000000000</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NWM5YzAxYzktMTIwMS00ZjhkLWJjOGMtN2U3NDlmOTlmMzRkOjU3MDE2</t>
+          <t>ZGMxMDhlMDAtNmY3Ni00OWE1LTg0MDMtZjVmNjUyZGVkNzZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>85</v>
+        <v>2073</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -4653,38 +4477,38 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NjRmMDVhODItNmU2Mi00ZDRhLTk5NmItNzM2ODI0YjE2MjRmOjU3MDE2</t>
+          <t>ZjczNzc1Y2UtNGU2Mi00NGEzLTk5NWUtYzRlZmRjMzFhMTI2OjU3MDE2</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>1365</v>
+        <v>36</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
+          <t>ZmQ5YTY2ZWEtZDM4NS00MWMwLWI0NWYtODI3ZjAxNzRjNzE1OjU3MDE2</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1365</v>
+        <v>9</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4693,38 +4517,38 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OGUzMjVkZDYtOTA3Yi00MjFjLWFjYzgtOWVlMGI3MjJkNjIzOjU3MDE2</t>
+          <t>ZmQ3OWNiYjEtZmY3Yi00MjVkLWJhODgtYjA3NjQyZWY1MzYwOjU3MDE2</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>350</v>
+        <v>1578</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>Y2I2NzA1MTItNDc5NS00ZWVmLWJkOTktY2JlZmJiZTNmNTFlOjU3MDE2</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>350</v>
+        <v>1578</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4733,21 +4557,21 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
+          <t>MzM2Mjc5YTMtZTM5Ny00M2RkLWIzZWYtOGQwZjY3N2U5N2FmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Yjk2YzIwMDktMzVkMy00ZGRjLWIwOTYtOTJjOWFlMjZiM2FhOjU3MDE2</t>
+          <t>MTE0NDUwMGUtM2ZiMi00OWQ1LWFmY2EtMzNjNzZmNjBhMTVmOjU3MDE2</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
@@ -4760,15 +4584,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4780,14 +4604,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ZTA0MDdkOTgtNjJjMi00ZTgyLWFmMzEtYzg4MzdkYzhjYmMzOjU3MDE2</t>
+          <t>NWM5YzAxYzktMTIwMS00ZjhkLWJjOGMtN2U3NDlmOTlmMzRkOjU3MDE2</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>2073</v>
+        <v>85</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
@@ -4800,11 +4624,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2073</v>
+        <v>85</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4820,31 +4644,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MDhmZjQ1YWQtNTY2Yi00YTlkLWIyMWEtZDI5Y2RkYThlODAwOjU3MDE2</t>
+          <t>NjRmMDVhODItNmU2Mi00ZDRhLTk5NmItNzM2ODI0YjE2MjRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>1365</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>NTU4NzNjNDctNjRiZS00YmQ3LWI0MjQtYTU3OTAxNmE0MzQzOjU3MDE2</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>1365</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4853,38 +4677,38 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>N2EyYTQzZjktNzgxZi00Mzk2LWEyNzMtODM0NmViMTE4MWE2OjU3MDE2</t>
+          <t>OGUzMjVkZDYtOTA3Yi00MjFjLWFjYzgtOWVlMGI3MjJkNjIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4893,78 +4717,78 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OWIyYjYwOTktYTg5MC00ZjRhLWEzOGMtNDI3YTE2MTA1NTI1OjU3MDE2</t>
+          <t>Yjk2YzIwMDktMzVkMy00ZGRjLWIwOTYtOTJjOWFlMjZiM2FhOjU3MDE2</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>700</v>
+        <v>375</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>YTJjM2ExNTAtOWExYi00Mzk1LWE1N2MtM2JkYTU3MDBiMzhlOjU3MDE2</t>
+          <t>ZTA0MDdkOTgtNjJjMi00ZTgyLWFmMzEtYzg4MzdkYzhjYmMzOjU3MDE2</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>375</v>
+        <v>2073</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>375</v>
+        <v>2073</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4973,21 +4797,21 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
+          <t>M2UzNjc5MDgtNWI5Yy00MzNkLWFjMjEtZTMzZWU5NDhkZDNmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>YTYxMjU3ODEtZjY4ZS00MDQyLTg5YmItYzg1YTA3YTdmZmY5OjU3MDE2</t>
+          <t>MDhmZjQ1YWQtNTY2Yi00YTlkLWIyMWEtZDI5Y2RkYThlODAwOjU3MDE2</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>350</v>
+        <v>9</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
@@ -5000,11 +4824,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>350</v>
+        <v>9</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -5020,14 +4844,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>YTg1ZmQyOGMtNDZkOC00YTgwLWJhODUtOGI5OTA5ZDliZjg1OjU3MDE2</t>
+          <t>N2EyYTQzZjktNzgxZi00Mzk2LWEyNzMtODM0NmViMTE4MWE2OjU3MDE2</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>8399999999999999</v>
+        <v>85</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
@@ -5040,11 +4864,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8399999999999999</v>
+        <v>85</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -5060,14 +4884,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>YTlhNDQ1NWItMWI4OS00ZGM0LThiOTgtMzZlOTcxNTE0NzcyOjU3MDE2</t>
+          <t>OWIyYjYwOTktYTg5MC00ZjRhLWEzOGMtNDI3YTE2MTA1NTI1OjU3MDE2</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>2073</v>
+        <v>700</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
@@ -5080,15 +4904,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2073</v>
+        <v>350</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5100,14 +4924,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ZTZmYzJiNjEtYzBjNS00NjM2LWI0YmEtNzZlMGE1NWI2ODIwOjU3MDE2</t>
+          <t>YTJjM2ExNTAtOWExYi00Mzk1LWE1N2MtM2JkYTU3MDBiMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>2502</v>
+        <v>375</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
@@ -5120,11 +4944,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2502</v>
+        <v>375</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5140,14 +4964,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ZWQ1NDY3MTUtZjAxMC00OTM2LTljZDctNzBmMjRlZjVhYTQwOjU3MDE2</t>
+          <t>YTYxMjU3ODEtZjY4ZS00MDQyLTg5YmItYzg1YTA3YTdmZmY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>6325</v>
+        <v>350</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
@@ -5160,11 +4984,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>6325</v>
+        <v>350</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5180,31 +5004,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NjA1ZWIxZDMtNWMxMC00NGE2LWEzZjEtYTZkZjM1MWVhNjQwOjU3MDE2</t>
+          <t>YTg1ZmQyOGMtNDZkOC00YTgwLWJhODUtOGI5OTA5ZDliZjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>1793</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NjdjMzI5NDAtMmU1Mi00MjQ1LTgxNGQtNjUyNWI3ZTQyNDU4OjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1793</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5213,82 +5037,78 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OTFkMjc2ZDEtOTkxOC00OGZlLWEyMWYtZGEwNDg3MDFiNzkxOjU3MDE2</t>
+          <t>YTlhNDQ1NWItMWI4OS00ZGM0LThiOTgtMzZlOTcxNTE0NzcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>350</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Hora de trabalho ECO</t>
-        </is>
-      </c>
+        <v>2073</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>350</v>
+        <v>2073</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>YTlhMGVhYzMtYjJhZS00OWUwLTg5YWQtNjdjYzIyMWUyZDZmOjU3MDE2</t>
+          <t>ZTZmYzJiNjEtYzBjNS00NjM2LWI0YmEtNzZlMGE1NWI2ODIwOjU3MDE2</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>2841</v>
+        <v>2502</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MGQ3YTYzZmEtOGQyZS00YWNiLTljMWYtNTNiM2JkMzRmOTYwOjU3MDE2</t>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2841</v>
+        <v>2502</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5297,38 +5117,38 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>YmUzOThhOTAtNGYyYi00YmViLWJmYzUtNDJmYTA2NDg0OGRhOjU3MDE2</t>
+          <t>ZWQ1NDY3MTUtZjAxMC00OTM2LTljZDctNzBmMjRlZjVhYTQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>660525</v>
+        <v>6325</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MGY5YWI3Y2UtNWJiMC00ZWMwLTgyZjktNzU4Zjc0YmUyZDg3OjU3MDE2</t>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>660525</v>
+        <v>6325</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5337,38 +5157,38 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
+          <t>M2Y2OThhZjYtNWNmYi00NTAxLWE2OGMtMjVkMjAyM2I0MTk5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MjA0Mzk0M2ItOWI2Ni00Y2NkLWJlNjgtOTUwNjdmMjVkM2Y3OjU3MDE2</t>
+          <t>NjA1ZWIxZDMtNWMxMC00NGE2LWEzZjEtYTZkZjM1MWVhNjQwOjU3MDE2</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>350</v>
+        <v>1793</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>NjdjMzI5NDAtMmU1Mi00MjQ1LTgxNGQtNjUyNWI3ZTQyNDU4OjU3MDE2</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>350</v>
+        <v>1793</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5377,78 +5197,82 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NDUwYmZhOGUtMTA3Ni00MmY2LWFhMjgtNWY5YzNmNzMzMWQ1OjU3MDE2</t>
+          <t>OTFkMjc2ZDEtOTkxOC00OGZlLWEyMWYtZGEwNDg3MDFiNzkxOjU3MDE2</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>18025</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+        <v>350</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Hora de trabalho ECO</t>
+        </is>
+      </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>ODY3OTE5NTMtMDdjZi00YzM1LThkN2QtNDc5NzNmNzVkMGY0OjU3MDE2</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MTY2NjMxNTAtYWUyMi00YzY2LTgwNDYtYTkzZTgzODgxNGQ4OjU3MDE2</t>
+          <t>YTlhMGVhYzMtYjJhZS00OWUwLTg5YWQtNjdjYzIyMWUyZDZmOjU3MDE2</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>350</v>
+        <v>2841</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MGQ3YTYzZmEtOGQyZS00YWNiLTljMWYtNTNiM2JkMzRmOTYwOjU3MDE2</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>350</v>
+        <v>2841</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -5457,38 +5281,38 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NTUzNzQwNTMtYmRmMC00ZDAxLWI5ZjgtOGMyOTQzNjMyZDRmOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MWM2N2JjOTQtYTFlYy00YjM5LTg5MjctNThkNjNhNGVkNWRkOjU3MDE2</t>
+          <t>YmUzOThhOTAtNGYyYi00YmViLWJmYzUtNDJmYTA2NDg0OGRhOjU3MDE2</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>1086</v>
+        <v>660525</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
+          <t>MGY5YWI3Y2UtNWJiMC00ZWMwLTgyZjktNzU4Zjc0YmUyZDg3OjU3MDE2</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1086</v>
+        <v>660525</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -5497,14 +5321,14 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NWU0M2UwNjgtNTI4MS00M2VmLWE5OTQtM2U2NWMzZjA4MDI5OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NjYzOTVlNjEtODVjOC00YmY4LTljNjEtODljNGZjNDM5OWY2OjU3MDE2</t>
+          <t>MjA0Mzk0M2ItOWI2Ni00Y2NkLWJlNjgtOTUwNjdmMjVkM2Y3OjU3MDE2</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -5515,16 +5339,16 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -5532,43 +5356,43 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NmY5NWU4YjctMTU4NC00NzJiLTgwODctMjkyYjg3NGY5ODU3OjU3MDE2</t>
+          <t>NDUwYmZhOGUtMTA3Ni00MmY2LWFhMjgtNWY5YzNmNzMzMWQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>3795</v>
+        <v>18025</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3795</v>
+        <v>18025</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -5577,21 +5401,21 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+          <t>NjJlMTYyODUtMGFiYi00NTE5LWE3ZTItYTJmNzNiOGU4OTE1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Yzg5MTQ4NTgtZjZhZS00M2VjLWI2OGItNGY0ZTA3YzYwM2E4OjU3MDE2</t>
+          <t>MTY2NjMxNTAtYWUyMi00YzY2LTgwNDYtYTkzZTgzODgxNGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
@@ -5604,11 +5428,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>18025</v>
+        <v>350</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5624,14 +5448,14 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ZGI4ODAzMmQtZTAzYS00YmQ5LWJmMjUtNjk1ZGUwODliNzI1OjU3MDE2</t>
+          <t>MWM2N2JjOTQtYTFlYy00YjM5LTg5MjctNThkNjNhNGVkNWRkOjU3MDE2</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>1.68e+16</v>
+        <v>1086</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
@@ -5644,11 +5468,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+          <t>ZTg4NmFmNzYtZDE1OS00MWU1LWE3MjItYmFiYzg4MjcxM2Q3OjU3MDE2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>2.1e+16</v>
+        <v>1086</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5664,14 +5488,14 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ZjQ5NjJjZjctN2U2ZS00ZWE3LTkwY2ItZWIxNjFlODE2YzNkOjU3MDE2</t>
+          <t>NjYzOTVlNjEtODVjOC00YmY4LTljNjEtODljNGZjNDM5OWY2OjU3MDE2</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>4050000000000001</v>
+        <v>350</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
@@ -5684,15 +5508,15 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4050000000000001</v>
+        <v>350</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5704,60 +5528,220 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MzkwMmU1MjMtZGQ5ZC00ZjEzLWIxZjItNTM4MThiODRhODY0OjU3MDE2</t>
+          <t>NmY5NWU4YjctMTU4NC00NzJiLTgwODctMjkyYjg3NGY5ODU3OjU3MDE2</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Transformaçao 380V- trifasico, para 220V/trifasico</t>
-        </is>
-      </c>
+        <v>3795</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>NDk0NTM0YTgtOGM0MC00ZTYwLWJhNDAtMzMxNDRiZjA3ZGY4OjU3MDE2</t>
+          <t>YTk2YTY5MTAtZjgyNy00YTNjLWIzNGYtZTg1NDljMTRkMGE0OjU3MDE2</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>3000</v>
+        <v>3795</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>Yzg5MTQ4NTgtZjZhZS00M2VjLWI2OGItNGY0ZTA3YzYwM2E4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>18025</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>8</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>MWNjNzU5N2QtZWQ0ZC00MmZmLWI0ODQtMDRhMzJjMTAyYzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>18025</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ZGI4ODAzMmQtZTAzYS00YmQ5LWJmMjUtNjk1ZGUwODliNzI1OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>8</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1.68e+16</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>8</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>NTE3OTY1NTMtNjNjYi00YjM4LWJhZTctOTI3OTNkNmRkZTUzOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>2.1e+16</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ZjQ5NjJjZjctN2U2ZS00ZWE3LTkwY2ItZWIxNjFlODE2YzNkOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="n">
+        <v>4050000000000001</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>8</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NjhhMzA2MDktZmIwZC00YzgxLWFiZmEtZGI0YTk1MzJjNWNiOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>4050000000000001</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>NjJlZTc1ZWItYTk4ZS00YmEzLWIwYmMtYjIzMzQ5OGJhZDNlOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MzkwMmU1MjMtZGQ5ZC00ZjEzLWIxZjItNTM4MThiODRhODY0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Transformaçao 380V- trifasico, para 220V/trifasico</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>NDk0NTM0YTgtOGM0MC00ZTYwLWJhNDAtMzMxNDRiZjA3ZGY4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>NjQxYmI0ZjMtNTE3YS00NjM4LTg0NjktY2Y5ZGExODcxMzc4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>YzM2MGY4YjEtODQ0Ny00MGFkLThjNDEtYzNlN2Q5ZjAyODExOjU3MDE2</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" t="n">
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
         <v>1700</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Cliente informa: equipamento nao gela
 Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
@@ -5765,214 +5749,214 @@
 senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E68" t="n">
         <v>2</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
         </is>
       </c>
-      <c r="H64" t="n">
+      <c r="H68" t="n">
         <v>1700</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>NjRhMDExNzktM2U5Zi00ODkzLTljNTQtMDczYzVmNzA2MjY0OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" t="n">
-        <v>47370</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="n">
-        <v>2</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>47370</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>NzVmMDU4ODAtZTJiMi00MmFlLTgzZmItYTJlYmYwY2EyNTgxOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>67</v>
-      </c>
-      <c r="C66" t="n">
-        <v>134</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>67Km de distancia</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>3</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>2</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>ZDQ0NDkzNjgtNjE2MS00YjRkLWEyNWUtOTdkOGFiMjFiMjVjOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" t="n">
-        <v>350</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Visita técnica</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>3</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>NWVmNmQ0MDEtNzBmMy00Yzg3LWFlZDAtYzJiYTM1MTc4OWNlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>350</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="n">
-        <v>3</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>NTMxNmNjMTEtNGYzNi00NjE5LTliZGMtMWNmYWJkNDlkNGJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>47370</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>47370</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>NjZkZDVhODgtZDIwMy00MTg5LWEwNGQtODg3ODU1YmM2ZWE2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>NzVmMDU4ODAtZTJiMi00MmFlLTgzZmItYTJlYmYwY2EyNTgxOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>67</v>
+      </c>
+      <c r="C70" t="n">
+        <v>134</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>67Km de distancia</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Zjc3ODdmZmQtNzZiNy00ZjNmLThmNjQtNjdjOGIyOGYxYzUwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ZDQ0NDkzNjgtNjE2MS00YjRkLWEyNWUtOTdkOGFiMjFiMjVjOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>350</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Visita técnica</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>NWVmNmQ0MDEtNzBmMy00Yzg3LWFlZDAtYzJiYTM1MTc4OWNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>350</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>NmIyYjA3ZmYtY2I3MC00NTBiLWJjMDMtNTM4ZGEyNmI1ZmIwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MjE4NjI1MWMtYzQ0OC00NWUwLTk4NjUtMWUyNTYyYmM4MWNlOjU3MDE2</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>M2ZjODg2ZTctOTVmYS00ZWE0LWJlZDItZDdlYzVkZDJjMjE5OjU3MDE2</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" t="n">
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
         <v>494677</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
 B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
@@ -5990,204 +5974,44 @@
 B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="E73" t="n">
         <v>3</v>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
         </is>
       </c>
-      <c r="H69" t="n">
+      <c r="H73" t="n">
         <v>494677</v>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t>NmM0Y2U5ZmItMzc5OC00MDMyLTkwMmUtZTA4OWZmMTBlNTA4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" t="n">
-        <v>350</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="n">
-        <v>6</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>350</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="n">
-        <v>6</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>2073</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" t="n">
-        <v>7375</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="n">
-        <v>6</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>7375</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="n">
-        <v>6</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>8399999999999999</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
+          <t>MGYzOGViYmMtMzAzZS00YTQwLTkwYmYtYmU1NzBjNDFhNmEyOjU3MDE2</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
@@ -6200,15 +6024,15 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6220,119 +6044,111 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
+          <t>OGJlZDhhMDktNjc5Ny00ZTAzLTllNTctMjE2OTRjMmIyYjU5OjU3MDE2</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>680</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>2073</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>680</v>
+        <v>2073</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
+          <t>YzllZjAzNWYtNTBiZi00ZjhhLTgyZGQtZTRkNjE5NmJlYWZlOjU3MDE2</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>855</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>7375</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>ZGRlNDk5MWMtYjg3Ny00N2MzLWE2MDgtNjc3MWVhODJjYjlhOjU3MDE2</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>855</v>
+        <v>7375</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
+          <t>ZTY4MjlkMDUtNTM3ZC00MmM2LWE2MDgtZjVkZmE0YzNhY2RjOjU3MDE2</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>43</v>
+        <v>8399999999999999</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>43</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6341,38 +6157,38 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
+          <t>ZmI1OWM5MTktNzVjYi00ZTYzLWE4MDAtMjkzNjA2OGY4NGQ4OjU3MDE2</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>85</v>
+        <v>375</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6381,122 +6197,126 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
+          <t>NTIzYmQ3M2MtMzQwOC00ZTM3LWJhYzctZDM2YzZjYjg0NjY5OjU3MDE2</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>350</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>350</v>
+        <v>680</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
+          <t>NjU4NTlmOGEtZWM4NC00NGE1LTliMmQtNzcwMzRkOTI0ZDMwOjU3MDE2</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>10000</v>
+        <v>855</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>10000</v>
+        <v>855</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
+          <t>YjRlNDcxNDUtMmEwZi00ZmEzLTlhODktMGYzNDdiZWFkNWEwOjU3MDE2</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
+          <t>MTZhMTdiZDUtYWI4OC00NjYwLTk2OGUtOWE4YmRiY2JmYTcyOjU3MDE2</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6505,38 +6325,38 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
+          <t>Y2IyMzg4Y2YtNDk4Yy00YjdmLWIwNzEtMmZhZGY1Mzk3YzRmOjU3MDE2</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>6325</v>
+        <v>85</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>6325</v>
+        <v>85</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -6545,38 +6365,38 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
+          <t>Y2Y0OGNkYzUtMGU3NS00MWM4LThkNzYtZDhhMDEyYjQ3NDNjOjU3MDE2</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6585,38 +6405,42 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
+          <t>M2FhZjdjZGYtYzBiNi00NjU1LWFjODAtMGViN2NhY2QzZWVjOjU3MDE2</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>350</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>REFRIGERADOR HORIZONTAL TOPEMA - GENÉRICO</t>
+        </is>
+      </c>
       <c r="E84" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
+          <t>MjE5MDBkYzItODI3ZS00YjYwLWJiNjgtYjQ0NWVlMDExOWUzOjU3MDE2</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>350</v>
+        <v>10000</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6625,21 +6449,21 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
+          <t>MGE2M2VmNWItNjRiZS00NjI4LTg1NjYtN2ZkNDY0NDJjMzhlOjU3MDE2</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>2502</v>
+        <v>9</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
@@ -6652,11 +6476,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
+          <t>YjEzMmNlNWQtOGU2Ny00NmIwLWJiYzMtNDk0Zjg1YzMyNGIyOjU3MDE2</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>2502</v>
+        <v>9</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6672,14 +6496,14 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
+          <t>MmRkOWE2OTYtMzQyNy00Y2M5LWJkNDMtNjNlMDNjYjQ2MDcyOjU3MDE2</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>8399999999999999</v>
+        <v>6325</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
@@ -6692,11 +6516,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
+          <t>Y2QzOGQ2YTYtNmYwMi00NGI3LTg1NmQtOTc2MjE0MzI0YmJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>8399999999999999</v>
+        <v>6325</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6712,14 +6536,14 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
+          <t>NjM3YjhiNTEtYzE0Ni00MTFlLTk0YmYtNzJlOGU5NGM2ZDA1OjU3MDE2</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>2073</v>
+        <v>375</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
@@ -6732,11 +6556,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
+          <t>MWFlNGQzYzItOWIxNC00YmQ1LTk2MmUtOWIwYjU2MmQ1OGQ1OjU3MDE2</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>2073</v>
+        <v>375</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6752,14 +6576,14 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
+          <t>N2VhYTkxZjQtMDU2ZC00MWE2LWIzMmYtMmFlYjVjZjMxMDhiOjU3MDE2</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
@@ -6772,11 +6596,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
+          <t>ODgyNmUxMWUtNWIyYy00NWFjLWE1ZWMtZDY3ZjVkNDg3M2E1OjU3MDE2</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6792,14 +6616,14 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
+          <t>YjJmN2E4MGUtODk1MC00OWQ0LTlhODMtOTMwYmVmNTRmNmIyOjU3MDE2</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>700</v>
+        <v>2502</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
@@ -6812,15 +6636,15 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
+          <t>YjRiNzk0MjYtYzkxMi00MTA0LWJkZTgtMmExNTJhMTJlYWNkOjU3MDE2</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>350</v>
+        <v>2502</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6832,119 +6656,111 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
+          <t>Y2Y3MmE5YTctNjc4MS00ZTMyLWE1OTctNDhmMmI0MWI2ZWYyOjU3MDE2</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>680</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
-        </is>
-      </c>
+        <v>8399999999999999</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
+          <t>MmY2Nzk2OGUtMDNlOC00MzZlLTk0ZjAtZTE1ODNmMDk3OTJiOjU3MDE2</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>680</v>
+        <v>8399999999999999</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
+          <t>ZDNhMWQ1YmItYjhjNy00MjA3LWI0YzgtNjU0NDJjZWQ0ZTZjOjU3MDE2</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>855</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
-        </is>
-      </c>
+        <v>2073</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
+          <t>YWZlNTgwOGEtNGJiZi00MDc3LTg1ZGMtMDBiNGU3MDcwNDgyOjU3MDE2</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>855</v>
+        <v>2073</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
+          <t>ZjE0ZTc0MjQtNTIzOC00ODE2LTkzMzYtNjhlZjU3Zjg3MTcwOjU3MDE2</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
+          <t>ZmJiMmM5MWQtMmQ1My00ZmUzLTljNjAtZjNiOTljZDMzZDc3OjU3MDE2</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6953,141 +6769,149 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
+          <t>ZjY2ZjQxZmYtODllOC00ZTcyLTg2YmYtZDRmYWYxMzdmZGIzOjU3MDE2</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>6000000000000001</v>
+        <v>700</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
+          <t>YmJmNjhlOWMtMWYyMS00MTVlLWI5MzctN2NmMDNhNDY5OWFkOjU3MDE2</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>6000000000000001</v>
+        <v>350</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
+          <t>NTMwYmZhMDQtZGU2Ny00ZmFlLWE2NmItNmM5YzMxODdiZTgwOjU3MDE2</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>3.8825e+16</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
+        <v>680</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>WRVT.00021 REALIZADO SERVIÇO LIMPEZA E CARGA DE GAS  R$680,00</t>
+        </is>
+      </c>
       <c r="E94" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
+          <t>NWIwZWFlMmYtYjVkOC00NTU0LTkzZmYtZGM2ZGIwM2E1ZmEwOjU3MDE2</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>3.8825e+16</v>
+        <v>680</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
+          <t>ZTFiNzY1Y2MtNTVhMS00NDU4LTliMmMtMTU3MzM1ZjU5ZTA4OjU3MDE2</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>2.1e+16</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
+        <v>855</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>WRVT.00020  REALIZADO RECUPERAÇAO DA ESTAÇAO MICRO MOTOR  E REALIZADO LIMPEZA  NO SISTEMA E CARGA DE GAS</t>
+        </is>
+      </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
+          <t>MWY3MGI1MWUtZWEwMC00YWEyLTgzZTItNDgwYzc2NzE1OTJkOjU3MDE2</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>2.1e+16</v>
+        <v>855</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>service</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
+          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
+          <t>NGM4MjM2YzAtZWJkZC00NTY1LWFkNGEtNjBiYzEwYzVlMjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96" t="n">
-        <v>3e+16</v>
+        <v>96</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
@@ -7100,11 +6924,11 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
+          <t>ODcwZTI1ZDEtMTRkNC00M2IyLTk0MTItOGJhNDdiYzIzMjg1OjU3MDE2</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>3e+16</v>
+        <v>48</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7120,75 +6944,71 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
+          <t>NmJjNjE2Y2UtOGFjZi00OTdiLTgyMWEtYTI4NmMzMDA1MjViOjU3MDE2</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>47370</v>
+        <v>6000000000000001</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
+          <t>OTgxYjZlMTAtNGZiMy00YjAwLWI4OTYtMTcxNGM5MTg2Y2NiOjU3MDE2</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>47370</v>
+        <v>6000000000000001</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>YjM4ZTVhZWEtZWNmYi00NjFjLTljYzAtYmU1YjRmMjcyNzA2OjU3MDE2</t>
+          <t>YTYwMTIwMzItNGMzNy00MGYyLThiMjktY2FhNjAzZTljY2YyOjU3MDE2</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>ORCAMENTO REALIZADO PELO BLING</t>
-        </is>
-      </c>
+        <v>3.8825e+16</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>YTU2NzBmZGYtNDUwYi00MDk3LWIwMzUtZGQ2YjI0Y2JiNGFkOjU3MDE2</t>
+          <t>YTQ4MzMzNDUtNWU2Yy00YmVmLWE4OWYtY2Y4ZWNkNjI2ZjM5OjU3MDE2</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>3.8825e+16</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7197,102 +7017,78 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>OWZmMDlmMTgtMGU0Ny00NDgxLTkxY2MtZTgyYmNiODI2NDAwOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Y2ZkYjU0ZGMtZmNlOC00MzBjLWFlNWQtZGRmMzdjYWQzNWUxOjU3MDE2</t>
+          <t>YTk2NmJhMzgtNDJkYS00OTQ3LWJlZWYtNzVlOGQzOTA4NjM4OjU3MDE2</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>1700</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Cliente informa: equipamento nao gela
-Conseguimos um tecnico para atendimento dentro da Bayer que dificil acesso para entrar
-Diagnostico tecnico micro vazamento e necessario fazer a carga de gas , e necessario laudo nitrogenio, maçarico (laudo da garrafa) e caneta para poder entrar com esses produtos para realizaçao do atendimento 
-senao vamos ter que pagar carreto + peça +Mao de obra para fazer serviço em oficina, custo menor pagar laudo e fazer na Bayer</t>
-        </is>
-      </c>
+        <v>2.1e+16</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MzE0YzQ5OTYtNGFlMy00NzkyLWJiYmYtZTY4NzJkNDcwNDIzOjU3MDE2</t>
+          <t>YmU4MzA1YWYtMThkMC00ODhkLTk0NTMtMzE3MGVkYjI2NGFiOjU3MDE2</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1700</v>
+        <v>2.1e+16</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>product</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>YTdiMzIyZmItN2E3NS00Mzc4LThiNzYtZWFlNDkxZTE2YzczOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>YTE2ZjAyY2UtYWNjZi00ODVkLTgxOWMtMDQ2ZjhmNWFiY2JhOjU3MDE2</t>
+          <t>ZTI4OGEyZDItNTQ3Ni00MmVjLWFlZTMtZDk4N2U3OGU3ODJmOjU3MDE2</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>494677</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
-B523034 - TELA PENEIRA DE INOX C/ FIO DE 0.35MM E ABERTURA DE 1.50MM (TELAS CUPECE) Qtd = 0,1 M2
-B527034 - MANTA ISOL FIBRA CERAMICA  ALUM 3810X610X38MM 2.32 M³ P/ROLO Qtd = 0,2 M2
-B538109 - TERMINAL C/ ISOLACAO CABO 1,5 - 2,5MM OLHAL AZUL TP2,5-4 - INTELLI Qtd = 6 PC
-B538119 - LUVA C/ ISOLACAO CABO 1,5 / 2,5 (EMENDA AZUL) INTELLI LEP-22 Qtd = 2 PC
-B538121 - CONJ.TERMOSTATO CAEM TU HC 120°C 30A 5MMX080MM 980MM 3/8CBP Qtd = 1 PC
-B538233 - INTERRUPTOR DE TECLA MARGIRUS 30223 M2FT1DE3Q/197 BIP. 10A VERDE Qtd = 1 PC
-B538345 - CABO ELETRICO FLEX. 1,5MM SILICONE C/ FIBRA DE VIDRO 200º Qtd = 2 MT
-B538683 - CABO PP C/PLUG CABO INJETADO 90º10A(3.0X1.5X2000MM) Qtd = 1 PC
-B538806 - TERMINAL DE ENCAIXE FEMEA "FASTON" C/ ISOL. (AZUL 1,5 - 2,5MM) Qtd = 4 PC
-B538A84 - PRENSA CABO BSP 1/2 LP+P/UV-LT-PA-40 DAN KRAUS MULLER Qtd = 1 PC
-B538I97 - ESPELHO PLASTICO CAEM PRETO Qtd = 1 PC
-B546053 - MICROVENT. LINEAR 110/220V 60HZ MOD. MINILINE Qtd = 1 PC
-B560251 - RESISTENCIA INOX ALETADA DE 800W X 220V (ESTUFA FRY WARMER) Qtd = 2 PC</t>
-        </is>
-      </c>
+        <v>3e+16</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>NTRjZjNjM2MtODlhYy00OTEzLTg0ZjEtYjZhYzY5NTRjMGY0OjU3MDE2</t>
+          <t>MWI1OWUzZTYtMTQxYi00NjY4LWFjZjAtNGI1OGE2Mjk3Nzk4OjU3MDE2</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>494677</v>
+        <v>3e+16</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7301,38 +7097,38 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+          <t>OTc4YTljYTItZGQ1Ni00MDIyLWEyMTItYWQwZWY4M2VkNWYxOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ZDBmMzE2ZjMtOGE3NS00Mzk5LWI3OWMtZjc1ODM0MmU3MDY5OjU3MDE2</t>
+          <t>MGJhYTRiMGQtYmU3NS00YjhhLTkwYTQtY2M0M2Y0MDVmOTY3OjU3MDE2</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>1050</v>
+        <v>47370</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>NTdmNWI0NDEtMWQxOC00M2E2LWE0ODEtODQyZDhlNDk0YzA0OjU3MDE2</t>
+          <t>NDNkODJkODMtNWM3NC00NjAyLWI2MzEtYWIyYWVjMGI4NTJhOjU3MDE2</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1050</v>
+        <v>47370</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7341,7 +7137,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>YTdlZmE0OWItMzc1YS00OThlLWEyZWEtNzllZjM4MTJlNzFmOjU3MDE2</t>
+          <t>OWRiNmYxNDMtZmIxMC00YThjLTllMTQtYTAxZGM4MjE4NjBkOjU3MDE2</t>
         </is>
       </c>
     </row>

--- a/orcamentos.xlsx
+++ b/orcamentos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,42 +2286,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
+          <t>NmU2NTU0ZTktZDBiNy00YzNiLTkyZjgtYWIzZjQ2YzE0MDg5OjU3MDE2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B1VS7ID2GL</t>
+          <t>RKGEPXYF-E</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MAQUINA 03</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>60478583000192 - FUNDACAO ANGLO BRAS. DE EDUC. E CULT SP</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Referente orçamento : Composteira - St Pauls</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="b">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>1756.6</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>490.38</t>
+          <t>1756.6</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-10-06T18:43:16.449Z</t>
+          <t>2025-12-11T14:05:43.837Z</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2334,12 +2338,12 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-09-29T18:44:47.397Z</t>
+          <t>2025-12-04T15:21:12.082Z</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+          <t>Y2NjZDRjMTgtOWYwOC00YjUwLWFiNzktOGU0NGNhZTQzMTg3OjU3MDE2</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2359,52 +2363,44 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzUzMTEwNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
+          <t>NzFkMWQwZWMtMDUwYi00ZjBhLThhYmItMTFmNDJjZmYyMTk4OjU3MDE2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BKHV0XAFEG</t>
+          <t>B1VS7ID2GL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Orçamento teste</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Reclamaçao do cliente :nao atinge temperatura</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
-        </is>
-      </c>
+          <t>MAQUINA 03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>490.38</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2414,7 +2410,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-09-04T16:01:06.048Z</t>
+          <t>2025-10-06T18:43:16.449Z</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2427,10 +2423,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-08-28T16:05:56.490Z</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>2025-09-29T18:44:47.397Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>NDIzOTk2OTo1NzAxNg==</t>
+          <t>MzU0MDM4MDo1NzAxNg==</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2460,36 +2460,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
+          <t>NzZhZGQwNGUtMmU5ZS00NjM5LTkzYzgtNWQxOTc3OGJlYWRlOjU3MDE2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R1R8PTIYBL</t>
+          <t>BKHV0XAFEG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
+          <t>Orçamento teste</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>orçamento</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>Reclamaçao do cliente :nao atinge temperatura</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Link do Relatório: https://app.fieldcontrol.com.br/relacionamento-cliente/#/relatorio/657fd93e-b9fd-457f-9f3a-db4c162fa0d7</t>
+        </is>
+      </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2499,7 +2503,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-11-10T19:48:40.136Z</t>
+          <t>2025-09-04T16:01:06.048Z</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -2512,14 +2516,10 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-11-03T19:49:41.839Z</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2025-08-28T16:05:56.490Z</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>NDgyMzkyMzo1NzAxNg==</t>
+          <t>NDIzOTk2OTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2549,70 +2549,66 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
+          <t>OGM2YTZkZjgtMmVjYS00MjA3LTk3YTktMDkzNTU0MDMzNDNiOjU3MDE2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HK9JZSR83</t>
+          <t>R1R8PTIYBL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>76500180001376 - COMPANHIA PROVIDENCIA INDUSTRIA E COMERCIO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>orçamento</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2023-06-07T21:55:05.692Z</t>
+          <t>2025-11-10T19:48:40.136Z</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>jose da silva</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>HENRIQUE</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
-        </is>
-      </c>
+          <t>Adriana Vieira Masini</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2023-05-31T21:56:50.448Z</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
+          <t>2025-11-03T19:49:41.839Z</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>MGIyNGUzMWQtMDM4OS00ZDc1LTg5MGEtYmNiNzViYTNjNGFiOjU3MDE2</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2620,88 +2616,92 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>MzE2ODMzNTo1NzAxNg==</t>
+          <t>NDgyMzkyMzo1NzAxNg==</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>expired</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
+          <t>OTEzYzY1NmQtOWU4OS00Y2VlLWJiNjMtNTI5N2YyMjA1N2M1OjU3MDE2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BJ0FAVCKBL</t>
+          <t>HK9JZSR83</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MAQUINA 01</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Autorizado por João</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1298.9</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Expirada</t>
+          <t>Aprovada</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-13T15:27:58.539Z</t>
+          <t>2023-06-07T21:55:05.692Z</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>jose da silva</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Kaue Teixeira Caldeira Venâncio</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>HENRIQUE</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>accounts/57016/quotations/913c656d-9e89-4cee-bb63-5297f22057c5/signatures/a8215aae-2f41-4179-a1ba-a923278bb210.png</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-11-06T15:28:06.348Z</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>NzdmMmMwZTItZWIyMy00ODUzLWJiZTgtM2Y3YTgzNGM0YzRmOjU3MDE2</t>
-        </is>
-      </c>
+          <t>2023-05-31T21:56:50.448Z</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>percentage</t>
@@ -2709,44 +2709,44 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>MzU0MDM4MDo1NzAxNg==</t>
+          <t>MzE2ODMzNTo1NzAxNg==</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OTcwY2YxNjktMmI1NS00ZWVkLWI3YmMtYzQxOGQzODUyMmY0OjU3MDE2</t>
+          <t>OTJkZTMyZDMtOWUxMi00NzVlLWEyMmEtMTBhMjdkYWFlZWU3OjU3MDE2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S1SWKWAKXG</t>
+          <t>BJ0FAVCKBL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>MAQUINA 01</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Reclamaçao do cliente: nao atinge temperatura, abaixo segue link</t>
+          <t>Autorizado por João</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -2755,46 +2755,42 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1298.9</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Aprovada</t>
+          <t>Expirada</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-09-04T16:07:52.834Z</t>
+          <t>2025-11-13T15:27:58.539Z</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-      